--- a/UNRWA.xlsx
+++ b/UNRWA.xlsx
@@ -413,8 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
@@ -450,6 +450,4675 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Syria, Lebanon and Jordan Humanitarian Appeal 2026 - Progress Report (For the reporting period 1 January – 30 June 2026) - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/syria-lebanon-and-jordan-humanitarian-appeal-2026-progress-report-reporting-period-1-january-30-june-2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Summary
+During the first half of 2026, Palestine Refugees across Syria, Lebanon and Jordan continued to confront a regional environment shaped by fragile early recovery, renewed conflict and persistent socioeconomic pressure. In Syria, the transition from emergency response towards recovery and reconstruction advanced against the legacy of 15 years of conflict and extensive damage to housing, infrastructure and basic services. In Lebanon, the escalation of hostilities in March triggered large-scale displacement and a sharp deterioration in humanitarian conditions. In Jordan, relative stability continued to contrast with wider regional volatility, while Palestine Refugees whose legal status is insecure or unrecognised, or who lack valid civil documentation, remained particularly vulnerable to economic hardship and barriers to employment and accessing essential services.
+In Syria, approximately 418,000 Palestine Refugees continued to face high levels of vulnerability, with 30 per cent remaining in protracted internal displacement, while 92 per cent were food insecure in 2025. Return movements, both within Syria and from abroad, continued to gather pace. The United Nations Relief and Works Agency for Palestine Refugees (UNRWA or ‘the Agency’) has been recording returns to Ein el Tal camp since 2016, Dera’a camp since 2017 and Yarmouk camp since 2020. By December 2024, the Agency had recorded 12,638 returns across the three camps. By June 2026, the cumulative total had risen to more than 50,000. For families seeking to rebuild their lives, the sustainability of return remained closely linked to access to habitable shelter, basic services such as education and health care and viable livelihood opportunities.
+In Lebanon, the March 2026 escalation of hostilities between Hezbollah and the State of Israel compounded longstanding socioeconomic vulnerabilities among Palestine Refugees, disrupting livelihoods, markets and access to essential services. Approximately 104,000 Palestine Refugees were projected to face crisis or worse levels of acute food insecurity between April and August 2026, up from around 69,000 during the preceding period (November 2025 to March 2026). In southern Lebanon, significantly impacted by the hostilities, the three Palestine Refugee camps in the Tyre area (El Buss, Burj Shemali and Rashidieh) had a pre-crisis combined population of approximately 28,000 people. Despite ongoing military operations, many remained in these areas because they lacked the resources to relocate. Others returned to the camps during periods of relative calm, and some families hosted displaced relatives and people from surrounding areas which were subject to more intensive military operations. Access to health care, water and sanitation, waste management and humanitarian supplies remained critical for those who stayed.
+UNRWA activated its emergency response in Lebanon on 4 March, opening collective emergency shelters at the Agency’s Siblin Training Centre and Battir School. During the reporting period, these shelters accommodated over 4,200 displaced people, including Palestine Refugees, Lebanese nationals and Syrian refugees, with occupancy fluctuating as displacement patterns shifted. Those accommodated received a package of assistance, including food and non-food items (NFIs).
+Palestine Refugees from Syria (PRS) in Lebanon continued to face additional pressures from economic hardship, insecurity and legal constraints, including the inability to renew residency permits since May 2024 due to policy changes. These pressures further contributed to decisions by some PRS to return to Syria during the reporting period.
+Jordan continued to grapple with the effects of regional instability, economic pressures and the protracted presence of refugees. Although the majority of Palestine Refugees in Jordan have citizenship, approximately 184,000 ex-Gazans and numerous PRS do not, constraining their access to legal protections, livelihood opportunities and public services. Of the 18,767 Palestine Refugees who fled the Syria conflict and continued to reside in Jordan as at 30 June, over 2,700 lacked any form of official Jordanian documentation. This included most of the more than 400 PRS residing in Garden Camp, a closed refugee reception facility where restrictions on movement further exacerbate their vulnerability. During the first half of 2026, 26,500 Syrian refugees returned from Jordan to Syria, while PRS movements remained comparatively limited.
+Against the backdrop of recovery, renewed conflict and continued regional fragility, UNRWA maintained essential humanitarian assistance across the three fields under the 2026 Syria, Lebanon and Jordan Humanitarian Appeal (HA), preserving access to critical services amid displacement, return movements and mounting socioeconomic pressures. In line with United Nations (UN) principles, the Agency also continued to support the right of individuals to return voluntarily to their habitual place of residence in Syria in a manner that is safe, dignified and sustainable.
+For Palestine Refugees returning to conflict-affected areas, those displaced by renewed hostilities and vulnerable families facing prolonged economic hardship, the Agency continued to provide health, education, relief, protection and other essential services. These interventions helped families meet immediate needs while preserving access to services and opportunities that remained critical to protection and stability. During the first half of 2026, multi-purpose cash assistance (MPCA) reached 122,792 conflict-impacted Palestine Refugees across Lebanon and Jordan, providing the most vulnerable with flexibility to prioritise essential expenditure including for food, medicine and rent.
+Health care remained central to the Agency’s response, helping mitigate the impact of declining household purchasing power on access to essential and critical treatment. Across the three fields of UNRWA operation, 485,396 health consultations were delivered or supported during the first half of 2026 under the HA, while a further 6,404 hospitalizations were subsidised for conditions requiring care beyond the primary level, including for chronic and critical conditions. Despite conflict, displacement and significant operational constraints, UNRWA education services continued throughout the reporting period. More than 60,000 students benefited from education support, including the distribution of back-to-school kits and stationery, recreational activities and school counselling. These interventions served to provide psychosocial support (PSS) to children affected by displacement and conflict-related disruption to their education.
+Support to Palestine Refugees returning to and within Syria also advanced during the reporting period. In Yarmouk camp, 634 families, including cross-border and internally displaced returnees, received cash assistance for shelter repairs through a community-based self-help approach. More broadly, 525 Palestine Refugees accessed short-term cash-for-work placements and 1,355 vulnerable students benefited from technical and vocational education and training (TVET), supporting immediate household needs while strengthening pathways towards sustainable employment and greater self-reliance. Protection interventions remained critical across Syria, Lebanon and Jordan, particularly where legal status, documentation, displacement and exposure to violence affected access to services, livelihoods and freedom of movement. During the first half of 2026, 5,262 Palestine Refugees received legal aid across the three fields. In Lebanon and Jordan, this included assistance to PRS seeking to voluntarily return to Syria. Explosive ordnance risk education (EORE) also reached 534 Palestine Refugees in Syria, while 1,136 people received emergency cash for protection across the three fields.
+Results under the HA were achieved amid an Agency-wide financial crisis that increasingly constrained the scope and scale of UNRWA operations. In January 2026, UNRWA was compelled to reduce service-delivery hours by 20 per cent, with a corresponding reduction in salaries for most local personnel. Within this context and despite prioritising the most urgent humanitarian needs in line with the Humanitarian Reset’s emphasis on directing scarce resources towards life-saving assistance, the HA remained severely underfunded. By 30 June 2026, only US$ 72 million, or 42 per cent of the US$170.2 million requirement, was available.
+Funding constraints under the HA prevented a number of priority interventions from being implemented during the first half of the year. In Syria, this included reintegration grants for Palestine Refugee returnee households, the rehabilitation of conflict-damaged installations and catch-up classes for students. In Lebanon, catch-up classes, humanitarian-funded TVET enrolment and planned health-centre rehabilitation were either not implemented or had to be delayed, while PRS received MPCA less frequently than planned. In Jordan, assistance for stranded Palestine Refugees15 and planned TVET, disability, livelihood and water, sanitation and hygiene (WASH) interventions could not be implemented under the HA.16 These gaps narrowed the package of support envisaged for the most vulnerable under the Appeal. Closing HA funding gaps through sustained, timely and flexible donor support will be critical to preventing the erosion of essential services, restoring interventions that could not be implemented during the first half of 2026 and enabling Palestine Refugees to meet immediate needs while pursuing more sustainable pathways to recovery.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:59:26.876139+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>IA Protection Advocacy Brief - Escalation in the Middle East and Beyond, September 2026 - World</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/world/ia-protection-advocacy-brief-escalation-middle-east-and-beyond-september-2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>The Inter-Agency Protection Advocacy Brief: Escalation in the Middle East &amp; Beyond provides a cross-regional protection analysis of the consequences of the escalation of hostilities since 28 February 2026 for populations affected directly or indirectly. Developed by a cross-regional reference group of NGOs and UN agencies, it draws on protection monitoring and analysis from partners working with affected populations. Intended for States, policymakers and advocates, it highlights the most critical emerging or exacerbated protection risks, promotes evidence-based support to specialized operational response, and supports humanitarian diplomacy and advocacy to prevent further harm. While cross-population in scope, it pays particular attention to internally displaced persons, refugees, migrants and returnees, reflecting the central role of internal displacement, refugee movements, migration and return dynamics in shaping protection risks faced by women, girls, men and boys across the region. The Brief highlights priority concerns including attacks on civilians and civilian infrastructure, forced displacement and return in adverse circumstances, legal identity and documentation challenges, gender-based violence, child protection risks, mental health and psychosocial needs, housing, land and property issues, exclusion from services, and the growing strain on national protection systems and frontline protection actors.
+The cross-regional analysis focuses on protection risks faced by populations in countries directly affected by the escalation in conflict – Iran, Iraq, Lebanon, Syria and Yemen. Alongside Syria, it also covers Afghanistan as countries affected by significant population movements (arrival and return) linked to the current situation, and references returns from Pakistan to Afghanistan. While hostilities have affected civilian populations and infrastructure across a broader range of countries in the region, the above contexts have been prioritised due to the magnitude of the crises, the severity of protection needs and the operational presence of established inter-agency protection mechanisms in support to the affected countries. Protection issues in the Occupied Palestinian Territory are presented separately.
+Disclaimer
+- UN Office for the Coordination of Humanitarian Affairs
+- To learn more about OCHA's activities, please visit https://www.unocha.org/.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:59:32.970990+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #14 on the Lebanon Emergency Response 2026 (16 July 2026) [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-14-lebanon-emergency-response-2026-16-july-2026-enar</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>All information is valid for 17 June - 14 July 2026
+Key Points
+- Following US-facilitated negotiations in Washington, Lebanon and Israel moved towards a conditional ceasefire on 3 June, contributing to a de-escalation of the conflict.
+- Amid renewed escalation between the United States and Iran on 25 June and a further intensification of tensions on 13 July following incidents affecting commercial shipping in the Strait of Hormuz, the situation continues to be closely monitored for potential spillover effects on the operating environment in Lebanon.
+- UNRWA launched its emergency response in Lebanon on 4 March 2026. The Agency has been operating two collective emergency shelters: Siblin Training Centre in Saida Area and Battir School in Nahr El Bared Camp in northern Lebanon.
+- By 14 July, all displaced persons accommodated in the two UNRWA emergency shelters had departed. Following this, UNRWA formally closed both facilities as emergency shelters. Battir School was closed on 11 July 2026, followed by Siblin Training Centre, which was closed on 13 July 2026.
+- Between 17 June and 14 July, no security incidents affecting on-duty UNRWA personnel or facilities were reported.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:59:39.011228+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>UNRWA Department of Health Annual Report 2025 - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/unrwa-department-health-annual-report-2025</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>This annual report presents a comprehensive overview of the work undertaken by UNRWA’s Department of Health, highlighting the Agency’s continued presence, mandate, and indispensable role in delivering essential services to Palestine Refugees. It showcases UNRWA’s achievements in sustaining quality and effective healthcare services despite increasingly complex and protracted emergencies across its five fields of operation, including the Gaza Strip and the occupied West Bank. In recent years, UNRWA and its staff have operated under extraordinary pressure marked by conflict, displacement, and resource constraints. Despite these challenges, the Agency has remained committed to ensuring equitable access to care and safeguarding public health.
+This report aims to document operational performance and programmatic outcomes and reaffirm the critical importance of UNRWA’s mandate and operational role. In doing so, it highlights the Agency’s responsiveness during crises, its continuous efforts to strengthen emergency preparedness and response capacities, and its strategic investments in health system digitalisation, telemedicine, and service improvement. Simultaneously, the report provides forward-looking insights into priorities, challenges, and opportunities, outlining a vision for enhancing resilience, efficiency, and sustainability in health services delivery.
+Ultimately, this report serves as both a record of accountability and an instrument of advocacy, demonstrating that, amid ongoing adversities, UNRWA remains essential, adaptive, and committed its mission to protect and promote the health and dignity of Palestine Refugees, now and into the future.
+Holistic care themes
+UNRWA’s Department of Health provides holistic healthcare to registered Palestine Refugees across its five fields of operation: the Gaza Strip, the occupied West Bank, including East Jerusalem, Jordan, Syria, and Lebanon.
+Primary healthcare is the main pillar of the health programme, ensuring adequate coverage and comprehensive healthcare. Additionally, support is provided to patients requiring secondary and tertiary healthcare, including coordination of referrals and financial coverage of outpatient consultations and inpatient care (i.e., hospital admission for more specialised treatment or surgery).
+Vaccination, newborn screening, and detection of growth problems, along with referrals, are offered to children below five. The essential programme of immunisation follows the host country programme, and UNRWA serves as a partner in essential immunisation and in reporting on vaccine-preventable outbreaks.
+Services provided to women include pre-conception, antenatal and post-natal care, as well as family planning services, multiple micronutrient supplementation (MMS), support against gender-based violence, and other outpatient services. Nutrition services are provided to pregnant women, infants, and children, especially in the Gaza Strip and Lebanon, where malnutrition is more common than in other fields due to conflict, instability, and displacement.
+Nursing and midwifery services play a pivotal role in linking maternal and child health interventions and in delivering planned training programmes to frontline workers. This work is carried out through workshops and discussions held at field offices and headquarters, thereby opening avenues for contact across the fields.
+In the context of non-communicable diseases (NCDs), UNRWA provides a robust programme for preventing and managing diabetes and hypertension. Prevention interventions include screening for NCDs and health promotion, while management includes counselling, medications, and insulin supply, following technical instructions designed by UNRWA which are aligned with the latest WHO protocols.
+Mental health is a key domain of UNRWA’s services. The Mental Health and Psychosocial Support (MHPSS) programme systematically screens vulnerable population groups, including pregnant women, children, and NCDs patients with uncontrolled disease, for mental health and psychosocial conditions. Individuals identified as being in need receive appropriate, tiered psychosocial and mental health interventions, including support for depression, with different levels of assistance provided for those with higher depression scores.
+Outpatient services include dental care, physiotherapy, laboratory services, and radiology. Oral screening is performed for first-year school students, along with medical and physical examinations.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:59:45.074579+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>UNRWA - Lebanon Quarterly Protection Update (Q1 2026) - Lebanon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-lebanon-quarterly-protection-update-q1-2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>During January and February 2026, the security situation in Lebanon remained tense but relatively contained. Protection monitoring highlighted persistent vulnerabilities among Palestine refugees, including worsening poverty levels, deterio‐ rating living conditions and ongoing anxiety, particularly among refugees living in camps located near high-risk areas. In early March, after Hezbollah fired rockets into Israel and the Israeli military responded, there was a sharp escalation in hostili‐ ties, triggering widespread displacement, rising civilian casual‐ ties and increased pressure on services. By the end of March, over one million people were displaced nationwide, including more than 136,731 individuals using collective shelters.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:59:51.048171+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #13 on the Lebanon Emergency Response 2026 (22 June 2026) - Lebanon</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-13-lebanon-emergency-response-2026-22-june-2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>All information is valid for 3 - 16 June 2026
+Key Points
+- Following US-facilitated negotiations in Washington, Lebanon and Israel announced on 3 June an agreement on a conditional ceasefire aimed at ending hostilities linked to the broader regional conflict. The agreement is contingent on a complete cessation of fire by Hezbollah and the withdrawal of its operatives from areas south of the Litani River.
+- The humanitarian situation in Lebanon remains fragile and unpredictable, with armed clashes continuing despite the ceasefire, alongside periodic escalations, including airstrikes, evacuation warnings, and new displacement, particularly in the south of the country.
+- UNRWA launched its emergency response in Lebanon on 4 March 2026. Since then, the Agency has been operating two collective emergency shelters[1]: Siblin Training Centre in Saida Area and Battir School in Nahr El Bared Camp in northern Lebanon.
+- By 16 June, a total of 1,911 displaced people from 605 families were registered in the two UNRWA emergency shelters.
+- Between 3 and 16 June, no security incidents affecting on-duty UNRWA personnel or facilities were reported.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:59:57.004418+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Inter-Agency Refugee Protection Overview for the Middle East Situation (June 2026) - Iran (Islamic Republic of)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/iran-islamic-republic/inter-agency-refugee-protection-overview-middle-east-situation-june-2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>The Inter-Agency Refugee Protection Overview for the Middle East Situation provides a cross-regional analysis of emerging protection risks and trends since the escalation of hostilities on 28 February 2026. The document draws on analysis from county level Protection Working Groups, relevant coordination forums and partners across the affected regions. The overview is intended to support shared situational awareness, inform preparedness and response adjustments, and highlight where displacement-related protection risks are intensifying — including in contexts where large-scale refugee movements have not occurred.
+From a displacement perspective, the escalation has unfolded on top of an already overstretched regional baseline, with over 31 million forcibly displaced people and recent returnees across the wider Middle East region before 28 February 2026. The current cross‑regional protection environment is shaped by the convergence of multiple compounding factors that have escalated in 2026 — including active conflict, erosion of International Humanitarian Law (IHL) and gender equality norms, macroeconomic decline and underlying climate-related vulnerabilities — producing increasingly complex and multilayered protection risks that require integrated, sustained inter‑agency response. 
+In Iran and Lebanon, hostilities have directly generated acute protection crises — including large-scale internal displacement, civilian casualties, damage to infrastructure and severe strain on national protection systems. Refugees and others in need of international protection face heightened risks linked to legal status, while women and girls are disproportionately affected by gender-based violence, increased caregiving responsibilities and barriers to assistance. Across neighbouring countries, growing risks are driven by macroeconomic shocks, service degradation, legal insecurity and psychosocial distress. Returns under adverse circumstances, falling short of voluntary and dignified character and of sustainable conditions, are a central cross‑regional protection concern. Returns to Syria and Afghanistan (including deportations from Iran and Pakistan) are taking place in contexts where reintegration capacity remains constrained. This can in turn derail fragile recovery efforts, overwhelm communities and generate new protection concerns as well as new displacement or onward movements.
+These dynamics are unfolding amid significant reductions in humanitarian and development funding, curtailing operational actors' ability to sustain protection responses and preparedness capacities. Taken together, the trends point to a protection environment under stress, with deepening vulnerabilities and increasing strain on national institutions, underscoring the need to link refugee protection to national systems and development planning frameworks.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:00:03.030921+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #12 on the Lebanon Emergency Response 2026 (4 June 2026) [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-12-lebanon-emergency-response-2026-4-june-2026-enar</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>All information is valid for 20 May - 2 June 2026
+Key Points
+- A 10-day ceasefire between Israel and Lebanon came into effect on 16 April. It was extended by three weeks on 23 April and again by 45 days on 15 May, bringing the current end date to mid-June. US-facilitated political negotiations continued on 2 June at the State Department in Washington, with the parties reviewing progress and working toward further extending the ceasefire.
+- The humanitarian situation in Lebanon remains fragile and unpredictable, with hostilities continuing despite the ceasefire, alongside periodic escalations, including airstrikes, evacuation warnings, and new displacement, particularly in the south of the country.
+- UNRWA launched its emergency response in Lebanon on 4 March. Since then, the Agency has been operating two collective emergency shelters[1]: Siblin Training Centre in Saida Area and Battir School in Nahr el-Bared Camp in northern Lebanon.
+- By 2 June, a total of 2,148 displaced people from 661 families were registered in the two UNRWA emergency shelters. This represents a significant increase from the 1,264 people recorded in the previous reporting period and follows the issuance of evacuation warnings and increased intensity of military activity, particularly south of the Litani River.
+- Between 20 May and 2 June, no security incidents affecting on-duty UNRWA personnel or facilities were reported.
+Overall Situation
+- By 26 May, the Ministry of Social Affairs had documented the displacement of over 1.1 million individuals[2], including 127,714 people in 631 shelters[3]. Monitoring returns remains challenging due to the fluidity of population movements.
+- On 27 May, Israeli forces issued evacuation warnings for all areas south of the Zahrani River. This included areas such as Tyre City, which has three adjacent Palestine Refugee camps, as well as Adloun and Sarafand, where Palestine Refugees reside.
+- Airstrikes on 25 and 28 May targeted the areas near the Palestine Refugee camps of Rashidieh and El Buss. Combined with evacuation warnings, this resulted in a significant exodus from the camps, with around one-third of the camps’ usual population of 28,000 estimated to have left. Most displaced families seek shelter with relatives or host communities.
+- During the reporting period, Hezbollah continued to launch drones and rockets into northern Israel. On 30 May alone, Israeli authorities reported that over 25 projectiles were launched from Lebanon into Israel.
+- In a statement on 1 June, Israeli Prime Minister Benjamin Netanyahu said he had instructed Israeli forces to strike targets in Beirut. In reaction, large numbers of people left the southern suburbs of the city.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:00:09.176403+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #11 on the Lebanon Emergency Response 2026 (21 May 2026) [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-11-lebanon-emergency-response-2026-21-may-2026-enar</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>All information valid for 6 - 19 May 2026
+Key Points
+- A 10-day ceasefire between Israel and Lebanon came into effect at midnight on 16 April. On 23 April, US President Donald Trump announced that the ceasefire would be extended for an additional three weeks, following a second high-level trilateral meeting between representatives of Israel, the United States and Lebanon. On 15 May, the ceasefire was extended again for an additional 45 days after two days of talks, facilitated by the United States, concluded with an agreement to hold further meetings in the coming weeks.
+- The humanitarian situation in Lebanon remains fragile and unpredictable, with a continued risk of conflict escalation and military operations in the south of the country.
+- UNRWA launched its emergency response in Lebanon on 4 March. Since then, the Agency has been operating two collective emergency shelters[1]: Siblin Training Centre in Saida Area and Battir School in Nahr el-Bared Camp in northern Lebanon.
+- By 19 May, a total of 1,264 displaced people from 372 families were registered in the two UNRWA emergency shelters. This represents a slight increase from 1,132 people recorded in the previous reporting period and follows the issuance of one evacuation order by Israeli forces over the past two weeks.
+- Between 6 and 19 May, no security incidents affecting on-duty UNRWA personnel or facilities were reported.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:00:15.336494+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #10 on the Lebanon Emergency Response 2026 (7 May 2026) [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-10-lebanon-emergency-response-2026-7-may-2026-enar</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>All information valid for 29 April - 5 May 2026
+Key Points
+- A 10-day ceasefire between Israel and Lebanon came into effect at midnight on 16 April. On 23 April, US President Donald Trump announced that the ceasefire would be extended for an additional three weeks, following a second high-level trilateral meeting between representatives of Israel, the United States and Lebanon.
+- The humanitarian situation in Lebanon remains fragile and unpredictable, with a continued risk of conflict escalation and military operations in the south of the country.
+- UNRWA launched its emergency response in Lebanon on 4 March. As of 21 April, it operates two emergency shelters[1]: Siblin Training Centre (STC) in Saida Area and Battir School in Nahr el-Bared Camp in northern Lebanon.
+- Renewed evacuation orders were issued by the Israeli military between 30 April and 1 May for 10 villages in southern Lebanon and Nabatieh District north of the Litani River area.
+- By 5 May, a total of 1,132 displaced people (328 families) were registered in the two UNRWA emergency shelters. This represents an increase from 951 people recorded in the previous week and follows the issuance of evacuation orders during the period.
+- Between 29 April and 5 May, no security incidents affecting on-duty UNRWA personnel or facilities were reported.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:00:21.510121+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Q1 Progress Report: Implementing the Colonna Report at UNRWA (January 2026 – March 2026) - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/q1-progress-report-implementing-colonna-report-unrwa-january-2026-march-2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Safeguarding Neutrality, Strengthening Trust
+This Quarterly Colonna Progress Report provides a summary of major milestones and developments during the first quarter of 2026 in the Agency’s implementation of the 50 recommendations of the ‘Colonna Report’, formally known as the Independent Review of Mechanisms and Procedures to Ensure Adherence by UNRWA to the Humanitarian Principle of Neutrality . It also summarises progress across thematic categories, associated funding requirements, and the Agency’s approach to sustainability of the reforms.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:00:27.512840+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #9 on the Lebanon Emergency Response 2026 (29 April 2026) [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-9-lebanon-emergency-response-2026-29-april-2026-enar</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>All information valid for 22 April – 28 April 2026
+Key Points
+- A 10-day ceasefire between Israel and Lebanon came into effect at midnight on 16 April. On 23 April, US President Donald Trump announced that the ceasefire would be extended for an additional three weeks, following a second high-level trilateral meeting between representatives of Israel, the United States and Lebanon.
+- Following the announcement of the ceasefire, both the Israeli military and Hezbollah called on displaced populations not to return immediately to areas south of the Litani River.
+- The humanitarian situation in Lebanon remains fragile and unpredictable, with a continued risk of conflict escalation and military operations in the south of the country.
+- UNRWA launched its emergency response in Lebanon on 4 March. As of 21 April, it operates two emergency shelters[1]: Siblin Training Centre (STC) in Saida Area and Battir School in Nahr el-Bared Camp in northern Lebanon.
+- By 28 April, a total of 951 displaced people (274 families) were registered in the two UNRWA emergency shelters, reflecting a substantial decrease compared to 1,337 people recorded last week. This is mainly due to the extension of the ceasefire and subsequent population returns.
+- Between 22 and 28 April, no security incidents affecting on-duty UNRWA personnel or facilities were reported.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:00:33.505758+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #8 on the Lebanon Emergency Response 2026 (23 April 2026) [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-8-lebanon-emergency-response-2026-23-april-2026-enar</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>All information valid for 15 April – 21 April 2026
+Key Points
+- A 10-day ceasefire between Israel and Lebanon came into effect at midnight on 16 April, following the first direct talks between the two sides in over 30 years on 14 April. While negotiations are ongoing between the parties towards a lasting peace agreement, the humanitarian situation in Lebanon remains fragile.
+- UNRWA launched its emergency response in Lebanon on 4 March. As of 21 April, it operates two emergency shelters[1]: Siblin Training Centre (STC) in Saida Area and Battir School in Nahr el-Bared Camp in northern Lebanon.
+- By 21 April, a total of 1,337 displaced people (401 families) were registered in the two UNRWA emergency shelters, reflecting a substantial decrease compared to the previous week’s 1,741 people. This is mainly due to the 16 April ceasefire and subsequent population returns.
+- On 13 March, UNRWA launched an appeal for US $12.3 million to support up to 10,000 people in the Agency’s two emergency shelters and 63,000 vulnerable Palestine Refugees outside its shelters.
+- Between 15 and 21 April, no security incidents affecting on-duty UNRWA personnel or facilities were reported.
+Overall Situation
+- By 20 April, the Ministry of Social Affairs had documented the displacement of over 1,1 million individuals[2], including 117,421 people in 631 shelters[3].
+- More than 250,000 people have crossed into Syria since 2 March, including over 1,200 Palestine Refugees from Syria who had fled to Lebanon in the past[4].
+- Despite cautious optimism after the announcement of the 10-day ceasefire, access to areas south of the Litani River, including 55 villages, remains restricted due to expanded activity by Israeli forces inside southern Lebanon. Damaged infrastructure, unexploded ordnance, and limited basic services are causing severe humanitarian challenges, with authorities urging caution regarding return movements.
+- Voluntary returns following the ceasefire announcement were limited and uneven, with about 26 per cent of displaced people leaving shelters in the first 48 hours[5], often only temporarily to check homes or collect belongings before returning to the shelters.
+- Despite the ceasefire, instability persists. On 18 April, a UN peacekeeper was killed and three others injured when a UNIFIL patrol came under fire in southern Lebanon. The UN Secretary-General condemned the attack, indicating that Hezbollah was presumed responsible. One of the injured peacekeepers subsequently died.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:00:39.652271+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #7 on the Lebanon Emergency Response 2026 (16 April 2026) [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-7-lebanon-emergency-response-2026-16-april-2026-enar</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Key Points
+- UNRWA launched its emergency response in Lebanon on 4 March 2026. As of 14 April, it operates two emergency shelters[1]: Siblin Training Centre (STC) in Saida Area and Battir School in Nahr el-Bared Camp in northern Lebanon.
+- By 14 April, a total of 1,741 displaced people (519 families) had been registered in the two UNRWA emergency shelters.
+- On 13 March, UNRWA launched an appeal for US $12.3 million to support up to 10,000 people in the Agency’s two emergency shelters and 63,000 vulnerable Palestine Refugees outside of its shelters.
+- On 8 April, a two-week ceasefire between the United States, Israel and Iran was announced. Israeli authorities subsequently communicated that Lebanon was excluded from the ceasefire arrangements. The security situation further deteriorated, marked by over 100 Israeli airstrikes across Lebanon on the same day.
+- On 9 April, most UNRWA services outside of its shelters, including administrative offices, schools, clinics and sanitation, were suspended for one day due to intensified airstrikes across Lebanon. However, services in North Lebanon Area as well as those for displaced persons in the shelters continued.
+- Between 8 and 14 April, no security incidents affecting on-duty UNRWA personnel or facilities were reported.
+Overall Situation
+- By 13 April, the Ministry of Social Affairs had documented the displacement of over 1.1 million individuals[2], including 140,914 in 684 shelters[3].
+- More than 200,000 people have crossed into Syria since 2 March, including over 1,200 Palestine Refugees from Syria who had fled to Lebanon in the past[4].
+- On 9 April, Lebanon observed a National Day of Mourning, signalling the severity of the impact of the airstrikes carried out the previous day.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:00:45.661769+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #6 on the Lebanon Emergency Response 2026 (9 April 2026) [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-6-lebanon-emergency-response-2026-9-april-2026-enar</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Key Points
+- UNRWA launched its emergency response in Lebanon on 4 March 2026. As of 7 April, it operates two emergency shelters[1]: Siblin Training Centre (STC) in Saida Area and Battir School in Nahr el-Bared Camp in northern Lebanon.
+- By 7 April, a total of 1,719 displaced people (512 families) had been registered in the two UNRWA emergency shelters.
+- On 13 March, UNRWA launched an appeal for US$12.3 million to support up to 10,000 people in the Agency’s two emergency shelters and 63,000 vulnerable Palestine Refugees outside of shelters.
+- Tensions in Ein El Hilweh Camp remain elevated in the wake of armed clashes that broke out at the end of March[2].
+- Between 1 and 7 April, no security incidents affecting on-duty UNRWA personnel were reported.
+Overall Situation
+- By 6 April, the Ministry of Social Affairs had documented the displacement of 1,049,000[3] individuals, including 138,532 individuals hosted in 678 shelters[4].
+- Between 1 and 7 April, the security situation in Lebanon remained highly volatile and deteriorating.
+- More than 200,000 people have crossed into Syria since 2 March, including over 1,200 Palestine Refugees from Syria[5].
+- In Ein El Hilweh Camp, critical operations have resumed since 2 April following the armed clashes and heightened tensions among armed groups on 30 March.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:00:51.990164+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #5 on the Lebanon Emergency Response 2026 (2 April 2026) [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-5-lebanon-emergency-response-2026-2-april-2026-enar</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>All information valid for 26 March – 31 March 2026
+Key Points
+- UNRWA launched its emergency response in Lebanon on 4 March 2026. As of 31 March, it operates two emergency shelters[1]: Siblin Training Centre in Saida Area and Battir School in Nahr el-Bared Camp in northern Lebanon.
+- By 31 March, a total of 1,867 displaced people (565 families) had been registered in the two UNRWA emergency shelters.
+- On 13 March, UNRWA launched an appeal for US$12.3 million to support up to 10,000 people in the Agency’s two emergency shelters and 63,000 vulnerable Palestine Refugees outside of shelters.
+- Between 26 and 31 March, no security incidents affecting on-duty UNRWA personnel were reported.
+Overall Situation
+- By 30 March, the Ministry of Social Affairs had documented the displacement of 1,049,000[2] individuals, including 136,156 individuals hosted in 669 shelters[3].
+- More than 189,000 people have crossed into Syria since 2 March, including over 1,200 Palestine Refugees from Syria[4].
+- In Ein El Hilweh Camp, all operations have been suspended since 30 March due to armed clashes and heightened tensions among armed groups.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:00:58.037764+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #4 on the Lebanon Emergency Response 2026 (26 March 2026) [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-4-lebanon-emergency-response-2026-26-march-2026-enar</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>All information valid for 19 March – 25 March 2026
+Key Points
+- UNRWA launched its emergency response in Lebanon on 4 March 2026. As of 25 March, it operates two collective emergency shelters[1] : Siblin Training Centre in the Saida Area and Battir School in Nahr el-Bared Camp in northern Lebanon.
+- By 25 March, a total of 1,892 displaced people (569 families) had been registered in the two UNRWA emergency shelters.
+- On 13 March, UNRWA launched an appeal for US$12.3 million to support up to 10,000 people in the Agency’s emergency shelters and 63,000 vulnerable Palestine Refugees outside of shelters.
+- Between 19 and 25 March, no security incidents affecting on-duty UNRWA personnel were reported.
+Overall Situation
+- By 24 March, the Ministry of Social Affairs had documented the displacement of 1,049,000[2] individuals, including 134,921 in 657 shelters[3].
+- Between 22 and 23 March, several key transport crossings in South Lebanon were damaged, including the Qasmiyeh Bridge and other Litani River bridges. Multiple airstrikes blocked major routes making it difficult to connect to the south of the country.
+- UNRWA is working with community-based organisations, local and international non-governmental organisations in its emergency shelters to provide a full range of services. In its emergency response, UNRWA coordinates with partners on the ground, which helps the Agency deal with is its financial limitations.
+- As of 23 March, approximately 147,823 people had fled Lebanon, crossing into Syria[4].</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:01:04.106539+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #3 on the Lebanon Emergency Response 2026 (19 March 2026) [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-3-lebanon-emergency-response-2026-19-march-2026-enar</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>All information valid for 11 March – 18 March 2026
+Key Points
+- UNRWA launched its emergency response in Lebanon on 4 March 2026. As of March 18, it operates two collective emergency shelters: Siblin Training Centre in the Saida Area and Battir School in Nahr el-Bared Camp in northern Lebanon.
+- On 11 March, UNRWA ceased managing the shelter at Bir Zeit/Beit Jala School compound.[1]
+- By 18 March, a total of 1,284 displaced people (371 families)[2] had been registered in UNRWA shelters.
+- UNRWA launched an appeal for US $12.3 million to support up to 10,000 people in UNRWA emergency shelters and 63,000 vulnerable Palestine Refugees outside shelters.
+- Between 11 and 18 March, no security incidents affecting on duty UNRWA personnel were reported.
+Overall Situation
+- By 16 March, the Ministry of Social Affairs had documented the displacement of 1,049,328 individuals, including over 130,000 in more than 612 shelters[3].
+- Between 11 and 18 March, the security situation in Lebanon continued to deteriorate as the conflict between Hezbollah and Israeli forces intensified. New evacuation orders were issued during the night of 17 March and the early hours of 18 March for parts of Tyre, including the three Palestine Refugee camps namely, Burj Shemali, Rashidieh and El Buss as well as for the southern suburbs of Beirut and the Bachoura neighbourhood in Beirut. This led to a sudden and substantial influx of individuals arriving at UNRWA emergency shelters on 18 March.
+- On 16 March, the Israeli forces announced the start of a ground incursion into southern Lebanon.
+- UNRWA is working with community-based organisations, local and international non-governmental organisations in its emergency shelters to provide a full range of services. In its emergency response, UNRWA ensures critical coordination with partners on the ground, to help address the Agency’s limited financial resources.
+- Between 2 and 14 March, an estimated 125,977 individuals crossed the border into Syria[4].</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:01:10.162727+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>UNRWA Lebanon Priority Emergency Response Requirements (March 2026) - Lebanon</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-lebanon-priority-emergency-response-requirements-march-2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>In response to the ongoing escalation in Lebanon, the United Nations Relief and Works Agency for Palestine Refugees in the Near East (UNRWA) is urgently seeking US$ 12.3 million to fund its priority emergency response over the next 90 days. These funds are required to address the immediate needs for food, shelter, health, protection, water and sanitation services for up to 10,000 individuals seeking safety in UNRWA-managed collective emergency shelters in Lebanon, and for up to 63,000 vulnerable conflict-impacted Palestine Refugees living outside of these shelters. In providing assistance, UNRWA will focus on serving the needs of vulnerable groups, including women, children, persons with disabilities, persons with fragile legal status, and the elderly.
+Lebanon context and needs
+Cross-border hostilities between Israel and Hezbollah escalated on 2 March with the entry of Lebanon’s Hezbollah in the Iran war. The Government of Israel issued displacement warnings and orders on 5 March impacting over 100 villages in the area south of the Litani River and the Bekaa region, as well as Beirut’s southern suburbs.1 Airstrikes intensified across the southern suburbs of Beirut, the governorates of the South, Saida and the Bekaa. Two targeted airstrikes also hit the Palestine Refugee camps of Ein El Hilweh (Saida) and Beddawi (Tripoli). As a result, as of 9 March, over 500,000 people are estimated to have been displaced within Lebanon, with over 100,000 people moving to collective shelters.2 Further displacement is anticipated as the situation remains fluid. The Government of Lebanon suspended education services nationwide, affecting students across the country, including 34,541 children enrolled in UNRWA schools.
+In response to the arrival of displaced Palestine Refugees, Lebanese and Syrian families in search of greater safety from conflict-affected areas in the South and in Beirut, the Agency has activated its emergency response. By 6 March, UNRWA had opened two collective shelters, in Siblin (Saida area) and in Nahr el-Bared (North area), providing ready‑to‑eat meals, safe drinking water, mattresses, pillows, hygiene items, and other essential non‑food items (NFIs). In line with humanitarian principles and to support social cohesion, the Agency shelters are open to all persons in need, irrespective of status or nationality. As at 9 March, 1,420 individuals had been registered in the UNRWA shelters, with numbers expected to increase as the conflict intensifies.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:01:16.360033+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #2 on the Lebanon Emergency Response 2026 (12 March 2026) [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-2-lebanon-emergency-response-2026-12-march-2026-enar</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>All information valid for 7 March – 10 March 2026
+Key Points
+- UNRWA activated its emergency response in Lebanon on 4 March 2026, when the Agency opened one emergency shelter in the Saida Area, located in Siblin Training Centre and the adjacent Bir Zeit/Beit Jala school compound. On 5 March, UNRWA opened a second emergency shelter in the Nahr el-Bared camp located north of Tripoli that comprises a total of six school buildings.
+- By 10 March, a total of 1,567 displaced people (436 families)[1] had been registered in UNRWA shelters.
+- Following evacuation orders issued on 5 March for several areas in the southern suburbs of Beirut and multiple towns and villages in South Lebanon, displacement among residents have continued to be reported.
+- On 8 March, an airstrike was reported on the periphery, but within the security barrier, of Ein El Hilweh Palestine Refugee Camp in Saida Area. The incident occurred in the northern surroundings of the camp in the Taamir area, a mixed‑community neighbourhood where Palestine Refugees and Lebanese citizens reside.
+- Between 7 and 10 March, no security incidents affecting UNRWA facilities or personnel were reported. On 11 March, UNRWA declared that Bir Zeit/Beit Jala school is no longer designated as an UNRWA emergency shelter. Displaced persons remaining in the premises were invited to relocate to the adjacent Siblin shelter and the UN flag was taken down, meaning that the shelter is no longer being managed by UNRWA.
+Overall Situation
+- By 9 March, the Ministry of Social Affairs had documented the displacement of over 667,000 individuals, including over 119,000 in more than 567 shelters.
+- Between 7 and 10 March, the security situation in Lebanon continued to deteriorate as hostilities between Hezbollah and Israeli forces intensified.
+- During the reporting period, airstrikes continued across South Lebanon (north and south of the Litani river), the Bekaa Valley, Beirut’s southern suburbs and locations in central Beirut.
+- UNRWA is working with a range of partner organisations (community based, local NGOs and international NGOs) in its emergency shelters to provide a full range of services. In its emergency response, UNRWA ensures critical coordination with partners on the ground, to complement the Agency’s limited financial resources.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:01:22.458276+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #1 on the Lebanon Emergency Response 2026 (6 March 2026) [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-1-lebanon-emergency-response-2026-6-march-2026-enar</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>All information valid for 2 March – 6 March 2026
+Key Points
+- UNRWA activated its Emergency Response in Lebanon on 4 March 2026 when the Agency opened one emergency shelter in the Saida Area, Siblin Training Centre and two adjacent schools. On 5 March, UNRWA opened a second emergency shelter in the Nahr el-Bared camp located North of Tripoli that comprises a total of six school buildings.
+- By 6 March, an estimated total of 1,300 displaced people had been registered in UNRWA shelters. UNRWA continues to register and record the families and will produce a detailed displacement dashboard.
+- Hostilities escalated in the night of 1 to 2 March, when Hezbollah launched missiles and drones toward northern Israel, marking its first major operation since the Cessation of Hostilities Agreement of November 2024.
+- On 2 March, Israeli forces initiated a widespread aerial campaign, conducting intense airstrikes across South Lebanon, the Bekaa Valley, and the southern suburbs of Beirut. Evacuation orders for over 50 towns and villages mainly south of the Litani river, were issued by Israeli forces. On 4 March, Israeli forces also issued evacuation orders for the southern suburbs of Beirut (Dahiyeh) and several villages in the Bekaa Valley.
+- No airstrike incident was reported in Palestine Refugee camps in Lebanon.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:01:34.986165+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Q4 Progress Report: Implementing the Colonna Report at UNRWA (October 2025 - December 2025) - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/q4-progress-report-implementing-colonna-report-unrwa-october-2025-december-2025</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>This Quarterly Colonna Progress Report provides a summary of major milestones and developments during Q4 2025 in the Agency’s implementation of the 50 recommendations of the ‘Colonna Report’, formally known as the Independent Review of Mechanisms and Procedures to Ensure Adherence by UNRWA to the Humanitarian Principle of Neutrality. It also summarizes key developments across thematic categories and associated funding requirements.
+oPt + 2 more</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:01:40.971683+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>UNRWA Humanitarian Appeal 2026: Syria, Lebanon and Jordan - Syrian Arab Republic</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/syrian-arab-republic/unrwa-humanitarian-appeal-2026-syria-lebanon-and-jordan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Executive Summary
+In 2026, Palestine refugees across Syria, Lebanon and Jordan will continue to endure the compounded impacts of conflict, displacement and precarious legal status. Ongoing regional instability and entrenched socioeconomic crises are expected to intensify humanitarian needs. These interconnected challenges underscore the need for a cohesive regional humanitarian and protection response, particularly as fragile stabilisation and early recovery efforts begin to take hold.
+In Syria, where 92 per cent of Palestine refugees (over 384,000 individuals) face food insecurity,1 approximately 30 per cent (over 125,000 individuals) remain in protracted internal displacement. The extensive destruction of Palestine refugee camps, most notably Ein el Tal, Yarmouk and Dera’a, which were formerly home to one-third of all Palestine refugees in the country, continues to pose significant obstacles to sustainable return. Despite this, following the fall of the Bashar al-Assad government, 2025 saw a sharp increase in return movements to and within Syria, frequently driven by economic pressures in displacement and precarious legal status abroad, alongside pull factors such as family reunification. In Lebanon, continued socioeconomic hardship, rising violence in camps and restrictions on legal status, continue to entrench multi-generational exclusion, with more than 80 per cent of Palestine refugees living below the poverty line.2 In Jordan, Palestine refugees without citizenship, including many ex-Gazans3 and Palestine refugees from Syria (PRS), remain marginalised and heavily dependent on humanitarian assistance due to limited access to employment, documentation and essential services.
+In 2026, the United Nations Relief and Works Agency for Palestine Refugees in the Near East (UNRWA or ‘the Agency’) will focus its humanitarian response in Syria, Lebanon and Jordan on preserving the dignity and resilience of Palestine refugees amid ongoing economic, social and security crises. In this regard, the Agency will prioritise life-saving assistance, protection and support for voluntary, dignified and sustainable returns to Syria through a multisectoral approach, targeting interventions to the most vulnerable Palestine refugees across all three countries. These include individuals without legal status, persons with disabilities, older persons, female‑headed households, at risk youth and returnees who face heightened risks and significant barriers to accessing their rights and essential services. Concurrently, UNRWA will remain prepared to respond swiftly and at scale to conflict and other crises, including displacement from renewed regional or local conflicts that may emerge.
+Under the 2026 Syria, Lebanon and Jordan Humanitarian Appeal (HA), UNRWA will provide cash assistance to approximately 124,000 vulnerable Palestine refugees to meet their most basic needs in a flexible and dignified manner, encompassing individuals affected by crisis-related shocks, as well as those undertaking voluntary return to or within Syria. To strengthen accountability and improve efficiency, the Agency will continue to implement advanced assurance measures, including digital identity verification, as a cornerstone for delivering targeted and transparent assistance to Palestine refugees.
+UNRWA will prioritise protection interventions, crucial for upholding rights and access to essential services for Palestine refugees across the three fields of Agency operation. Legal aid and referral services will be provided in Syria, Lebanon and Jordan to assist 16,520 Palestine refugees, particularly those lacking official documentation. UNRWA will also provide explosive ordnance risk education (EORE) to 51,530 individuals in high-risk areas in Syria, to enhance their safety. Across all three fields, case management will support gender-based violence (GBV) survivors, at-risk children and youth, persons struggling with negative coping mechanisms, as well as individuals facing heightened psychosocial distress, among other vulnerable cases.
+UNRWA will provide primary health care services supported by the Appeal to meet the evolving needs of Palestine refugees, including hospitalisation coverage in response to the increasing unaffordability of secondary and tertiary care. Across the fields, up to 123,000 Palestine refugees will receive mental health and psychosocial support (MHPSS). In this regard, around 90,000 children enrolled in UNRWA schools will be supported, addressing the profound psychosocial impact of protracted conflict, displacement and socioeconomic hardship. The Agency will also prioritise the provision of education in emergencies interventions to ensure learning continuity for the most vulnerable students, including returnees to and within Syria, PRS and ex-Gazans.
+UNRWA will provide shelter or winterisation support to over 17,000 conflict-affected households, helping to ensure access to safe living conditions and protection from the elements. This support will include shelter repairs in Syria for vulnerable returnees, the replacement of unfit shelters in Jordan’s Garden Camp and winterisation cash-based assistance in Lebanon for the most vulnerable.4 As a key preparedness measure, UNRWA will likewise ensure the readiness of seven designated emergency shelters (DESs) in Lebanon, capable of accommodating up to 3,000 displaced persons, through maintaining critical infrastructure, pre-positioned essential supplies, contingency fuel and linked rapid mobile health response capacity for immediate activation during crises.
+In parallel, the Agency will rehabilitate or reconstruct UNRWA installations damaged by conflict, including schools and health centres in Syria, to support the safety and continuity of essential services. Over 180 facilities across all three fields will undergo maintenance and/or repairs, including upgrades to improve accessibility and the installation of sustainable energy systems at critical sites - strengthening UNRWA’s environmental sustainability and operational resilience during emergencies.
+The Agency will take a community-centred approach, integrating mental health, psychosocial services and skills development. It will strengthen social cohesion and build a safer, more resilient environment. UNRWA’s interventions will remain guided by the Humanitarian-Development-Peace nexus approach, linking relief with resilience-building and conflict prevention, and the imperative to ensure dignity, protection and inclusion for all Palestine refugees across the region.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:01:46.946374+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Syria, Lebanon and Jordan Emergency Appeal 2025 - Progress Report (For the reporting period 1 January – 30 June 2025) - Syrian Arab Republic</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/syrian-arab-republic/syria-lebanon-and-jordan-emergency-appeal-2025-progress-report-reporting-period-1-january-30-june-2025</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Summary
+The close of 2024 offered the reprieve of a ceasefire between Israel and Hezbollah in Lebanon, following a period of intense conflict and widespread displacement. In Syria, the transfer of authority following the fall of Bashar al-Assad’s government unfolded swiftly and with relative order. For many Palestine refugees, this juncture carried a renewed sense of optimism and the hope of return.
+During the first half of 2025, all three countries under this Appeal experienced ongoing uncertainty. In Syria, sporadic violence persisted across several areas, while in Lebanon, ceasefire violations continued, albeit at a low intensity. In Jordan, spillovers from the conflicts in Gaza and Lebanon and broader regional tensions weakened tourism, exports and revenues, straining already tight public finances and livelihoods. In this context of hope and fragility, the region saw major population movements, including substantial returns to highly challenging circumstances.
+Palestine refugee returns to and within Syria during the first half of 2025 exceeded 29,000, more than double the approximately 14,000 recorded over the previous five years combined. Inability to pay rent in displacement and the desire for family reunification were key drivers of returns, even to areas where homes remained partially destroyed, some still lacking walls or electricity, and where public infrastructure remained heavily damaged. Food insecurity sharply increased, rising from 56 per cent in 2023 to 63 per cent in 2024, and reached 92 per cent in 2025.
+In Lebanon, by June 2025, nearly all Palestine refugee families displaced by the 2024 conflict had returned, finding their homes largely intact. However, around 201,100 Palestine refugees in Lebanon (PRL), including around 23,600 Palestinian refugees from Syria (PRS), remained among the most socioeconomically marginalized, facing continued restrictions on access to public services and syndicated professions, with over 80 per cent living below the poverty line.
+For PRS in Lebanon, the lack of access to legal residency since May 2024 has affected all facets of life, barring them from formal employment and restricting civil registration of vital events (e.g., birth registration), participation in national school examinations, the issuance of educational certificates and freedom of movement. For many PRS returning to Syria, mounting legal restrictions in their countries of refuge, and associated economic hardship, contributed to the decision to return, whereas inadequate shelter and lack of livelihood opportunities were the most frequently cited challenges to return.
+Jordan continued to grapple with the compounding effects of regional instability, including economic pressures and the protracted presence of refugees. Vulnerable groups, including ex-Gazans and PRS, faced persistent barriers to legal status, livelihoods and essential public services. Although the majority of Palestine refugees in Jordan hold citizenship, approximately 181,649 ex-Gazans and many PRS do not, limiting their access to public services and legal protections. Of the 19,578 Palestinian refugees who fled the Syria conflict and continued to reside in Jordan as at June 2025, 2,946 lacked any form of official Jordanian documentation. This group included most of the 402 PRS residing in Garden Camp, a closed refugee reception facility where restrictions on movement further exacerbate their vulnerability.
+In this context of continued regional fragility, the United Nations Relief and Works Agency for Palestine Refugees in the Near East (UNRWA or the Agency) maintained essential humanitarian assistance for the most vulnerable Palestine refugees across Syria, Lebanon, and Jordan amid protracted displacement, rising return movements, and mounting socioeconomic pressures.
+For Palestine refugees returning to conflict-devastated areas in the hope of rebuilding their lives, the Agency provided shelter support as well as education, health, and protection services. At the same time, the broader population of crisis-affected Palestine refugees who remained displaced continued to rely almost entirely on UNRWA for essential services. These include critical multi-purpose cash assistance (MPCA) and protection support, including legal aid to address persistent barriers to obtaining legal documentation, as well as assistance related to the regularisation of legal status.
+MPCA remained a flexible lifeline for vulnerable families struggling to meet rent, food, and other basic needs. A total of 25,348 PRS (22,616 in Lebanon and 2,732 in Jordan) received MPCA, providing much-needed relief amid rising living costs and economic insecurity. In Lebanon, 8,332 families also received winterisation assistance to help them endure harsh seasonal conditions.
+Health care remained central to the Agency’s response; across the three fields, around 570,000 primary health care consultations were delivered or supported, alongside 3,463 hospitalizations subsidised in Lebanon and Jordan for chronic and critical conditions. Over 21,900 Palestine refugees accessed psychosocial support services (PSS) in Lebanon, addressing the trauma of displacement and conflict.
+Education services continued despite immense challenges, with nearly 86,400 children supported through the Appeal enrolled in UNRWA schools across all three fields. Of these, approximately 62,000 benefited from counselling and/or recreational activities designed to help them cope with the effects of prolonged instability.
+In Syria, where an increasing number of returnees were faced with destroyed homes and infrastructure, 43 families (175 individuals) received cash assistance for minor shelter repairs under the self-help approach in Yarmouk camp, while 603 Palestine refugees accessed short-term cash-for-work (CfW) opportunities and 1,729 students enrolled in long- and short-term technical and vocational education and training courses to support future livelihoods.
+Protection interventions remained essential across all three fields, with 5,303 Palestine refugees receiving legal assistance to address issues such as legal documentation barriers affecting access to services, employment, and freedom of movement. Explosive ordnance risk education (EORE) reached over 3,200 Palestine refugees in Syria and Lebanon, raising awareness of the dangers posed by explosive remnants of war in contaminated areas.
+To strengthen accountability and improve efficiency, the Agency advanced digital identity verification (DIV) in the first half of 2025. In Lebanon, 224,791 Palestine refugees were verified, including 201,136 PRL and 23,655 PRS, while in Jordan, 19,578 PRS completed verification during the reporting period. In Syria, UNRWA is engaging with the Interim Government to roll out DIV. The process serves as a cornerstone for delivering targeted and transparent assistance to Palestine refugees, enhancing both efficiency and accountability.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:01:52.952887+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Lebanon: UNRWA Protection Update (October – December 2024) - Lebanon</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/lebanon-unrwa-protection-update-october-december-2024</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>This quarterly update is intended to provide information on protection risks and trends impacting Palestine Refugees in Lebanon. It reflects key protection concerns arising from UNRWA’s protection monitoring and is not intended to be exhaustive.
+Context Update
+The final quarter of 2024 saw a significant escalation in cross-border hostilities between Israel and Hezbollah culminating in Israeli forces entering southern Lebanon in October. Israeli airstrikes and artillery shelling targeted multiple areas of Lebanon, particularly the southern suburbs of Beirut, the eastern Beqaa region, and across southern Lebanon, causing widespread damage and destruction to infrastructure, homes, and agricultural lands and leading to a sharp increase in civilian casualties, with women and children among those killed.i Hezbollah also continued to launch rockets into northern Israel.
+The intensification of Israeli airstrikes triggered new waves of displacement towards northern Lebanon. Humanitarian needs surged, especially among the internally displaced. The conflict also disrupted UNRWA operations, with 12 out of 27 UNRWA health centres forced to close during this period. In response, UNRWA coordinated mobile clinics and the distribution of medicines on designated days in affected areas. The Agency was also forced to delay reopening all 61 UNRWA schools at the start of the new academic year scheduled to begin on 14 October 2024. In total, 11 UNRWA schools served as Designated Emergency Shelters (DES) housing displaced Lebanese and Syrian nationals as well as Palestine refugees. Damage to some UNRWA installations was reported in southern Beirut, the Beqaa and Tyre areas.
+The conflict also significantly affected livelihoods, including in sectors such as construction and agriculture in the south of Lebanon where Palestine Refugees are typically employed, adding to the financial burden caused by years of economic crisis in Lebanon. Rising commodity prices and increased pressure on housing, which led to a surge in rental costs, further exacerbated this situation. The entry into force of a ceasefire on 27 November 2024 brought temporary relief. As of the end of Q4, the ceasefire remained in effect but faced significant challenges due to ongoing military activities and reported ceasefire violations.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:01:58.922829+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Lebanon: UNRWA Protection Update (January – March 2024) - Lebanon</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/lebanon-unrwa-protection-update-january-march-2024</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Context update
+Cross-border strikes between the Israeli military and armed groups operating from Lebanese territory continued with growing intensity and scope between January and March 2024. Israeli airstrikes increasingly targeted areas north of the Litani River, including Jezzine, and, for the first time, the Beqaa valley and the outskirts of Saida. In addition, an air strike on 2 January targeted a meeting in south Beirut of senior members of a Palestinian faction and an associated Lebanese political and armed group, killing seven individuals. This was the first Israeli strike on Beirut since cross-border clashes began on 8 October 2023 following the outbreak of war in Gaza.
+As of 2 April, cross-border fighting had killed at least 331 people in Lebanon, including at least 66 civilians according to UN OCHA.i As of 7 April, 18 people including both Israeli soldiers and civilians were reported to have been killed in northern Israel.ii The continued escalation has led to largescale displacement in southern Lebanon, where 93,000 people had been displaced as of 2 April,iii and in northern Israel, where approximately 60,000 people were reported to have been displaced.iv
+Among other developments during the reporting period, Lebanon’s Parliament approved the national budget for 2024 on 26 January 2024, which included substantial rises in fees for obtaining civil documents, such as travel documents, marriage and birth registration documents, and driver’s licenses, and for submitting cases to civil courts, including those related to rent, contracts, commercial issues, labour law and criminal matters.v Many administrative fees increased up to ten times their previous level, with some up to forty times higher. The fee for issuing an individual civil extract, for example, which was previously less than 100,000 LBP (with some variation depending on the area of issuance), increased to at least 1,000,000 LBP. Furthermore, a shortage of the stamps needed to formalize civil documents has seen prices soar on the black market.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:02:04.974180+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Q3 Progress Report: Implementing the Colonna Report at UNRWA (July 2025 - September 2025) - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/q3-progress-report-implementing-colonna-report-unrwa-july-2025-september-2025</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Quarterly Implementation Progress Overview
+This Quarterly Colonna Progress Report provides a summary of major milestones and developments during the third quarter of 2025 in the Agency’s implementation of the 50 recommendations of the Independent Review of Mechanisms and Procedures to Ensure Adherence by UNRWA to the Humanitarian Principle of Neutrality. 1 It also provides an updated overview of progress across thematic categories and funding requirements.
+Following the completion of the first year of implementation in June 2025, UNRWA has maintained steady momentum in translating the Colonna Report’s recommendations into institutional reform.2 As of the end of Q3 2025, 21 out of 50 recommendations have been completed, with formal acknowledgement of completion pending by the Advisory Commission (AdCom). The newly completed recommendation since Q2 pertains to strengthened oversight functions and enhanced governance mechanisms within the Agency (Recommendation 2).
+Each completed recommendation undergoes a formal review and endorsement process through both the internal Neutrality Task Force and the AdCom Sub-Working Group on Neutrality and Integrity. The sustainability of completed recommendations is ensured through continuous monitoring, integration into policy and operational systems, and follow-up reviews. Progress remains a standing item for regular reporting to Member States through the Working Group, the full AdCom, and the biannual Integrity Briefings.
+During Q3 2025, the Agency advanced important structural and procedural milestones. The Advisory Commission formally convened the Working Group on Neutrality and Integrity under Recommendation 2, marking a key step toward embedding neutrality oversight within an intergovernmental framework. The Working Group now serves as the main platform for structured dialogue, policy exchange, and oversight of implementation progress. Progress reporting will continue on a quarterly basis through meetings of the Working Group, covering both newly closed and ongoing recommendations.
+Implementation of the remaining 29 recommendations continues on schedule, with targeted sequencing across all eight thematic categories: Engagement with Donors; Governance; Management and Internal Oversight; Neutrality of Staff; Neutrality of Installations; Education; Unions; and Cooperation with other UN Agencies. Based on current projections, an additional 10 recommendations are expected to reach completion by the end of 2025, with a total of 43 recommendations anticipated to be completed by the end of 2026. Adjustments to completion timelines will be communicated in subsequent reporting, reflecting operational developments, interdependencies, and resource availability.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:02:11.065684+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Palestinian population in Lebanon: Findings from UNRWA’s digital identity verification - Lebanon</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/palestinian-population-lebanon-findings-unrwas-digital-identity-verification</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Executive Summary
+This snapshot report presents the findings of UNRWA’s first digital identity verification of the Palestinian population in Lebanon, conducted from mid-2023 to mid-2025 through the eUNRWA mobile platform. The verified population totals 231,515 as at 30 June 2025, with a nearly equal proportion of females and males, and a relatively high dependency ratio, comprising 33 per cent children and 10 per cent elderly. Half of the population resides in the South Governorate, where the largest official camps and informal gatherings are located. Facing long-standing severe restrictions on their socio-economic rights, the population remains heavily reliant on UNRWA, with 94 per cent accessing one or more of the Agency’s services during the verification period. Access to cash or in-kind assistance is largely uniform across the population, whereas variations are noticeable in the use of health and education services.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:02:17.063789+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>China supports UNRWA with insulin syringes for improved diabetes care - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/china-supports-unrwa-insulin-syringes-improved-diabetes-care</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>RAMALLAH,
+The first batch of insulin syringes procured with the generous contribution from the Government of China has arrived in UNRWA warehouses in the occupied West Bank. The batch is ready for distribution to Palestine Refugee patients with diabetes who rely daily on insulin treatment.
+The China International Development Cooperation Agency signed the agreement with UNRWA in October 2024, providing US$ 2.3 million worth of insulin syringes to diabetic Palestine Refugees in the Gaza Strip, Jordan, Lebanon, Syria, and the occupied West Bank, including East Jerusalem.
+Non-communicable diseases, including diabetes, are responsible for 70-80 per cent of deaths among Palestine Refugees in UNRWA’s five fields of operation. This vital support from the Government of China will contribute to ensuring a regular and uninterrupted supply of insulin syringes to Palestine Refugees in need of insulin therapy, significantly improving their health conditions, and preventing severe health complications associated with lack of access.
+UNRWA Director of Health Dr Akihiro Seita, said, “The generous support from China will enable UNRWA to effectively respond to the significant health burden posed by diabetes and other non-communicable diseases. By addressing the critical need for insulin syringes, this grant will improve the overall health and well-being of diabetic patients in need of insulin, improve their access to essential treatments, and alleviate the burden of diabetes for 43,268 Palestine Refugees identified across UNRWA’s fields of operation.”
+Highlighting China’s continued support to the Agency, Ambassador Zeng Jixin, Head of the Office of the People’s Republic of China to the State of Palestine, said, “th anniversary since the launch of China’s Global Development and South-South Cooperation Fund (GDSSCF), as China’s concrete contribution towards the realisation of the UN 2030 Development Agenda.”
+He continued, “The provision of insulin syringes for Palestine Refugees with diabetes is yet another highlight of the robust collaboration between UNRWA and the Government of China and demonstrates China’s resolute commitment towards supporting Palestine Refugees and the irreplaceable work of UNRWA. We wish every success for the project implementation and that the health conditions of the Palestine Refugees with diabetes will be substantially improved. "
+The People’s Republic of China has been a long-standing supporter of UNRWA and Palestine Refugees. Since October 2023, China has provided financial contributions totaling US$ 5.5 million in support of the Agency’s core operations in Syria, Lebanon, Jordan, the Gaza Strip, and the occupied West Bank, including East Jerusalem.
+The insulin syringe project is funded through the Global Development and South-South Cooperation Fund under China’s Global Development Initiative, which places development back at the centre of the global agenda. Through this initiative, UNRWA can provide Palestine Refugees living with diabetes with the care they urgently need.
+ENDs -</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:02:23.167521+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Lebanon: UNRWA Protection Update (1 April – 30 June 2025) - Lebanon</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/lebanon-unrwa-protection-update-1-april-30-june-2025</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>The security situation in Palestine refugee camps across Lebanon remained tense during the reporting period, with sporadic incidents of armed violence as well as increased security measures maintained by the Lebanese Armed Forces (LAF). On 2 May, the Supreme Defense Council publicly warned Hamas against conducting operations from Lebanese territory that could compromise national security, noting its intention to recommend further measures to the cabinet.i On 21 May, Palestinian President Mahmoud Abbas met with senior Lebanese officials in Beirut where it was agreed to initiate a process for the disarmament of the camps.ii The disarmament process was slated to commence in mid-June, though no concrete measures had been observed by the end of the reporting period.
+The prevailing mood in the Palestine refugee camps is one of uncertainty over future prospects including related to the ability of UNRWA to continue providing vital services in the absence of alternative service providers.
+During the reporting period, UNRWA carried out a targeted food assistance distribution from 12 to 25 June 2025 to address food insecurity. This round of distribution focused on Social Safety Net Programme (SSNP) beneficiaries, reaching a total of 15,181 families (54,459 individuals) across 11 sites. Due to funding shortfalls, UNRWA has not been able to disburse a quarterly amount of $50 to 165,000 Palestine refugees, targeting children, elderly and disabled, as was the case in previous years.
+More broadly, funding shortfalls and delayed donor contributions continue to force UNRWA to resort to emergency financial measures in a context where Palestine refugees in Lebanon are heavily dependent on UNRWA for basic health, hospitalization, education and maintenance of water and sanitation in the 12 refugee camps.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:02:29.239567+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>EU aid reaches 23,000 Palestine Refugees from Syria striving to survive in Lebanon - Lebanon</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/eu-aid-reaches-23000-palestine-refugees-syria-striving-survive-lebanon</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Samer carefully manages his family’s limited electricity supply. The 39-year-old Palestine Refugee from Syria, who fled his home in 2014 during the civil war, is doing his best to keep his family afloat in Lebanon. With only four hours of government electricity a day, the family relies on a two-ampere private subscription, just enough to power lights, an old television, a refrigerator, two fans and a washing machine. If they exceed their share, the breaker trips, plunging them into darkness.
+“Without this back-up power, we’d be without light for more than 20 hours a day,” says Samer. “Thanks to the cash assistance I receive from UNRWA, I can rent this small space and keep the lights on through the generator.”
+Thanks to European Union (EU) Humanitarian Aid, UNRWA was able to deliver two cycles of cash assistance in 2025, reaching around 23,000 Palestine Refugees from Syria – or 8,500 households, including Samer’s.
+Samer works at a local bakery earning the equivalent of about US$ 50 per month. For Palestine Refugees coming from Syria now living in Lebanon, access to employment is extremely difficult. Even Palestine Refugees from Lebanon are barred from 39 professions. For those from Syria, the situation is even tougher.
+Access to legal residency for Palestine Refugees from Syria has become increasingly challenging since May 2024, when the Government of Lebanon introduced new measures affecting the renewal of residency permits. This has created additional obstacles to moving freely outside Palestine Refugee camps where UNRWA provides basic services.
+Samer is a father to two boys aged 15 and 11, both attending UNRWA schools. The family would struggle to survive without receiving free UNRWA education services along with the EU humanitarian cash support.
+Palestine Refugees from Syria living in Lebanon are among the most vulnerable communities in the country, with poverty levels at around 70-80 per cent according to UNRWA’s latest surveys. A total of 80 per cent of them fled their homes in Yarmouk, a refugee camp near the Syrian capital Damascus which was heavily destroyed during the civil war that broke out in 2011. The EU cash assistance provided through UNRWA enables families to address urgent needs.
+“This money brings us some comfort,” Samer says quietly. “It gives us a roof and a little food. Without it, we would be on the street.”
+While some families have started thinking about returning to Syria, most, including Samer’s, feel they lack the needed support to rebuild their lives there. They wait for an improvement in security, living conditions and employment in Syria before they can consider returning. Until then, Samer remains in Lebanon, relying on UNRWA and the EU to keep the roof over his family’s head and the lights on at home.
+UNRWA continues to advocate for the rights of Palestine Refugees from Syria and coordinates with relevant authorities in both Lebanon and Syria to ensure that any return home is voluntary, safe, and dignified.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:02:35.230580+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Qatar Fund for Development signs US$ 20 million core contribution agreement to support UNRWA [EN/AR] - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/qatar-fund-development-signs-us-20-million-core-contribution-agreement-support-unrwa-enar</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Today, the Qatar Fund for Development (QFFD) and UNRWA signed a core contribution agreement of US$ 20 million to support the Agency’s work in 2025–2026 across the occupied Palestinian territory (oPt), Syria, Lebanon and Jordan.
+This contribution will help UNWRA to continue its essential human development work in support of Palestine Refugees, especially in the core areas of primary healthcare and education.
+The Qatari contribution will also support UNRWA’s humanitarian operations in the Gaza Strip, where the Agency remains a critical part of the UN response, over twenty months into a brutal war. Despite anti-UNRWA legislation passed by the Israeli Knesset posing immense challenges to the Agency’s operations in the oPt, schools and health centers continue to operate, in some cases through altered modalities.
+The signing ceremony was witnessed by H.E. Sheikh Thani bin Hamad Al Thani, Chairman of the Board of Directors of the Qatar Fund for Development, and H.E. Mrs. Maryam bint Ali bin Nasser Al Misnad, Minister of State for International Cooperation and Vice Chairman of the Board of Directors of the Qatar Fund for Development. The agreement was signed by Mr. Fahad bin Hamad Al Sulaiti, Director General of the Qatar Fund for Development, and H.E. Mr. Philippe Lazzarini, Commissioner-General of UNRWA.
+On the occasion of signing the agreement, Mr. Fahad bin Hamad Al-Sulaiti, Director General of QFFD, stated: “This agreement reaffirms the State of Qatar’s unwavering commitment to supporting the brotherly Palestinian people amid the most severe humanitarian crisis of our time. Our contribution to UNRWA reflects a long-standing partnership dedicated to ensuring the continued delivery of essential services, preserving the dignity of refugees, and reinforcing their resilience. We firmly believe that international solidarity and a shared sense of responsibility are fundamental to an effective humanitarian response that paves the way for a more stable and prosperous future.”
+UNRWA Commissioner-General Philippe Lazzarini stated: “Qatar was the first Arab country to sign a multiyear agreement with UNRWA in December 2018. The consistent and generous support of the Qatar Fund for Development (QFFD) reflects the unwavering commitment of Qatar to Palestine Refugees in the occupied Palestinian territory and across the region. I hope that other Arab countries will also provide additional contributions to UNRWA at a time of unprecedented financial precarity and ongoing political attacks. I look forward to reinforcing our valuable partnership with QFFD and the State of Qatar.”
+ENDS
+Background Information:
+UNRWA is the United Nations Relief and Works Agency for Palestine Refugees in the Near East. The United Nations General Assembly established UNRWA in 1949 with a mandate to provide humanitarian assistance and protection to registered Palestine refugees in the Agency’s area of operations pending a just and lasting solution to their plight.
+UNRWA operates in the West Bank, including East Jerusalem, The Gaza Strip, Jordan, Lebanon and Syria.
+Tens of thousands of Palestine refugees who lost their homes and livelihoods due to the 1948 conflict continue to be displaced and in need of support, nearly 75 years on.
+UNRWA helps Palestine Refugees achieve their full potential in human development through quality services it provides in education, health care, relief and social services, protection, camp infrastructure and improvement, microfinance, and emergency assistance. UNRWA is funded almost entirely by voluntary contributions.
+For more information, please contact:
+UNRWA on Twitter: @UNRWA
+Email: media@unrwa.org</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:02:41.273147+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>UNRWA Department of Health Annual Report 2024 - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/unrwa-department-health-annual-report-2024</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AMMAN/GENEVA,
+UNRWA has released its 2024 Health Report, highlighting the immense toll on Palestine Refugees and the extraordinary dedication of UNRWA health staff working under some of the most dangerous and difficult conditions in the Agency’s history.
+Nineteen months into the Gaza war, UNRWA health teams keep providing lifesaving services amid bombardment, displacement, and the collapse of basic and civilian infrastructure. UNRWA recently surpassed the gruesome milestone of 300 staff members killed in the Gaza Strip, including 13 health workers. Despite the mass destruction, doctors, nurses, pharmacists and other healthcare staff remained committed to their patients, often risking their lives to reach them.
+Amid the challenges in the Gaza Strip, UNRWA continues to provide critical health services across its five fields of operation. In 2024, UNRWA provided healthcare to more than 4.7 million Palestine Refugees across the occupied West Bank including East Jerusalem, Jordan, Lebanon and Syria, excluding the Gaza Strip. Of these, over 200,000 patients received treatment for non-communicable diseases, more than 200,000 children under the age of five got child health services, and over 70,000 pregnant women delivered safely thanks to UNRWA support.
+“This report honours the dedication and courage of our frontline teams and of the Palestine Refugees’ community they serve,” said Dr Akihiro Seita, UNRWA’s Director of Health. “Our staff continue to provide critical care, often without rest, and sometimes without the most basic resources.”
+Before the war in Gaza started in October 2023, medical consultations averaged up to 15,000 per day across 22 health centres. By the end of 2024, with only seven to nine UNRWA health centres still functioning in the Gaza Strip, daily consultations had increased to nearly 18,000. To meet the unprecedented needs, UNRWA scaled up its emergency response, deploying 97 mobile medical teams across 53 different locations and coordinating vital shipments of medicine and supplies.
+“We had to adapt and reinvent our healthcare model," Dr Seita explained. "We provided care where it was most needed, in shelters and open spaces, by using mobile units, temporary medical points, and working around the clock to provide healthcare to vulnerable people who are cut off from everything.”
+While needs soared in Gaza, the Agency also faced growing restrictions in the occupied West Bank, including East Jerusalem, where curfews, road closures, other measures, and operations by Israeli forces made access to care increasingly difficult.
+UNRWA’s priorities remain maternal and child health, preventing and managing non-communicable and communicable diseases, and promoting dignity and equity in healthcare delivery.
+-ENDs-
+Notes to Editors
+The Agency’s 2024 report provides data and analysis from all five fields of UNRWA operations, based on a variety of health indicators. It gives a sobering but essential account of how war, displacement, and extended occupation affect the access to healthcare of Palestine Refugees.
+Background Information:
+UNRWA is the United Nations Relief and Works Agency for Palestine Refugees in the Near East. The United Nations General Assembly established UNRWA in 1949 with a mandate to provide humanitarian assistance and protection to registered Palestine refugees in the Agency’s area of operations pending a just and lasting solution to their plight.
+UNRWA operates in the West Bank, including East Jerusalem, The Gaza Strip, Jordan, Lebanon and Syria.
+Tens of thousands of Palestine refugees who lost their homes and livelihoods due to the 1948 conflict continue to be displaced and in need of support, nearly 75 years on.
+UNRWA helps Palestine Refugees achieve their full potential in human development through quality services it provides in education, health care, relief and social services, protection, camp infrastructure and improvement, microfinance, and emergency assistance. UNRWA is funded almost entirely by voluntary contributions.
+Your support is crucial to help us provide emergency aid
+to displaced families in Gaza</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:02:47.238158+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>UNRWA Health Services: A Lifeline for Palestine Refugees in Lebanon [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-health-services-lifeline-palestine-refugees-lebanon-enar</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Through its network of health clinics throughout the country, UNRWA offers maternal and child healthcare services to all Palestine Refugees in Lebanon.
+Walaa, a 35-year-old Palestine Refugee from Nahr El Bared camp in northern Lebanon, is a mother of three, with her youngest child, Mayan, just two months old.
+Before Mayan’s birth, Walaa says, "I always made sure to visit the clinic for regular check-ups. They gave me valuable advice on how to take care of myself and my baby while she was still in my womb.” During her visits, she received essential check-ups, had her blood pressure and sugar levels monitored, and was provided with supplements like iron and folic acid. Inside the clinic, she was surrounded by the care and support of doctors and nurses who guided her every step of the way.
+With rising healthcare costs in Lebanon, Walaa adds, "Healthcare is so expensive. Going to a private gynecologist costs between US$ 50 to US$ 70, not including transportation. My husband doesn’t have stable work, and I have three children to care for."
+Walaa gave birth at the hospital with support from UNRWA, which covered 90 per cent of the delivery costs. "I continue to receive support from the UNRWA team at the clinic after the birth. They regularly weigh my baby and ensure she receives her vaccinations on time, along with any necessary treatments and medication,” Walaa said.
+UNRWA’s health services are essential for Walaa and other vulnerable Palestine Refugees in Lebanon, where the poverty rate is high, reaching 70-80 per cent. “We cannot survive without this support,” she explains.
+In Lebanon, Palestine Refugees rely heavily on UNRWA services, as they have no access to the country's public health system. The Agency provides these services in its 27 primary healthcare centres, as well as by giving subsidies for hospital coverage, and offering access to basic and life-saving medications and treatments.
+“The exclusion of Palestine Refugees from access to public services in Lebanon makes them highly dependent on UNRWA. Without UNRWA, 200,000 patients in need of primary health care—mainly women and children—would have no basic health service provider to turn to. And without our hospitalization support, 30,000 patients requiring urgent secondary or tertiary care each year would simply have nowhere to go,” said Dorothee Klaus, Director of UNRWA Affairs in Lebanon.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:02:53.441153+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Press remarks by UNRWA Commissioner-General Philippe Lazzarini (10 March 2025) - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/press-remarks-unrwa-commissioner-general-philippe-lazzarini-10-march-2025</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>GENEVA, checked against delivery
+It has been almost 10 days since the State of Israel banned the entry of humanitarian aid and commercial supplies into the Gaza Strip.
+Somehow a situation similar to the one which prevailed in October 2023. This decision threatens the lives and survival of civilians in Gaza, who have had only a brief respite from 16 months of brutal war.
+The ceasefire agreement has shown that whenever there is a political will, humanitarian assistance can be unhindered and un-interrupted. Between the beginning of the cease fire and 2 March, humanitarian assistance has increased 10 folds.
+It is critical that humanitarian aid is allowed into Gaza again, to maintain the progress made during the first phase of the ceasefire and meet people’s basic needs.
+I echo the call of the Secretary General for the immediate, unconditional, and dignified release of all hostages, the dignified release of Palestinian detainees as previously agreed, and for the ceasefire to hold.
+It is important also to shed light on the situation in the West Bank. In the West Bank the operation by the Israeli Security Forces, which started six weeks ago, is severely impacting Palestinians, especially in the north. Palestinian armed groups are also increasingly active in the area.
+Several refugee camps have been nearly emptied, displacing around 40,000 Palestine Refugees.
+This is the largest displacement of Palestinians in the West Bank since 1967.
+The large-scale demolition of buildings, including residential areas is alarming. People have nowhere to return to.
+UNRWA continues to track displaced people and provide humanitarian aid, including food, healthcare and basic items.
+In Syria, we have witnessed over the last few days terrible violence. One of our staff was also tragically caught up in the crossfire. We continue, in the country, to provide healthcare and education, which for many Palestine Refugees are absolutely essential to their survival.
+In Lebanon, socioeconomic crises have increased the reliance of Palestine Refugees on UNRWA services. We just did a survey, and we have seen that the UNRWA cash assistance to Palestine Refugees has become one of the main sources of income for 70 percent of Palestine Refugees in the country.
+Now, about the Knesset laws. The Knesset legislation I briefed the Member States on is not just about UNRWA. This is about any individual or organisation calling for adherence to international humanitarian law or promoting the rights of Palestinians.
+While a number of International NGOs have already been silenced, there is now a larger, concerted effort in Israel to undermine, or restrict through legislative measures, the operations of international organisations and NGOs.
+The Agency has faced serious operational challenges since the Israeli parliament’s anti-UNRWA legislation came into force at the end of January.
+In occupied East Jerusalem, the Agency is facing increased pressure from the municipality to vacate premises and end service provision.
+International staff have been effectively expelled from the occupied West Bank due to the lack of valid visas.
+While some international staff remain in Gaza, Israel refuses to facilitate their entry or exit via Kerem Shalom.
+Despite these challenges, UNRWA will stay and deliver its General Assembly mandate until it is no longer possible to do so in a principled manner.
+For example:
+- Since the ceasefire began in Gaza, UNRWA has provided food to 2 million people, opened nearly 40 new emergency shelters, and provided over 60,000 people with tents.
+- UNRWA health teams supported the polio vaccination campaign last month reaching nearly 200,000 children below the age of 10.
+- Through temporary learning spaces and remote learning, UNRWA is reaching children with education. As an anecdote we have opened registration for distance learning for the children in Gaza at the beginning of January. Three weeks later we had more than 250,000 children having registered. Today, 70 per cent of them are having distance learning through the digital platform.
+- In the West Bank, nearly 50,000 children go to the Agency’s schools and hundreds of thousands of people rely on our health services.
+I must highlight again the disinformation campaign portraying the Agency as a terrorist organisation, and our staff as terrorists or terrorist sympathizers.
+I do believe that, talking to an audience of journalists, checking facts and reporting through firsthand, official sources is the foundation of independent reporting and key to countering this vicious campaign.
+This is especially critical given the prolonged ban on independent, international media in Gaza. There has been no independent international media in Gaza since October 2023.
+I continue to urge you - the international media - to do more to get into Gaza to cover untold stories and verify information. I asked the same to Member States: to help journalists to get access into Gaza.
+On funding, UNRWA’s financial situation – you would be surprised should I tell you that everything is under control – is critical and precarious. Cashflow is managed monthly, and we urgently require additional financial support if the Agency is to survive.
+To conclude, this is a time of tremendous geopolitical uncertainty.
+For UNRWA, the status quo is no longer an option. We have a choice to make.
+We can allow the Agency to implode due to the fierce disinformation campaign; the Knesset legislation; and the suspension of funding by key donors.
+- Collapse would create a dangerous vacuum in the occupied Palestinian territory and send shockwaves through Jordan, Lebanon and Syria.
+- An environment in which children are deprived of education, and people lack access to basic services, is fertile ground for exploitation and extremism.
+- This is a threat to peace and stability in the region and beyond.
+Alternatively, UNRWA can be supported to progressively conclude its mandate within the framework of a political process like that championed by Saudi Arabia, the European Union, and the League of Arab States through the Global Alliance for the Implementation of the Two-State Solution.
+The Agency, would this be the case, would then gradually transition its public-like services to empowered and prepared Palestinian institutions.
+This would preserve the rights of Palestine Refugees and their access to basic services.
+I have also repeatedly stressed that dismantling the Agency abruptly will only deepen the suffering of Palestine Refugees, but it will not cancel their refugee status. The rights of Palestine Refugees exist independently of the Agency.
+If UNRWA ceases to protect and assist Palestine Refugees, their rights will not only remain, but there will be much greater emphasis on the right to return or to be resettled, for which UNRWA has no mandate.
+So, to conclude, the main ask to Member States has been: sustain UNRWA until the political direction of travel is clear. That is, until the international community considers the political pathway proposed by Arab States through the recovery and reconstruction plan outlined in the Cairo Declaration, and the proposal of the Global Alliance for the Implementation of the Two-State Solution.
+Thank you.
+Background Information:
+UNRWA is the United Nations Relief and Works Agency for Palestine Refugees in the Near East. The United Nations General Assembly established UNRWA in 1949 with a mandate to provide humanitarian assistance and protection to registered Palestine refugees in the Agency’s area of operations pending a just and lasting solution to their plight.
+UNRWA operates in the West Bank, including East Jerusalem, The Gaza Strip, Jordan, Lebanon and Syria.
+Tens of thousands of Palestine refugees who lost their homes and livelihoods due to the 1948 conflict continue to be displaced and in need of support, nearly 75 years on.
+UNRWA helps Palestine Refugees achieve their full potential in human development through quality services it provides in education, health care, relief and social services, protection, camp infrastructure and improvement, microfinance, and emergency assistance. UNRWA is funded almost entirely by voluntary contributions.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:02:59.538591+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2023 Socioeconomic Survey of Palestine Refugees in Lebanon - Lebanon</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/2023-socioeconomic-survey-palestine-refugees-lebanon</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Executive summary
+The data for this survey was collected between the end of 2022 and the beginning of 2023 based on a representative sample using the ‘National Population and Housing Census in Palestinian Camps and Gatherings in Lebanon’ (2017) data as sample frame for the resident Palestine Refugee population in Lebanon including Palestine Refugees from Syria residing in the country. The combined survey results present a snapshot of the socio-economic development of the Palestine Refugee community in Lebanon. The survey records the effects of decades of social and economic segregation and exclusion which are linked to the legal status of this population in Lebanon, and are evidenced by poor indicator outcomes across all sections of the report. For decades Palestinians in Lebanon have been unable to work legally in a number of key professions, are not permitted to own property or businesses and are excluded from accessing public service employment and use of public services. The survey data confirms that UNRWA is the core reference and service provider for Palestinians in Lebanon.
+Key findings
+The average age of the Palestine Refugee population in Lebanon is 31 years, with an average 4 persons per household.
+A total of 27 per cent of households report at least one family member living abroad. Remittances are received by 37 per cent of households.
+Waged labour was reported as one of the main sources of income by about half of the households. UNRWA’s cash assistance was reported as one of the main income sources by 70 per cent of camp inhabitants and 58 per cent of refugees living outside the camps. About ten per cent of households indicated political organisations being one of the main income sources.
+Among the population 25 years and above, 21 per cent did not complete elementary level education and a total of 54 per cent did not complete the mandatory preparatory education level. A total of 12.5 per cent hold an academic degree.
+School enrolment is high in the early years; 95 per cent of children aged 6-12 years are enrolled. For the age group 13-15 years, a total of 92 per cent of girls remain enrolled in school, but only 81 per cent of boys. The gender gap further increases at the age of 16-18 years reflecting the general regional trends, with 77 per cent of girls enrolled but only 55 per cent of boys.
+Among all children enrolled, 70 per cent are learning in UNRWA primary or secondary schools, 17 per cent in private education institutions, 9.5 per cent in government institutions and 2.8 per cent in free private institutions for children with special needs.
+Nearly three out of 10 persons across all age groups suffer from chronic illnesses that indicate limited ability to generate income and incur additional high costs on households for medical expenses where UNRWA is unable to cover for full medication and treatment. Particularly concerning are high malnutrition rates among children with 6 per cent of children under the age of 5 years holding a respective medical certificate.
+The poverty rate at the beginning of 2023 stood at 83 per cent as per the adjusted national poverty line of 2012.
+The labour force participation rate is 41 per cent for the population above 15 years (as per ILO definition). This compares to a national labour force participation rate of 50 per cent in Lebanon for the same time period (Worldbank, 2022). Respectively, the unemployment rate among Palestine Refugees stands at 32 per cent compared to 11 per cent nationally (Worldbank, 2022).</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:03:05.821288+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Join UNRWA’s Ramadan campaign - 100 per cent of your Zakat contributions become lifesaving food and cash assistance to Palestine refugees - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/join-unrwas-ramadan-campaign-100-cent-your-zakat-contributions-become-lifesaving-food-and-cash-assistance-palestine-refugees</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>To watch UNRWA's Ramadan campaign video, click here
+AMMAN, 2 March 2025 – As the holy month of Ramadan begins, UNRWA is launching its annual fundraising campaign that invites supporters around the world to use its Zakat Programme to share their blessings with Palestine Refugees. This vital lifeline transforms every individual contribution into emergency food and cash assistance, delivered with a strict 100 per cent distribution policy.
+“Ramadan inspires reflection, compassion, and giving. By donating during this holy month, donors will be providing critical, life-sustaining support to families in desperate need – particularly in Gaza, where the humanitarian needs are unprecedented,” said Tamara Alrifai, UNRWA’s Director of External Relations and Communications.
+Throughout 15 months of constant bombardment and forced displacement, the people of Gaza have faced severe shortages of food and essential supplies. Since the ceasefire took effect on 19 January, UNRWA teams have reached two million people with vital food assistance and hundreds of thousands of people with clean water. UNRWA stands as the backbone of the emergency humanitarian response.
+For 75 years, UNRWA has stood by Palestine Refugees across the region through every UNRWA doctor’s care, every teacher’s lesson, and every food package distributed. In times of war, Palestine Refugee families across the region turn to UNRWA – which has always been there for them – for food, water, tents, cash, emergency education and health services. In Gaza, humanitarian needs continue to escalate, and the entire population is reliant on aid.
+This Ramadan, UNRWA aims to raise US$ 9 million in donations to ensure that its support reaches more people in need of food and cash assistance across the Gaza Strip, the West Bank including East Jerusalem, Lebanon, Syria, and Jordan. “Whether donors are fulfilling their religious obligations through Zakat or Sadaqah, or donating for any other reason, every contribution counts. Our new donation website makes it easier for our supporters to calculate their Zakat obligation and contribute securely to Palestine Refugees,” said Alrifai.
+UNRWA warmly invites donors to be part of this campaign and help us expand our emergency relief efforts to ensure that more families receive the vital food and care they urgently need. Your generosity and solidarity during Ramadan reaffirm that hope, courage, and dignity can prevail against all odds.
+To donate and learn more about our Ramadan campaign, please visit: donate.unrwa.org/zakat
+Background Information:
+UNRWA is the United Nations Relief and Works Agency for Palestine Refugees in the Near East. The United Nations General Assembly established UNRWA in 1949 with a mandate to provide humanitarian assistance and protection to registered Palestine Refugees in the Agency’s area of operations pending a just and lasting solution to their plight.
+UNRWA operates in the West Bank, including East Jerusalem, The Gaza Strip, Jordan, Lebanon and Syria.
+Tens of thousands of Palestine Refugees who lost their homes and livelihoods due to the 1948 conflict continue to be displaced and in need of support, nearly 75 years on.
+UNRWA helps Palestine Refugees achieve their full potential in human development through quality services it provides in education, health care, relief and social services, protection, camp infrastructure and improvement, microfinance, and emergency assistance. UNRWA is funded almost entirely by voluntary contributions.
+Your support is crucial to help us provide emergency aid to displaced families in Gaza
+For more information, please contact:
+UNRWA on Twitter: @UNRWA
+Email: media@unrwa.org</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:03:13.615209+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Assessment of patients’ satisfaction with the quality and care of UNRWA primary healthcare services - Final report - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/assessment-patients-satisfaction-quality-and-care-unrwa-primary-healthcare-services-final-report</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>UNRWA's patient satisfaction survey shows how Palestine Refugees value the Agency’s healthcare
+A new report on UNRWA’s health services has underscored how highly they are rated by the Palestine Refugees that use them.
+Providing free healthcare is at the heart of the mandate given to UNRWA by the UN General Assembly, and the Agency commissioned an independent organisation, CRSM Consulting, to take stock of its performance and areas for improvement.
+The comprehensive survey took place from July 2023 to September 2024 and covered healthcare services across Jordan, Lebanon, Syria, and the West Bank including East Jerusalem. It had 2,400 respondents at 72 UNRWA health centres in these four fields of operation. UNRWA’s fifth field, the Gaza Strip, had to be excluded from the research because of the outbreak of the war there in October 2023.
+The aim of the survey was to assess the overall satisfaction of patients, identify gaps, ensure quality healthcare delivery, and provide insights for health providers, policymakers, and stakeholders within UNRWA in order to improve the delivery of primary healthcare services.
+The report revealed that the accessibility of healthcare services was evaluated as high, with 90 per cent positive responses regarding geographic accessibility. Social accessibility was reported as good, with 98 per cent of respondents indicating they faced no barriers to accessing healthcare. Interpersonal skills among health staff also received high ratings, especially in Lebanon and the West Bank including East Jerusalem, where staff communication and privacy during consultations were highly rated.
+A 35-year-old Palestine Refugee in Lebanon told the survey team that “the health services are of high quality and always save us from paying a lot of money to buy medicines that are mostly missing from private pharmacies, and from the expenses that we pay for private doctors.”
+Some concerns were noted on the availability of chaperones in the healthcare system, particularly in Syria and Jordan, where only 38 per cent and 53 per cent of respondents, respectively, reported that these were usually available.
+Overall, health care quality and compliance with the standards varied in the four fields of which were assessed. Administrative quality was the highest in Lebanon, whereas Syria had the lowest scores. Compliance with clinical guidelines was overall high in basic medical care, with Syria leading at 99 per cent. Though referral mechanisms showed variability, the West Bank including East Jerusalem was reported to have the strongest system.
+Compliance with standards and best practices varied, ranging from a low of 68 per cent in Jordan to a high of 82 per cent in the West Bank including East Jerusalem. Quality of facility management also varied: Jordan and Lebanon generally had high standards for facility management, while Syria faced serious challenges in terms of maintenance and emergency preparedness.
+The report outlines several recommendations to address gaps. These include improving infrastructure for better accessibility, enhancing telemedicine services to reduce overcrowding, conducting training sessions to improve staff communication and clinical examination procedures, standardising referral processes, and optimising appointment scheduling.
+This report also reaffirms UNRWA’s irreplaceable role in delivering essential primary healthcare services to millions of Palestine Refugees, particularly under the current challenging conditions. As the only international organisation equipped to provide comprehensive public-like services at this scale, UNRWA’s efforts are vital to ensuring access to quality healthcare in refugee communities.
+Dr. Akihiro Seita, Director of UNRWA’s Health Department, reiterated this commitment, stating, “UNRWA’s Health Programme, through its healthcare providers, host countries, and partners, will continue working to ensure high-quality care and satisfaction for every Palestine Refugee.”
+ENDS
+Background Information:
+UNRWA is the United Nations Relief and Works Agency for Palestine Refugees in the Near East. The United Nations General Assembly established UNRWA in 1949 with a mandate to provide humanitarian assistance and protection to registered Palestine refugees in the Agency’s area of operations pending a just and lasting solution to their plight.
+UNRWA operates in the West Bank, including East Jerusalem, The Gaza Strip, Jordan, Lebanon and Syria.
+Tens of thousands of Palestine refugees who lost their homes and livelihoods due to the 1948 conflict continue to be displaced and in need of support, nearly 75 years on.
+UNRWA helps Palestine Refugees achieve their full potential in human development through quality services it provides in education, health care, relief and social services, protection, camp infrastructure and improvement, microfinance, and emergency assistance. UNRWA is funded almost entirely by voluntary contributions.
+For more information, please contact:
+UNRWA on Twitter: @UNRWA
+Email: media@unrwa.org</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:03:19.626195+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Syria, Lebanon and Jordan Emergency Appeal 2025 - Syrian Arab Republic</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/syrian-arab-republic/syria-lebanon-and-jordan-emergency-appeal-2025</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2024-12-24</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Foreword by the directors of UNRWA Affairs in Syria, Lebanon and Jordan
+In 2025, Palestine refugees across Syria, Lebanon and Jordan will face the impacts of a sharp rise in interrelated conflicts, deep economic crises, and layered displacements within and across their borders. These interconnected challenges demand a cohesive regional humanitarian and protection response.
+The crisis in Syria stands as the deadliest conflict of the 21st century and one of the largest displacement emergencies in the world.(1) Forced to relocate beyond the country’s borders, over 6 million Syrians have become refugees while even more are internally displaced.(2) Before the crisis, 560,000 Palestine refugees were registered with UNRWA in Syria. Today, 438,000 remain of whom 40 per cent are internally displaced,(3) while one fifth have left. This includes 44,202 Palestine refugees displaced to neighbouring countries, with 20,324 in Jordan and 23,878 in Lebanon.(4) Following a prolonged impasse in the political process, the armed opposition in Syria launched a major offensive on 27 November. In the week that followed, over 1,000,000 people displaced.(5) On 8 December, as this Appeal was nearing publication, the government of Bashar alAssad fell, thousands of political detainees were released and a new caretaker administration assumed control.
+In a moment filled with profound hope, thousands of the 5.6 million refugees in countries bordering Syria, along with many more displaced within the country, began their journey home. As the caretaker authorities worked to restore law and order, Israel intensified military action on Syrian soil and in the region. The transitional administration will have to consolidate governance and rebuild essential health, education and water systems, against substantial challenges to regional stability, military action on Syrian territory, and a crippling inherited economic crisis.
+The vast majority of the newly displaced in Syria, whether internally displaced or fleeing recent violence in Lebanon, have initially sought shelter with family and friends, already unable to meet their own needs.(6) Even before the latest surges in local and regional violence, nearly 90 per cent of Palestine refugees in Syria lived on less than US$ 2.15 per person, per day, with 62 per cent suffering from food insecurity.(7) Malnutrition among children under five has doubled in the past two years.(8) Economic pressures (i.e., the prohibitive cost of rent in protracted displacement) have forced some of the most vulnerable Palestine refugees to return to damaged homes in Yarmouk, Ein el Tal and Dera’a Palestine refugee camps where they live in the midst of destroyed buildings and decimated water, sewage and energy infrastructure.(9) Approximately 30 per cent of populated areas in Syria, including Palestine refugee camps, remain affected by explosive remnants of war (ERW).(10)
+In Lebanon, which has the highest refugee density per capita in the world, individual and community resilience is stretched to the breaking point amid chronic poverty, socioeconomic exclusion and escalating social tensions.(11) Palestine refugees, among the most vulnerable in this context, face entrenched structural marginalization on an intergenerational scale, with Palestinian refugees from Syria (PRS) enduring further hardship, as the renewal of their residency permits was halted as of May 2024. Eighty per cent of Palestine refugees in Lebanon live below the national poverty line, a figure that would stand at over 90 per cent in the absence of emergency cash assistance provided by UNRWA.(12)
+Since September 2024, Lebanon has experienced its most severe conflict in two decades, triggered by heightened violence between Israel and Hezbollah, related to the war in Gaza. This conflict has destroyed homes, health facilities and water systems in the country. Nearly 900,000 people have been internally displaced,(13) with around 600,000 forced to seek safety in Syria,(14) including thousands of Palestine refugees, both those registered in Lebanon and those originally from Syria. Many are from vulnerable backgrounds, such as femaleheaded households and those already reliant on humanitarian aid.(15) Despite the conditional ceasefire of 27 November 2024, the overall situation remains precarious. Armed exchanges between the parties to the conflict continue.
+In Jordan, the regional escalation of hostilities, relating to the conflict in Gaza, has negatively impacted the national socioeconomic landscape and heightened security risks.(16) Those most affected are among Jordan’s most vulnerable, including PRS, Palestinian refugees from Lebanon (PRL), Palestinian refugees from Iraq (PRI), as well as Gazans stranded in Jordan following the events of 7 October 2023,(17) and ex-Gazans(18) faced with limited access to public services due to documentation barriers. Jordan already hosts the second largest refugee population per capita in the world.(19) Rises in the cost of living further challenge the country’s capacity to manage influx of crisis-affected populations and push more Palestine refugees and other at-risk groups into deeper vulnerability.
+In response to these overlapping and interlinked protracted crises and new shocks, through regionally coherent and coordinated assistance modalities under the 2025 Emergency Appeal (EA), UNRWA will continue to adapt its response to meet the evolving needs of those affected, ensuring humanitarian assistance reaches the most vulnerable. The Agency will provide cash assistance to over 600,000 vulnerable Palestine refugees across Syria, Lebanon and Jordan to meet their most basic needs in a flexible and dignified manner. UNRWA will extend rapid transitional shelter support to up to over 57,000 Palestine refugees in Syria and Lebanon, displaced by recent surges in conflict. A further 6,800 Palestine refugee in Syria will receive shelter support for more substantial repairs using the self-help approach, with the support of UNRWA engineering oversight.
+Addressing the risks affecting the sustainability of returns to Palestine refugee camps, targeted shelter and protection interventions will be critical to promoting more durable solutions. In this regard, UNRWA will provide explosive ordnance risk education (EORE) to over 52,000 individuals in high-risk areas in Syria and Lebanon to enhance their safety and awareness. Across all three fields of UNRWA operations under this emergency appeal, Agency legal aid and referrals will assist 13,520 Palestine refugees, particularly those lacking official documentation and facing barriers to access essential services and legal protections. In addition, over 73,000 refugees will benefit from winterization assistance or anticipatory actions to help them withstand harsh weather conditions, including winter flooding.
+Through the 2025 EA, the Agency will prioritize the adaptation of primary health care services to meet the demands of evolving emergencies, including increased nutrition response needs, as well as maintaining education during crises. Across all three fields, nearly 123,000 Palestine refugees, including nearly 82,000 children enrolled in UNRWA schools, will receive psychosocial support (PSS) associated with conflict, displacement and economic hardship, which expose them to trauma, stress and disrupted development.
+UNRWA will also rehabilitate installations damaged by conflict in Syria and Lebanon to ensure service continuity in a dignified and safe environment. Maintenance and repairs will be carried out on over 200 UNRWA facilities across all three fields, including upgrades for accessibility and the installation of sustainable energy systems at critical installations, to enhance longer term environmental sustainability, as well as immediate operational capacity during emergencies.
+The crises in Syria, Lebanon and Jordan are deeply interconnected, presenting compound challenges that require a cohesive regional approach to humanitarian and protection response. In this regard, UNRWA will be prepared to maintain, adapt and scale up emergency service provision, as required. In alignment with the humanitarian-development-peace nexus, the Agency will enhance collaboration with development and peacebuilding actors to address the root causes of vulnerability and promote more sustainable solutions for Palestine refugees. UNRWA will also develop humanitarian early recovery efforts to promote more sustainable solutions in Syria, while safeguarding legal status and key protection mechanisms across the region. Further, the Agency will strengthen partnerships with Member States, humanitarian actors and development organizations to ensure coordinated, impactful and sustainable support for Palestine refugees. These measures are essential to protecting and upholding the rights of the most vulnerable Palestine refugees during this period of profound change.
+The stability of countries in the region, including Syria, Lebanon and Jordan, is deeply interconnected with that of their neighbours, carrying significant regional implications. Consequently, a unified regional response not only strengthens cohesion but also fosters recovery and stability across borders. Through this Appeal, UNRWA calls on Member States and partners to extend sustained and meaningful support to Palestine refugees in Syria, Lebanon and Jordan. This commitment is vital to protect their survival, dignity and resilience during this period.
+endnotes
+- According to the World Bank, between 2011 and 2023, over 409,000 conflict-related deaths have been recorded in Syria - more than any other conflict of the past three decades. World Bank, “Macro Poverty Outlook for Syrian Arab Republic: October 2024”, October 2024.
+- UNHCR, “Operational Portal,” accessed on 16 December 2024.
+- Given the recent return of Palestine refugees to Yarmouk, Ein el Tal and Dera'a camps, in 2025, UNRWA will conduct an assessment to update the number of refugees who remain displaced.
+- As at 30 November 2024, there were 20,324 PRS in Jordan and 23,878 PRS in Lebanon registered with UNRWA.
+- OCHA, “North-west Syria: Escalation of Hostilities - Flash Update No. 4, 8 December 2024”, 8 December 2024.
+- From late September to 28 November 2024, approximately 562,000 persons had been displaced from Lebanon to Syria. UNHCR, “UNHCR Syria Emergency Response Brief - 28 November 2024”, 28 November 2024. As at 8 December, one million people have displaced internally in Syria following major changes in internal frontlines. OCHA, “North-west Syria: Escalation of Hostilities - Flash Update No. 4, 8 December 2024”, 8 December 2024.
+- UNRWA, “Post-distribution Monitoring Survey, Syria”, September 2022. UNRWA, “Post-distribution Monitoring Survey, Syria”, March 2024.
+- UNRWA, Health Department data, 2024. Please note that, according to the World Health Organization (WHO), child wasting refers to a child who is too thin for her or his height and is the result of recent rapid weight loss or the failure to gain weight.
+- Some 90 per cent of refugees who returned to these camps cited the primary reason as the inability to afford rent in their area of displacement. UNRWA, "Living Conditions of Palestine Refugees Returning to Yarmouk - An Exploratory Shelter and Socioeconomic Analysis", June 2024.
+- UNRWA, “Protection in Syria”, 2024.
+- World Bank, “Lebanon: Poverty More than Triples over the Last Decade Reaching 44% under a Protracted Crisis”, 23 May 2024. UNHCR, “UNHCR Lebanon at a Glance”, 2024.
+- According to UNRWA data, poverty rates among Palestine refugees are extremely high, with 80 per cent reported to be living below the national poverty line (adjusted for inflation), as at March 2023. Data modelling confirmed that without the distribution of quarterly cash assistance from UNRWA, poverty would stand at over 90 per cent.
+- International Organization for Migration, “Displacement Tracking Matrix, Mobility Snapshot Round 65”, 25 November 2025.
+- From late September to 28 November 2024, approximately 562,000 persons had been displaced from Lebanon to Syria. UNHCR, “UNHCR Syria Emergency Response Brief - 28 November 2024”, 28 November 2024.
+- UNRWA, “Protection Note: Cross-border Movement of Palestine Refugees Affected by the Conflict in Lebanon”, 1 November 2024.
+- World Bank, "Jordan Economic Monitor, Summer 2024: Strength Amidst Strain: Jordan’s Economic Resilience", 2 October 2024.
+- Stranded Gazans are Palestine refugees who became stranded in Jordan following the onset of the Gaza conflict on 7 October 2024, and who have self-reported to UNRWA. The number of stranded Gazans is likely higher as not all approach the Agency for assistance.
+- Ex-Gazans refer to those who fled the Gaza Strip during the 1967 Arab-Israeli War, seeking safety and stability. Many settled in Jordan, but unlike other Palestinian refugees, they are often not granted full Jordanian citizenship, leaving them in a precarious legal and socio-economic situation, with restricted access to national health care system, higher education, government aid programmes, public-sector jobs and other employment opportunities.
+- Over several decades, Jordan has received large numbers of refugees, including from Palestine, Iraq, Yemen, Sudan and Syria. UNHCR, “UNHCR Jordan Multi-Year Strategy 2023-2025 Summary”, 1 January 2023.
+- Given the recent return of Palestine refugees to Yarmouk, Ein el Tal and Dera'a camps, in 2025, UNRWA will conduct an assessment to update the number of refugees who remain displaced.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:03:25.693989+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Insights on Child Marriage: Discussions on Gender-Based Violence - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/insights-child-marriage-discussions-gender-based-violence</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Introduction to Gender-Based Violence at UNRWA
+From July 2023 to March 2024, UNRWA conducted primary and secondary research on Palestine refugee community perceptions of Gender-Based Violence (GBV). This research, which included focus group discussions (FGD) and Key Informant Interviews (KII), sought to capture thematic priorities and key trends related to GBV to better inform evidence-based gender-responsive policies, programmes and survivor-centred services provided by the Agency. Reflections from over 600 community members of all ages across UNRWA’s five fields of operation revealed four recurring thematic GBV priorities: domestic violence, child marriage, violence in schools and sexual violence. This brief is part of a series which will present insights on the prevalence, causes and impact of these forms of GBV on the Palestine refugee community. These briefs accompany UNRWA’s longer report encompassing findings, analysis and recommendations across all GBV themes emerging from the research across all five operational contexts. In Gaza, the research was conducted prior to 7 October 2023 and serves as a unique snapshot of community perceptions prior to this date.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:03:31.694519+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Rising above: the inspiring journey of Fatima Suleiman - Lebanon</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/rising-above-inspiring-journey-fatima-suleiman</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Fatime Suleiman lives in the Rashidieh Palestine Refugee camp in Tyre, Lebanon. Born in 1990, she grew up in a close-knit family, surrounded by her four brothers and sister. As her siblings eventually started their own families, Fatima found herself facing life’s challenges with only her parents by her side. Despite the obstacles, she remains a beacon of hope and strength in her community.
+“My life changed dramatically in 2008 when I was involved in a devastating bus accident. Struck by a reckless driver, I spent nearly two months hospitalized, fighting to recover,” she said.
+Fatima was left with a profound challenge: a left transfemoral, or above-knee, amputation. This suddenly altered her physical capabilities and forced her into a world filled with obstacles.
+“I'll never forget the moment I realized my life had changed forever. It was a wave of emotions: fear, sadness, and uncertainty about the future," she said.
+Despite this life-altering event, Fatima was determined not to be defined by her disability. With unwavering spirit, she took on the responsibilities of daily life, managing house chores and supporting her family.
+"I decided that I wouldn’t let my circumstances define me. Every day became a challenge, but I embraced it. I pushed myself to find new strengths, to learn new ways to navigate life, and to keep moving forward," she said.
+However, the financial burden of her artificial limb soon became a daunting reality. Before the economic crisis hit Lebanon in 2019, Fatima could afford the expenses associated with her prosthetic limb. But as inflation surged and economic stability crumbled, her ability to do was increasingly threatened.
+In 2016, Fatima had already reached out to the UNRWA Disability Programme, a crucial resource for others who share her experiences. This programme, part of UNRWA’s Relief and Social Services Department, works in collaboration with various partners to provide essential services for people with disabilities and their caregivers. These partnerships are essential for delivering comprehensive support to those who need it the most.
+What distinguishes the Disability Programme is its human rights-based approach. It empowers beneficiaries by allowing them to select personalized assistance that aligns with their unique needs and available resources. Previously, they contributed 20 per cent of the cost of their devices. But in light of the ongoing economic crisis, they no longer need to do this, ensuring that individuals can access these vital services without financial burdens. This flexibility and understanding made a significant difference for Fatima, who reapplied in 2021 when her first prosthetic limb began to wear out.
+Education has always been a cornerstone of Fatima’s life. A bright student at Al Aqsa UNRWA school, she excelled academically, eventually earning her bachelor’s and later a master’s degree in social sciences from the Lebanese University. Yet, the path was fraught with challenges. Navigating her university campus was not easy; winter rains often turned the streets slippery, leading to falls that tested her resolve. But each time she fell, she rose again, determined to succeed.
+Despite her impressive credentials and several internships with various organizations, Fatima encountered a harsh reality in the job market. Employers often overlooked her potential, and society’s bias against people with disabilities cast a shadow over her dreams. Yet, Fatima remained undeterred, reminding herself that circumstances do not define her worth.
+“I refused to let anything stop me,” she said. “Every fall was just another lesson, reminding me that I could rise again, no matter how hard it got.”
+The Disability Programme has been more than just a source of support. It plays a crucial role in the lives of Palestine Refugees in Lebanon and helps them pursue their dreams without financial barriers holding them back. The programme delivers awareness sessions to the beneficiaries, teaching them how to take proper care of and maintain their devices, and connect with others who share similar experiences.
+During a recent awareness session, Fatima served as a resource for her peers with disabilities who use artificial limbs, demonstrating her eagerness to assist others in caring for their devices. Her commitment to supporting her peers is truly inspiring and aligns seamlessly with the programme's objectives.
+“Through our various initiatives, we actively work to assist persons in need like Fatima, ensuring they have the resources to lead an equal-opportunity life as they manage their very personal challenges," said Dorothee Klaus, Director of UNRWA Affairs in Lebanon.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:03:44.115866+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #15 on the Lebanon Emergency Response: All information from 13 November - 20 November 2024, valid as of 27 November 2024 at 1:00 PM [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-15-lebanon-emergency-response-all-information-13-november-20-november-2024-valid-27-november-2024-100-pm-enar</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1. Key Points
+• UNRWA activated its Emergency Response in Lebanon on 24 September. The Agency is currently operating 11 emergency shelters across the country.
+• As of 27 November, a total of 3,316 Internally Displaced People (IDPs) are registered in UNRWA shelters.
+• On 26 November, a ceasefire agreement was announced to be effective as of 27 November at 4:00 am. As of 27 November at 1:00 pm, the ceasefire agreement was holding.
+• On 22 November, the Israeli military issued displacement orders affecting Burj Chemali Camp and Maashouk Palestinian gathering in Tyre Area.
+• On 26 November in the lead up to the announcement of the ceasefire agreement Rashidieh Camp was hit by Israeli airstrikes.
+• No incidents affecting UNRWA facilities, and no casualties among UNRRWA staff, were reported between 20 November and 27 November.
+2. Overall Situation
+• The International Organization for Migration (IOM) reports a total of 899,725 IDPs (51 per cent female and 49 per cent male) as of 25 November. The implications of the ceasefire will be reflected in the next situation report.
+• As of 27 November, 990 households, representing 3,316 people, were registered in UNRWA emergency shelters across the country, indicating a minor increase for the first time in several weeks. This is likely due to the intensity of airstrikes over the reporting period.
+• UNRWA is working with a range of partner organisations (community based, local NGOs and international NGOs) in all its emergency shelters to provide a full range of services, including hot meals and psychosocial support activities. In its emergency response, UNRWA has relied on the dedication and commitment of partners on the ground.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:03:50.233620+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #14 on the Lebanon Emergency Response: All information from 13 November - 20 November 2024, valid as of 20 November 2024 at 1:00 PM [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-14-lebanon-emergency-response-all-information-13-november-20-november-2024-valid-20-november-2024-100-pm-enar</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Key Points
+- UNRWA activated its Emergency Response in Lebanon on 24 September. The Agency is currently operating 11 emergency shelters across the country.
+- As of 20 November 2024, a total of 3,281 Internally Displaced People (IDPs) has registered in UNRWA shelters.
+- No incidents affecting UNRWA facilities were reported between 13 November and 20 November 2024. No casualties among UNRWA staff have been reported during the reporting period.
+- During the reporting period, there were no new displacement orders that specifically referenced any area containing a Palestinian refugee camp or an UNRWA shelter. On 17 November, Beirut faced renewed airstrikes, including on Ras el Nabaa, Mar Elias and Zoukak el Blat on 18 November.
+- UNRWA is working with a range of partner organisations (community based, local NGOs and international NGOs) in all its emergency shelters to provide a full range of services, including hot meals and psychosocial support activities. In its emergency response, UNRWA has relied on the dedication and commitment of partners on the ground.
+UNRWA has partnered with Lebanon’s national vaccination campaign in collaboration with the Ministry of Public Health (MoPH), WHO, and UNICEF to ensure all children receive essential vaccines for protection against polio, measles, rubella and mumps. At the
+Overall Situation
+- The International Organization for Migration (IOM) reports a total of 886,028 IDPs[1](51 per cent female and 49 per cent male) as of 18 November 2024. New displacements continue to be reported and recorded.
+- As of 20 November, 965 households, representing 3,281 people, are registered in UNRWA emergency shelters across the country, indicating a continued slow decrease for the eighth consecutive reporting period. UNRWA is monitoring this trend, noting that some Internally Displaced People (IDPs) have returned to their homes in the camps, while others have secured alternative housing arrangements by staying with relatives or renting. Despite the overall decrease in numbers, it is worth noting that UNRWA shelters do continue to record new arrival of IDPs in its shelters.
+[1] IOM Mobility Snapshot - Round 63: Lebanon: Displacement Tracking Matrix: Mobility Snapshot – Round 63 (18 November 2024)
+Humanitarian Access, Protection of Civilians
+- During the reporting period, there were no new displacement orders that specifically referenced any area containing a Palestinian refugee camp or an UNRWA shelter. On 17 November, Beirut faced renewed airstrikes, including on Ras el Nabaa, Mar Elias and Zoukak el Blat on 18 November.
+- No casualties among UNRWA staff have been reported during the reporting period. The UNRWA security team closely monitors the situation and staff movements to ensure the safety of frontline humanitarian workers.
+- No incident affecting UNRWA facilities was reported between 13 November and 20 November 2024.
+- The security situation in Tyre remains very tense, with the suspension of most services. On both 18 and 20 November, planned health service missions to refugee camps in the Tyre area were suspended. Through the support of ICRC, hygiene kits and food items could be distributed to the three camps in Tyre, over the reporting period.
+Partnerships
+- In all areas, UNRWA coordinates with local partners to provide additional services to displaced people. At each emergency shelter, a co-support partner has been identified. These co-support partners include Nabaa, Tadamon, Beit Atfal El-Somoud, Najdeh, Mobader and the Arab Resource Center for Popular Arts (ARCPA), al - Jana. UNRWA is also coordinating closely with UN Agencies and international organisations, including IOM, UNICEF, WFP, the Norwegian Refugee Council (NRC), Save the Children International, Cooperazione Internazionale (COOPI), and Action Against Hunger.
+UNRWA Shelters
+Open UNRWA Emergency Shelter Locations as at 20 /11/2024
+Programmatic &amp; Operational Response
+- On 3 October, UNRWA launched a Flash Appeal for US$ 27.3 million to address the urgent humanitarian needs resulting from the ongoing escalation in Lebanon, in addition to the displacement from Lebanon into Syria, over the next 90 days.
+Health
+- As of 20 November, out of 27 UNRWA health centers, 15 are operational while 12 remain closed due to the security context. Family Health Teams are rotating inside the 11 designated emergency shelters.
+- As of 20 November, UNRWA conducted over 12,229 consultations inside the shelters to Palestine Refugees from Lebanon (PRL), Palestine Refugees from Syria (PRS), Lebanese and others. The total number of health consultations at the remaining 15 operational health centers is 156,365, specifically for PRL and PRS.
+- On both 18 and 20 November, planned health missions to refugee camps in the Tyre area were suspended due to security concerns. Routine opening of primary health clinics in the Tyre area remains suspended.
+- In the Beqaa Area, all health centers remain operational. However, Wavel Camp Clinic is operational on an emergency basis only. In Central Lebanon Area (CLA), Shatila Health Center remains operational on a daily basis as of 7 November for primary health care services but had to suspend its services on 18 and 19 November due to security situation. In Saida, health clinics in Nabatieh, Ghazieh and Adloun remain closed.
+- The Musaytbeh Emergency Health Center will start providing dental care shortly, with mobile dental units pending maintenance.
+- Since the activation of the emergency, 105 emergency hospitalizations for the treatment of civilian war injuries were reported, including one UNRWA staff member.
+- On 12 November, UNRWA’s Health team started a vaccination campaign, in coordination with the Lebanese Ministry of Public Health, inside the 11 shelters. Children below five will be vaccinated against polio and children between 9 months and 10 years for Measles, Mumphs and Rubella (MMR) as well as a Vitamine A Supplementation (VAS). As of 20 November, 1,314 children below were vaccinated.
+- Six solar fridges have been provided by UNICEF to store vaccines in the newly established health centers with remote temperature monitoring devices. Two solar fridges have been installed in Musaytbeh Center and one in Beqaa, during the reporting period. The health team also plans to install solar fridges in Saida.
+- Active surveillance systems are established in all health centers and medical facilities to identify early signs of infectious disease outbreaks. Water tanks undergo chlorination and are routinely monitored for waterborne diseases. No further cholera cases have been reported.
+- On 17 November two Palestine refugees were killed in separate airstrikes in the city of Tyre; a male was targeted while riding his motorcycle, and a female was struck in the Shabriha neighborhood.
+- In al-Jarmak shelter, an incident between two displaced persons led to injuries and hospitalization. Most such sporadic conflics are solved through dialogue with support from the shelter managers and community committees. This underlines the continued need for community engagement activities in UNRWA shelters and effective conflict resolution mechanisms.
+- Palestine refugees remaining in the camps in Tyre area continue to appeal for protection and access to services, particularly health services.
+- On 19 November, a sit-in was conducted in Nahr el Bared Camp by Heraks activists to protest the delays in cash assistance. The same day, a list of demands was submitted by a committee of the displaced individuals of the shelters in the camp. Similar protests took place in Saida for cash assistance and hospitalization coverage.
+- UNRWA’s protection team continues to mainstream protection considerations aimed at improving the situation of the most vulnerable IDPs in the shelters. For example, over the reporting period, eleven Palestine refugees with disabilities in Yabud shelter were consulted on the accessibility in the shelter to ensure their needs are recognized.
+- On 13 November, the Legal Aid team conducted two online awareness sessions on the Cash for Work Programme, targeting a total of 51 youth. On 14 November, UNRWA and NRC conducted an awareness session in STC shelter on civil documentation and safeguarding of these documents. The session targeted 17 individuals.
+- On 14 November, the CCCM Specialist visited Nablus and Rafidiya shelters to discuss security management, challenges and support needed. Community Committees have been established in Nablus with a clear ToR. UNRWA’s Protection and Social Services teams are looking into expanding this model to other shelters, including through a training on the Code of Conduct.
+- UNRWA social workers provided 32 psychosocial support group sessions over the reporting period, targeting 655 individuals (383 women, 115 girls, 46 men and 111 boys) within the 11 shelters. Group sessions aim to address family issues and strengthen relationships.
+- Since the onset of the conflict, the social work team has provided 659 group interventions and awareness sessions, targeting 2,426 IDPs. These sessions cover topics such as the rights and duties of those residing in UNRWA shelters, GBV and child protection sensitization sessions, parenting skills, services information sessions, self-care sessions, hygiene sessions, communication skills and online safety.
+- The social workers coordinate closely with partners such as UNICEF, TDH, Save the Children, Hemaya, UPEL, Najdeh, Nabaa, Tadamon, Beit Afal and Al Somoud for additional support in UNRWA’s shelters.
+Water, Sanitation and Hygiene (WASH)
+- While UNRWA Water and Sanitation services are currently being maintained, UNRWA faces a risk of fuel shortage, especially in the Tyre area, where access to fuel is severely limited. Water pumping is operating at minimal levels. UNRWA is undertaking efforts to secure regular fuel deliveries to the camps in the Tyre area to enable the ongoing operation of water facilities.
+- The water levels in Nahr el Bared Camp (NBC) and its shelters, including Mount Tabour, Amqa, Toubas, Majeddo Mazar and Battir, have experienced challenges over the reporting period. In the camp, water shortages were reported as one of the water wells was out of order. Booster bumps have been installed in Battir and Mount Tabour schools to enhance the water supply and repairs will be taking place shortly.
+- Two water wells in Burj Shemali are currently non-operational and require maintenance. Repairs have been hindered by the security concerns. The camp currently relies on the three remaining functional water wells.
+- The generation of solid waste is also increasing in the Nahr el Bared Camp (NBC) and its shelters. During the reporting period, two compactors were out of order, requiring a private contractor to collect and dispose of the accumulated waste.
+- On average, there is a ratio of 15 IDPs per toilet in the 11 UNRWA designated shelters. UNRWA’s sanitation teams clean the sewer lines and manholes to avoid blockage and floodings. Some flooding already occurred two weeks ago in shelters in Saida City (Nablus and Rafidiya Schools). Despite previous successful interventions by the municipality, the issue has re-emerged again over the reporting period. The UNRWA team is working on finding a solution.
+- UNRWA teams are conducting maintenance and repairs across all 11 emergency shelters. Technical assessments have been completed. The team is currently in the tendering phase for Internal Accommodation Works for existing buildings in STC and rehabilitation of the existing water well in STC. Technical assessments for additional accommodation are in progress.
+- Winterization efforts are underway, with preparations ongoing such as clearing rooftop areas, manholes, as well as the inspection and maintenance of drainage systems. Additional winterization efforts are required, such as insulation, waterproof sealing, roof waterproofing systems, among others.
+Food Security
+- Preparations for the community kitchen in Nahr el Bared Camp are underway. This kitchen will serve all northern shelters and is anticipated to start operating on 1 December. WFP is providing lunch and dinner meals until the end of November. On 18 November, Al Kasser Bakery began baking and distributing bread to the IDPs. A total of 1,020 bags was distributed, 450 bags to IDPs inside shelters and 570 bags to displaced people outside the shelters.
+- In addition to the Community Kitchens, UNRWA is collaborating extensively with other organisations to ensure IDPs can fulfill their nutritional requirements. The Chief Area Officers coordinate closely with local NGOs. For instance, over the reporting period, ICRC supported in the distribution of food items to Tyre. In Central Lebanon Area (CLA) the Fingerprint of Change has increased their daily meals from 60 to 125 meals per day. Additionally, the Women’s Humanitarian Association delivers 100 breakfast sandwiches a day from Monday to Saturday. The Children’s Kitchen continues supplying daily meals, snacks, and toys for up to 30 children and 15 volunteers. Since 19 November, CLA will also distribute 70 bread packs daily at Yabud shelter through a partnership with a local bakery.
+Education
+- The start of the 2024/2025 academic year was postponed to 11 November due to insecurity in the country. During the Readiness Phase (Phase I), education staff started off with an administrative week to begin the year. Since 18 November, students have been engaged remotely with their teachers in social and emotional Learning, mental health and psychosocial support, recreational activities.
+- A review of the readiness phase will take place in the week of 25 November, Phase II – including the possibility of rolling out more formal learning and academic elements, depending on the outcome of the review, is due to start from 2 December. UNRWA remains dedicated to providing educational services to 38,006 students in grades 1 to 12, comprising 19,760 girls and 18,246 boys.
+- With the support of 42 school counselors, UNRWA provides psychosocial support services to children, youth, and adults across and beyond all 11 shelters in Lebanon. This includes psychosocial first aid, individual and group counseling, awareness sessions on gender-based violence (GBV) and protection from sexual exploitation and abuse (PSEA), as well other essential PSS interventions.
+- Since the onset of the armed conflict, approximately 3,500 people, including more than 1,500 children, have benefited from 3,008 psychosocial support sessions and recreational activities.
+- UNRWA has distributed 1,946 sets of psychosocial support kits. During the reporting period a total of 608 individuals, including 471 children (288 girls and 243 boys) accessed these vital services.
+- UNRWA's Education team is also providing remote psychosocial support to students and their families/caregivers outside emergency shelters to foster resilience, develop coping skills, and enhance wellbeing and safety. During the reporting period, 13 school counselors have conducted 1,334 care calls, reaching 120 adults and 194 children (124 girls and 70 boys).</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:03:56.614906+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #12 on the Syria emergency response to displacement from Lebanon: All information from 18-24 November 2024, valid as of 24 November at 14:00 [EN/AR] - Syrian Arab Republic</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/syrian-arab-republic/unrwa-situation-report-12-syria-emergency-response-displacement-lebanon-all-information-18-24-november-2024-valid-24-november-1400-enar</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2024-11-25</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Key Points
+- As of 21 November, an estimated 557,000 people have been displaced from Lebanon to Syria since 24 September, according to UNHCR
+- As of 24 November, 1,176 displaced Palestine Refugee families (3,373 people) had approached UNRWA in Syria. Out of them, 662 families (1,821 people) are Palestine Refugees registered in Syria who had fled during the crisis and our now returning, while 514 families (1,552 people) are Palestine Refugees registered in Lebanon
+- 949 heads of households (2,791 people) have so far responded to UNRWA’s displacement monitoring questionnaire. Out of the interviewees, over 78 per cent are women and children, and one per cent are people with disabilities.
+- Most of the above interviewees continue to be hosted by extended family and friends in increasingly crowded and deteriorating conditions. Over 91 per cent of them travelled with all their family members. Close to 56 per cent of them had previously lived in Syria and had fled the country during the crisis there. About 79 per cent of this group returned to the area or location where they lived before they fled Syria, and about 95 per cent cited the security situation in Lebanon as the key factor behind their decision to return to Syria.
+- During visits by UNRWA to homes that have taken in Palestine Refugees displaced from Lebanon, the reverberating message has been that the ability of families to continue hosting them has severely dwindled.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:04:02.689618+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #11 on the Syria emergency response to displacement from Lebanon: All information from 11-17 November 2024, valid as of 18 November at 14:00 [EN/AR] - Syrian Arab Republic</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/syrian-arab-republic/unrwa-situation-report-11-syria-emergency-response-displacement-lebanon-all-information-11-17-november-2024-valid-18-november-1400-enar</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Key Points
+- An estimated 528,000 people have been displaced from Lebanon to Syria since 24 September, according to UNHCR
+- As of 17 November, 1,184 displaced Palestine Refugee families (an estimated 5,920 people) had approached UNRWA in Syria. Another 17 families have now reportedly returned to Lebanon and one family has reportedly moved onwards to Iraq.
+- 938 heads of households (2,764 people) have so far responded to UNRWA’s displacement monitoring questionnaire. Out of the interviewees, over 78 per cent are women and children, and one per cent are people with disabilities.
+- Most of the above interviewees continue to be hosted by extended family and friends in increasingly crowded and deteriorating conditions. Over 91 per cent of them travelled with all their family members. Close to 56 per cent of them had previously lived in Syria and had fled the country during the crisis there. About 78 per cent of this group returned to the area or location where they lived before they fled Syria, and about 95 per cent cited the security situation in Lebanon as the key factor behind their decision to return to Syria.
+- During by UNRWA to homes that have taken in displaced Palestine Refugees from Lebanon, the reverberating message has been that the ability of families to continue hosting them has severely dwindled.
+Overall Situation
+- On the14 November, an Israeli missile attack launched from Lebanese airspace impacted Al Mouh Bridge near Al Qusair town, close to the Syrian-Lebanese border in south rural Homs, affecting an unofficial crossing point used by people fleeing Lebanon. From 26 September to the present, this marks the 34th attack in Al Qusair.
+UNRWA response overview
+- UNRWA’s response to the displacement includes information-sharing and referrals; inclusion in UNRWA’s pre-existing core education and health services; and the distribution of emergency relief and multipurpose cash assistance.
+- Palestine Refugees displaced from Lebanon to Syria are receiving the same UNRWA services (including health and education) as Palestine Refugees already living in Syria. However, the increasing numbers and inadequate funding received by the Agency this year areputting a strain on these services.
+- UNRWA’s Syria office has received a contribution of US$ 200,000 for multi-purpose cash assistance and hospitalization from the Agency’s regional flash appeal. However, this is only about 13% of what is required for this response for October-December 2024.
+Programmatic &amp; Operational Response
+Health
+- UNRWA continues to provide primary health care services in its clinics, in addition to referral services to contracted hospitals, x-ray centres and laboratories as needed.
+- With UNRWA’s system-wide E-health system, UNRWA doctors in Syria are able to access patient medical records online from their files in Lebanon in order to provide quality care.
+- As of 17 November, a total of 1,286 Palestine Refugees displaced from Lebanon had received medical services from UNRWA in Syria. 233 of these were new patients who received treatment between 11-14 November.
+- Services provided include treatment for non-communicable diseases, maternal and childcare, dental care, psychological and psychiatric care, hospitalization, among others.
+Protection
+- Palestine Refugees displaced from Lebanon participated in awareness-raising activities where they received key messages on the Prevention of Sexual Exploitation and Abuse (PSEA) as part of the emergency response.
+- UNRWA social workers are conducting visits to homes hosting displaced Palestine Refugees.
+- Psychosocial support activities are being conducted for children from displaced families.
+Non-Food Items (NFIs)/ Multipurpose Cash Assistance
+- Since the beginning of the response, UNRWA has provided 795 families (2,459 people) with NFI kits including blankets, jerrycans, kitchen sets, mats, mattresses, and tarpaulins. Distributions continue, and UNRWA anticipates that an additional 50 families will be reached this week.
+- To date, 716 families (2,127 individuals) have received the first round of multipurpose cash assistance with a transfer value of US$ 50 per family.
+- A second round of multi-purpose cash assistance to 1,120 families (3211 individuals) will be distributed this week with a transfer value of US$ 76 for those who received the first round and US$ 126 for those who did not receive it. By end of the second round, each family should have received a total of US$ 126.
+Food Assistance
+- UNRWA expects to receive and distribute 600 food baskets from WFP under an agreement between both agencies.
+Education
+- A total of 325 Palestine Refugee children displaced from Lebanon have been enrolled in UNRWA schools in Syria. One additional student has been enrolled in the UNRWA Technical and Vocational Education Programme.
+- They are receiving the same services provided to other UNRWA students, such as textbooks, back-to-school kits – which include a backpack or satchel, notebooks, and stationary - and psychosocial support. UNRWA education staff are developing materials to support students in the transition to the Syrian curriculum.
+- A few reports have been received about the inability of students coming without any identification documents to have the government placement tests administered to determine which grades they are supposed to be placed in.
+Quotes from female heads of Palestine Refugee families whose lived in Burj Shemali camp in Lebanon, and who fled to Syria and are being hosted by relatives and friends in Khan Danoun camp in rural Damascus:
+Mrs. Ruqia: "We thank UNRWA for the genuine and essential support it has provided. While we are grateful for the assistance received, we hope that efforts will be strengthened to provide further aid that can ease the burden of daily life and help us regain some stability.”
+Mrs. Lamia: "We are grateful to the family who hosted us, but we are in urgent need of further assistance, particularly in the form of rent support, so that we do not burden our relatives who have opened their doors to us in these difficult times."
+ENDS-
+Your donations can help provide emergency humanitarian assistance.
+FOR MORE INFORMATION, PLEASE CONTACT:
+Email:
+media@unrwa.org</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:04:08.909966+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #13 on the Lebanon Emergency Response: All information from 7 November - 12 November 2024, valid as of 12 November 2024 at 1:00 PM [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-13-lebanon-emergency-response-all-information-7-november-12-november-2024-valid-12-november-2024-100-pm-enar</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Key Points
+- UNRWA activated its Emergency Response in Lebanon on 24 September. The Agency is currently operating 11 emergency shelters across the country.
+- As of 12 November 2024, a total of 3,466 Internally Displaced People (IDPs) have registered in UNRWA shelters.
+- No incidents affecting UNRWA facilities were reported between 7 November and 12 November 2024. No casualties among UNRWA staff have been reported during the reporting period.
+- UNRWA is working with a range of partner organisations (community based, local NGOs and international NGOs) in all its emergency shelters to provide a full range of services, including hot meals and psychosocial support activities. In its emergency response, UNRWA has relied on the dedication and commitment of partners on the ground.
+Overall Situation
+- The International Organization for Migration (IOM) reports a total of 878,497 IDPs￼[1](52 per cent female and 48 per cent male) as of 11 November 2024. New displacements continue to be reported and recorded.
+- As of 6 November, 996 households, representing 3,466 people, are registered in UNRWA emergency shelters across the country, indicating a continued slow decrease for the seventh consecutive reporting period. UNRWA is monitoring this trend, noting that some Internally Displaced People (IDPs) have returned to their homes in the camps, while others have secured alternative housing arrangements by staying with relatives or renting.
+Humanitarian Access, Protection of Civilians
+- On 11 November, a displacement order included the Rashidieh area in Tyre and on 12 November, a warning disseminated through UN channels alerted staff of potential risks of airstrikes for the area next to the UNRWA Burj al-Barajneh’s Health Center.
+- No casualties among UNRWA staff have been reported during the reporting period. The UNRWA staff security team closely monitors the situation and staff movements to ensure the safety of frontline humanitarian workers.
+- No incident affecting UNRWA facilities was reported between 7 November and 12 November 2024.
+- The security situation in Tyre remains very tense, with the suspension of most services. On 8 November, El Buss Clinic was opened, and 166 patients were treated. During the reporting period, no further health service missions to Tyre were approved due to the security situation. Regular primary health service provision in Tyre remains suspended. UNRWA managed to provide 5,000 litres of gasoline for the operating of generators in Burj el Chamali as well as to the Rashidiyeh water well.
+Partnerships
+- In all areas, UNRWA coordinates with local partners to provide additional services to displaced people. At each emergency shelter, a co-support partner has been identified. These co-support partners include Nabaa, Tadamon, Taawon, Beit Atfal El-Somoud, Najdeh, Mobader, the Palestinian American Medical Association (PAMA), the Arab Resource Center for Popular Arts (ARCPA), the Palestine Red Crescent Society and the American Near East Refugee Aid (ANERA). UNRWA is also coordinating closely with UN Agencies and international organisations, including IOM, UNICEF, WFP, the Norwegian Refugee Council (NRC), Save the Children International, Cooperazione Internazionale (COOPI), and Action Against Hunger.
+UNRWA Shelters
+Programmatic &amp; Operational Response
+- On 3 October, UNRWA launched a Flash Appeal for US$ 27.3 million to address the urgent humanitarian needs resulting from the ongoing escalation in Lebanon, in addition to the displacement from Lebanon into Syria, over the next 90 days.
+Health
+- As of 12 November, out of 27 UNRWA health centers, 15 are operational while 12 remain closed due to the security context. Family Health Teams are rotating inside the 11 shelters.
+- As of 8 November, UNRWA conducted over 11,627 consultations inside the shelters to Palestine Refugees from Lebanon (PRL), Palestine Refugees from Syria (PRS), Lebanese and others. The total number of health consultations at the remaining 15 operational health centers is 118,291, specifically for PRL and PRS.
+- On 8 November, El Buss Clinic was opened, and 166 patients were treated. During the reporting period, no additional missions were approved to deliver health services in Tyre, due to the security situation. Regular primary health service provision in Tyre remains suspended.
+- In the Beqaa Area, all health centers remain operational. However, Wavel Camp Clinic is operational on an emergency basis only. In Central Lebanon Area(CLA) , Shatila Health Center remains operational on a daily basis as of 7 November for primary health care services, including for laboratory services. The Musaytbeh Emergency Health Center will start providing dental care as of next week, with mobile dental units currently undergoing maintenance. On 11 November, the mobile clinic in Amqa shelter in North Lebanon Area (NLA) opened for all IDPs inside the shelters.
+- Since the activation of the emergency, 90 emergency hospitalizations for the treatment of civilian war injuries were reported, including one staff member from UNRWA. No new cases have been reported since the last reporting period.
+- Active surveillance systems are established in all health centers and medical facilities to identify early signs of infectious disease outbreaks. Water tanks undergo chlorination and are routinely monitored for waterborne diseases. Vaccination efforts take place daily, with UNRWA collaborating with UNICEF to provide six solar refrigerators for vaccine storage in newly set up centers.
+- On 12 November, UNRWA’s Health team started a vaccination campaign, in coordination with the Lebanese Ministry of Public Health, inside the 11 shelters. Children below five will be vaccinated against polio and children between 9 months and 10 years for Measles, Mumphs and Rubella (MMR).
+Education
+- The start of the 2024/2025 academic year was postponed to 11 November due to the insecurity in the country. During the Readiness Phase (Phase I), education staff started off with an administrative week to begin the year. On 18 November, students will be provided with Social and Emotional Learning, Mental Health and Psychosocial Support, recreational activities, and structured activities to ensure readiness.
+- The Formal Education Phase (Phase II) is planned to start on 2 December. Classes will take place either in person or remotely – depending on the security situation and physical space available in each school and shelter. UNRWA remains dedicated to providing educational services to 38,006 students in grades 1 to 12, comprising 19,760 girls and 18,246 boys.
+- With the support of 42 school counselors, UNRWA provides psychosocial support services to children, youth, and adults across and beyond all 11 shelters in Lebanon. This includes psychosocial first aid, counseling, awareness sessions on gender-based violence (GBV) and protection from sexual exploitation and abuse (PSEA), as well as recreational and educational activities.
+- Since the onset of the armed conflict, approximately 3,500 people, including more than 1,500 children, have benefited from 2,723 psychosocial support sessions and recreational activities.
+- UNRWA has distributed 1,946 sets of psychosocial support kits during the reporting period to a total of 825 individuals, including 486 children (265 girls and 221 boys).
+- UNRWA's Education team is also providing remote psychosocial support to students and their families/caregivers outside emergency shelters to foster resilience, develop coping skills, and enhance wellbeing and safety. During the reporting period, 13 school counselors have conducted 860 care calls, reaching 134 adults and 166 children (75 girls and 91 boys).
+- On 7 November, UNRWA, UNICEF and the sub-partners conducted a partner coordination meeting to assess the needs and gaps in North Lebanon Area (NLA) and improve collaboration and coordination with the partners. On 13 November, an Activity Mapping Workshop will take place to ensure no-one is left behind and make the most efficient use of the available resources.
+Protection
+- On 9 and 11 November, when displacement orders were issued by the Israeli Army, the Protection Unit encountered access constraints. It has been unable to determine the exact impact of the displacement orders on the IDPs at Rashidiyeh Camp during the reporting period.
+- On 12 November, a message disseminated through UN channels warned of potential risks of airstrikes around the area next to UNRWA’s Health Clinic in Burj al-Barajneh Camp and urged its evacuation.
+- In North Lebanon Area(NLA), the Lebanese Armed Forces and Interior Security Forces continue to access the shelters in Nahr el Bared Camp to inquire about the number of IDPs and whether support is needed. In Saida, concerns are related to the loss of livelihood opportunities among Palestine refugees working in sectors such as construction and waste management.
+- On 6 November, the Legal Aid team conducted an awareness session on the Cash for Work Programme, and on 7 November on civil documentation. On the same day, the GBV Working Group reviewed the GBV risk assessments.
+- On 11 November, Humanitarian Principles sessions were provided to the Area Education Officers ahead of the Back-to-School 2024/2024 preparations.
+- The psychosocial support task force, composed of UNRWA’s Protection Specialists, Partnership Coordinator, Relief and Social Services, Health, and Education Psychosocial Support Focal Points, meets bi-weekly to strengthen coordination on case management and psychosocial support in Designated Emergency Shelters (DESs) .
+Water, Sanitation and Hygiene (WASH)
+- While UNRWA Water and Sanitation services are currently being maintained, UNRWA faces a risk of fuel shortage, especially in the Tyre area, where access to fuel is severely limited. Water pumping is operating at minimal levels. UNRWA is undertaking efforts to secure regular fuel deliveries to the camps in the Tyre area to enable the ongoing operation of water facilities.
+- The water levels in Bedawi, NBC and the UNRWA shelters in NLA are currently adequate, with no reported shortages. However, more fuel is required to support the extended operating hours to accommodate the residents in the camps and the displaced in the shelters.
+- Solid waste management activities have shown improvement across all areas in recent weeks, largely due to the identification of alternative dumping sites by the UNRWA sanitation team and effective coordination with municipalities responsible for final disposal in various regions. Shatila noted a buildup of waste resulting from the positioning of the communal collection points, owing to the municipality's inability to collect solid waste there for final disposal.
+- On average, there is a ratio of 15 IDPs per toilet in the 11 UNRWA designated shelters. UNRWA’s sanitation teams clean the sewer lines and manholes to avoid blockage and floodings. Some flooding already occurred two weeks ago in shelters in Saida City (Nablus and Rafidiya Schools). Unfortunately, these floodings have re-emerged over the reporting period. The issue was immediately addressed to the municipality.
+- UNRWA teams are conducting maintenance and repairs across all 11 emergency shelters. Technical assessments are starting to take place by the engineering teams to prepare for additional buildings. Filters for the reverse osmosis systems in Siblin Training Center and Beit Jala Shelter are being replaced.
+- Winterization efforts are underway, with preparations ongoing such as clearing rooftop areas, manholes, as well as the inspection and maintenance of drainage systems.
+Food
+- The kitchen at the Sibleen Training Center in Saida Area and the kitchens in Beqaa have started operating, including through support of in-kind dry food in bulk by COOPI to STC and warehouses in the North. The kitchen team is financially supported by Taawon and implemented by the Arab Resource Center for Popular Arts (ARCPA), commonly known as al-Jana, until the end of 2024. The kitchen in Nahr el Bared, which will serve all northern shelters, is ready, the recruitment of the kitchen team is currently ongoing. UNRWA is receiving support from WFP for the provision of bulk dry food for use in the kitchens.
+- In addition to the Community Kitchens, UNRWA is collaborating extensively with other organisations to ensure IDPs can fulfill their nutritional requirements. The Chief Area Officers coordinate closely with local NGOs. For instance, in CLA, the Fingerprint of Change provided 60 hot meals daily for IDPs for ten days. Additional hot meals were provided by Dream of Refugee. Furthermore, the Women’s Humanitarian Association supported UNRWA with 100 breakfast sandwiches daily. The Children’s Kitchen supplies daily meals, snacks, and toys for up to 30 children and 15 volunteers.
+ENDS-</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:04:14.940874+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Remarks by UNRWA Commissioner-General Philippe Lazzarini to the United Nations General Assembly Fourth Committee (13 November 2024, New York) [EN/AR] - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/remarks-unrwa-commissioner-general-philippe-lazzarini-united-nations-general-assembly-fourth-committee-13-november-2024-new-york-enar</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Madam Chair,
+Excellencies,
+This is a critical moment for UNRWA, our 33,000 staff members, and the millions of Palestine Refugees we serve.
+The risk of the Agency’s collapse threatens the lives and futures of individuals and communities, the stability of the region, and the integrity of our multilateral system.
+In open defiance of the United Nations Charter, the resolutions of the General Assembly and the Security Council, and the binding orders of the International Court of Justice, the State of Israel is working to unilaterally shift the long-established parameters for resolving the Israel-Palestine conflict.
+Last month, the Israeli parliament passed legislation that could end UNRWA’s operations in the occupied Palestinian territory in less than three months.
+This would fulfill an explicitly stated objective of the war in Gaza.
+Madam Chair,
+Unique among United Nations agencies, UNRWA is mandated to directly provide public-like services, including education for more than half a million children and primary healthcare.
+The Agency provides human development services for Palestine Refugees in the absence of a Palestinian state.
+During conflicts, UNRWA also provides humanitarian assistance to all those in need.
+Yet today, UNRWA is a casualty of the war in Gaza.
+At least 243 UNRWA personnel have been killed.
+Others have been detained and report being tortured.
+More than two-thirds of UNRWA premises have been damaged or destroyed.
+Palestinian armed groups, including Hamas, and Israeli forces have allegedly used our premises for military purposes.
+I have strongly, repeatedly and publicly condemned this alleged use of our premises.
+I continue to call for accountability for the attacks on UN personnel, premises and operations through an independent investigation into these violations.
+Excellencies,
+In addition to the attacks within the occupied Palestinian territory, the Agency has also been subjected to a fierce, global disinformation campaign.
+Intense lobbying by the Government of Israel and affiliated groups has targeted parliaments and governments in top donor countries.
+The attacks against UNRWA are justified by allegations that the Agency is colluding with or infiltrated by Hamas.
+UNRWA takes allegations of neutrality breaches extremely seriously.
+While we do not operate in a zero-risk environment, we take a zero-tolerance approach to any proven breaches.
+The Independent Review of UNRWA’s neutrality found that the Agency has a more robust neutrality framework than any comparable entity.
+We are making every effort to implement the recommendations of the review.
+I must emphasize that UNRWA – like comparable United Nations entities – does not have police, military or intelligence capabilities.
+We rely on Member States when such capacities are needed.
+For over 15 years, UNRWA has shared annually the names of its staff with the Government of Israel.
+We now share these names on a quarterly basis.
+This includes the names of staff about whom the government never previously raised concerns, but now include in lists alleging armed militancy.
+We have repeatedly asked the Government of Israel for evidence, and proposed how sensitive evidence might be shared.
+We have not received a response.
+UNRWA cannot address allegations for which it has no evidence.
+Yet, these allegations continue to be used to undermine the Agency.
+Madam Chair,
+UNRWA is a soft target for warring parties that view its presence and activities as a threat.
+Hamas has repeatedly and publicly accused UNRWA, especially its senior management, of colluding with the Israeli occupation.
+For many years, Hamas has strongly opposed UNRWA’s education programme, challenging our commitment to gender equality and neutrality.
+Hamas has even disapproved of the Agency’s Summer Fun Weeks programme, which brings girls and boys together for art, games, music and sports.
+Let me state the obvious – UNRWA is not a party to this conflict.
+It is a United Nations agency.
+It is the mechanism through which the United Nations is tasked – by the General Assembly – to assist Palestine Refugees.
+All parties to the conflict must allow UNRWA to fulfill its mandate.
+If the Agency cannot operate in the occupied Palestinian territory, the responsibility for providing services to Palestinians – and for bearing the cost of these services – will lie not with the United Nations, but with Israel as the occupying power.
+Excellencies,
+A year ago, I described to you the horror that I personally witnessed in Gaza a month into the war.
+I did not know then how much worse it would get.
+A year later, more than 43,000 people are reported killed. Nearly 70% are women and children.
+Thousands more lie unaccounted for under the rubble or have succumbed to disease.
+Nearly the entire population has been displaced, repeatedly.
+Hostages taken from Israel remain in terrifying captivity, and I continue to call for their immediate and unconditional release.
+North Gaza is under siege and Palestinians are being burned and buried alive by airstrikes.
+Hunger is widespread and famine has likely already taken hold.
+Israeli officials state that people will not be allowed to return there.
+Across Gaza, 660,000 children who should be in school are learning nothing more than how to survive.
+***
+The stakes are also high in the occupied West Bank.
+Settler violence and military incursions by the Israeli Security Forces are a daily reality.
+Public infrastructure is destroyed systematically during military operations, inflicting collective punishment on Palestinians.
+Illegal settlement activity is expanding aggressively, in total impunity.
+***
+Meanwhile, war has spilled into Lebanon.
+Nearly a million people have been displaced.
+And as in Gaza, UNRWA is supporting the humanitarian response.
+We have opened shelters hosting thousands of displaced people.
+***
+Nearly half a million people – among them 5,000 Palestine Refugees – have fled from Lebanon to Syria, which is struggling to recover from war, an economic crisis, and devastating earthquakes.
+Funding for Syria has dried up.
+UNRWA has had to cut back on critical cash and food assistance.
+***
+Jordan is not immune to growing regional instability.
+Many Palestine Refugees there are highly vulnerable to social and economic shocks.
+In this time of profound crisis and uncertainty, Palestine Refugees across the region are turning to UNRWA.
+And the Agency has never been in greater peril.
+Madam Chair,
+The implementation of the Knesset legislation will have catastrophic consequences.
+In Gaza, dismantling UNRWA will collapse the United Nations humanitarian response, which relies heavily on the Agency’s infrastructure.
+Glaringly absent from discussions about Gaza without UNRWA, is education.
+Palestinians value education highly – it is the only asset from which they have not, until now, been dispossessed.
+In the absence of a capable public administration or state, only UNRWA can deliver education to more than 660,000 girls and boys across Gaza.
+In the absence of UNRWA, an entire generation will be denied the right to education.
+Their future will be sacrificed, sowing the seeds for marginalization and extremism.
+Before the war, UNRWA addressed 70 to 80 percent of primary healthcare needs in Gaza.
+We still provide 16,000 medical consultations each day.
+In the West Bank, UNRWA’s collapse would deprive at least 50,00 children of education, and half a million Palestine Refugees of primary healthcare.
+Dismantling UNRWA will not terminate the refugee status of Palestinians – this status exists independently of the Agency – but it will severely harm their lives and future.
+***
+The Knesset legislation strikes a terrible blow to our staff.
+17,000 staff in the occupied Palestinian territory fear that they will lose their employment.
+They also fear further attacks, legitimized by these laws.
+It is a valid fear.
+Just last week, a female staff member in the West Bank was detained, intimidated and harassed by Israeli Security Forces.
+They accused her of working for a terrorist organization, seized her UNRWA laptop, and used it to access internal information.
+A total violation of United Nations privileges and immunities.
+Despite everything they have been through, my staff is afraid that the worst is yet to come.
+Excellencies,
+I will conclude by reiterating three requests I made to Member States last week, and making an additional request:
+First, I ask that Member States act to prevent the implementation of the legislation against UNRWA.
+Changes to UNRWA’s mandate are the prerogative of the General Assembly, not individual Member States.
+Second, I ask that Member States ensure that any plan for a political transition delineates UNRWA’s role.
+The Agency must progressively conclude its mandate within the framework of a political solution, and, in the occupied Palestinian territory, hand over its services to an empowered Palestinian administration.
+Third, I ask that Member States maintain funding to UNRWA, and do not withhold or divert funds on the assumption that the Agency can no longer operate.
+The cost of providing critical services, including education and healthcare, during a transition will be immense.
+My final request concerns the future of our multilateral system and the United Nations – of which UNRWA is an integral part.
+I ask that Member States utilize all the legal and political tools at their disposal to ensure that the international rules-based order is upheld.
+The United Nations and its staff are in an increasingly untenable position – if the legal and political framework within which we operate does not hold, we cannot stay and deliver.
+I urge you to consider seriously what that would mean for our collective future.
+Thank you.
+Background Information:
+UNRWA is the United Nations Relief and Works Agency for Palestine Refugees in the Near East. The United Nations General Assembly established UNRWA in 1949 with a mandate to provide humanitarian assistance and protection to registered Palestine refugees in the Agency’s area of operations pending a just and lasting solution to their plight.
+UNRWA operates in the West Bank, including East Jerusalem, The Gaza Strip, Jordan, Lebanon and Syria.
+Tens of thousands of Palestine refugees who lost their homes and livelihoods due to the 1948 conflict continue to be displaced and in need of support, nearly 75 years on.
+UNRWA helps Palestine Refugees achieve their full potential in human development through quality services it provides in education, health care, relief and social services, protection, camp infrastructure and improvement, microfinance, and emergency assistance. UNRWA is funded almost entirely by voluntary contributions.
+For more information, please contact:
+UNRWA on Twitter: @UNRWA
+Email: media@unrwa.org</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:04:21.299189+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #10 on the Syria emergency response to displacement from Lebanon: All information from 4 - 10 November 2024, valid as of 11 November 2024 at 14:00 [EN/AR] - Syrian Arab Republic</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/syrian-arab-republic/unrwa-situation-report-10-syria-emergency-response-displacement-lebanon-all-information-4-10-november-2024-valid-11-november-2024-1400-enar</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Key Points
+- An estimated 473,000 people have been displaced from Lebanon to Syria since 24 September, according to UNHCR.
+- As of 10 November, 1,084 displaced Palestine Refugee families (an estimated 5,420 people) had approached UNRWA in Syria. This excludes 17 families that have reportedly returned to Lebanon, and one family that has reportedly moved onwards to Iraq.
+- 895 heads of households (2,648 people) have so far responded to UNRWA’s displacement monitoring questionnaire. Out of the interviewees, over 78 per cent are women and children, and one per cent are people with disabilities.
+- Most of the above interviewees continue to be hosted by extended family and friends in increasingly crowded and deteriorating conditions. Over 91 per cent of them travelled with all their family members. Close to 56 per cent of them had previously lived in Syria and had fled the country during the crisis there. About 79 per cent of this group returned to the area or location where they lived before they fled Syria, and about 95 per cent cited the security situation in Lebanon as the key factor behind their decision to return to Syria.
+- During home visits conducted by UNRWA to families hosting displaced Palestine Refugees from Lebanon, these families have largely shared that their ability to continue hosting has severely dwindled due to their own socio-economic struggles and their worsening food security situation. Successive post-distribution monitoring by UNRWA show a consistently worsening food security situation among Palestine Refugees in Syria over the past three years, with food insecurity rates having increased from 46 per cent in September 2022 to 62 per cent in March 2024.
+Overall Situation
+- Since the 26 September, UN security has recorded at least 29 airstrikes by Israeli forces on south rural Homs, and at least 18 airstrikes on border crossing points between Lebanon and Syria. Locations hit include Al Qusayr town, in rural Homs, and Sayedah Zeinab in rural Damascus, where large numbers of displaced families are being hosted. UNRWA has had to postpone two missions to the latter location for security reasons due to these airstrikes.
+- Multiple aerial attacks were reported at border crossing points between Lebanon and Syria, notably two airstrikes at the Joussieh border crossing point, one of which was only a few metres from a UNHCR-supported community centre for the displaced. Another aerial attack was reported at an irregular crossing point in the Akkum village in the southern countryside of Homs. Two attacks were also reported in the same area, in Al Qusair, where displaced people from Lebanon are being hosted.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:04:27.412639+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Italy provides EUR 1 million to UNRWA for inclusive education for Palestine refugee children with disabilities in Lebanon [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/italy-provides-eur-1-million-unrwa-inclusive-education-palestine-refugee-children-disabilities-lebanon-enar</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>11 November 2024
+BEIRUT,
+UNRWA is pleased to announce a contribution of EUR 1 million from the Government of Italy to a 12-month project aimed at enhancing the social integration of vulnerable Palestine Refugees in Lebanon by improving inclusive education services and support for people with disabilities.
+The project will foster inclusive education services by supporting children with special education needs and disabilities in UNRWA schools, as well as improving access to both structured and unstructured psychosocial activities. It will also support people with disabilities by providing mobility devices, facilitating access to therapeutic services, and offering individualized follow-up support for children with disabilities enrolled in specialized institutions, thereby strengthening their external support system.
+The Director of UNRWA Affairs in Lebanon, Dorothee Klaus, said: “UNRWA is firmly committed to creating an inclusive educational environment that values the unique learning styles of every student. We aim to dismantle obstacles that impede the full participation of children with disabilities in our schools. With this generous support from the Italian government, we will significantly improve our capacity to identify and assist children with disabilities, providing essential resources for both them and our educators to foster a genuinely inclusive learning environment.”
+This project is critically important amid the escalation of violence in Lebanon, which has compounded existing challenges faced by the Palestine Refugee community in the country, notably because vulnerability of children often intensifies during and after disasters and conflict.
+Whether or not they are living with disabilities, many children in Lebanon are navigating changed family dynamics amid the escalation. For children with disabilities, access to essential equipment including mobility devices, along with tailored psychosocial support, can significantly enhance their overall well-being.
+“By addressing their unique needs, the project contributes to fostering psychosocial resilience, promoting a more stable family and community life, and improving dignity and independence for children in displacement settings. This support is not just essential for their current situation but also lays the groundwork for a more hopeful future,” said Klaus.
+Fabrizio Marcelli, Ambassador of Italy to Lebanon, said: “While the humanitarian context in Lebanon continues to deteriorate, education and protection remain fundamental pillars for the future of the most vulnerable children. As we call for an immediate ceasefire, we are simultaneously increasing humanitarian assistance to civilians: this contribution to UNRWA, a longstanding partner in the effort to ensuring that all children have the opportunity to learn and grow in a safe and inclusive environment, is part of a larger envelope of 28M euro Italy has immediately allocated to respond to the most pressing needs in Lebanon.”
+Alessandra Piermattei, Head of the Beirut office of the Italian Agency for Development Cooperation (AICS), added: "This contribution will support the social integration and protection of vulnerable children, guaranteeing over 12,000 Palestine Refugee children, including those with disabilities, access to quality, inclusive and equitable education, and promoting their social inclusion and participation in community life.”
+Italy has long been one of UNRWA’s most reliable donors. In 2023, Italy’s overall contribution to UNRWA amounted to US$ 1.46 million. Italy’s continuous support is of critical importance in view of the particularly dramatic conditions in which the Palestine Refugees in Lebanon are living.
+ENDs-
+Background Information:
+UNRWA is the United Nations Relief and Works Agency for Palestine Refugees in the Near East. The United Nations General Assembly established UNRWA in 1949 with a mandate to provide humanitarian assistance and protection to registered Palestine refugees in the Agency’s area of operations pending a just and lasting solution to their plight.
+UNRWA operates in the West Bank, including East Jerusalem, The Gaza Strip, Jordan, Lebanon and Syria.
+Tens of thousands of Palestine refugees who lost their homes and livelihoods due to the 1948 conflict continue to be displaced and in need of support, nearly 75 years on.
+UNRWA helps Palestine Refugees achieve their full potential in human development through quality services it provides in education, health care, relief and social services, protection, camp infrastructure and improvement, microfinance, and emergency assistance. UNRWA is funded almost entirely by voluntary contributions.
+Your support is crucial to help us provide emergency aid
+to displaced families in Gaza
+FOR MORE INFORMATION, PLEASE CONTACT:
+UNRWA on Twitter:
+Email:
+media@unrwa.org</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:04:33.427935+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #12 on the Lebanon Emergency Response: All information from 31 October - 6 November 2024, valid as of 6 November 2024 at 1:00 PM [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-12-lebanon-emergency-response-all-information-31-october-6-november-2024-valid-6-november-2024-100-pm-enar</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Key Points
+- UNRWA activated its Emergency Response in Lebanon on 24 September. The Agency is currently operating 11 emergency shelters across the country.
+- As of 6 November 2024, a total of 3,530 Internally Displaced People (IDPs) are registered in UNRWA shelters.
+- UNRWA is working with a range of partner organisations (community based, local NGOs and international NGOs) in all its emergency shelters to provide a full range of services, including hot meals and psychosocial support activities. In its emergency response, UNRWA has relied on the dedication and commitment of partners on the ground.
+- No incidents on UNRWA facilities were reported between 31 October and 6 November 2024. No casualties among UNRWA staff have been reported during the reporting period.
+Overall Situation
+- On 24 October, an International Conference in Support of Lebanon’s People and Sovereignty was held in Paris, to discuss the urgent need for increased contributions to UNRWA. An amount of US$800 million in humanitarian aid pledges was announced.
+- The International Organization for Migration (IOM) reports a total of 872,808 IDPs[1] (52 per cent female and 48 per cent male) as of 4 November 2024. New displacements continue to be reported and recorded.
+- As of 6 November, 1,015 households, representing a total of 3,530 people, are registered in UNRWA emergency shelters across the country, indicating a continued slow decrease for the sixth consecutive reporting period. UNRWA is monitoring this trend, noting that some Internally Displaced People (IDPs) have returned to their homes in the camps, while others have secured alternative housing arrangements by staying with relatives or renting.
+[1] IOM Mobility Snapshot - Round 59: Lebanon: Displacement Tracking Matrix: Mobility Snapshot – Round 59 (4 November 2024)
+Humanitarian Access, Protection of Civilians
+- A displacement order from the Israeli Army was issued for the city of Baalbek in the Beqaa Valley and the surroundings on 30 October and 31 October. The perimeter of the order also included the Wavel Palestine Refugee camp where several UNRWA installations are located.
+- On 31 October, the Israeli Army issued its first displacement order explicitly mentioning a Palestine refugee camp: Rashidieh (south of Tyre), along with ten other villages in southern Lebanon[2].
+- No casualties among UNRWA staff have been reported during the reporting period. The UNRWA staff security team closely monitors the situation and staff movements to ensure the safety of frontline humanitarian workers.
+- No incident on UNRWA facilities was reported between 31 October and 6 November 2024.
+- The security situation in Tyre remains very tense, with the suspension of all services except for water and waste management in the three camps. The security situation in Tyre has made it difficult to provide health services. However, following security clearance, two missions were authorized to deliver health services in camps in the Tyre area on November 4 and 6, and a third mission is planned for 8 November. On 5 November 2024, UNRWA delivered 11 tons of flour to the Rashidiyeh Camp to bake bread that was offered at no cost to the Palestine Refugees in the Tyre area. Delivery of flour will also take place to additional five bakeries in other locations across the country and close to UNRWA points of operations.
+[2] OCHA Lebanon Flash Update #40: Escalation of hostilities in Lebanon (31 October 2024)
+Partnerships
+- In all areas, UNRWA coordinates with local partners to provide additional services to displaced people. At each emergency shelter, a co-support partner has been identified. These co-support partners include Nabaa, Tadamon, Taawon, Beit Atfal El-Somoud, Najdeh, Mobader, the Arab Resource Center for Popular Arts (ARCPA), the Palestine Red Crescent Society (PRCS) and the American Near East Refugee Aid (ANERA). UNRWA is also coordinating closely with UN Agencies and international organisations, including the International Organization for Migration (IOM), the International Children's Emergency Fund (UNICEF), the World Food Programme (WFP), the Norwegian Refugee Council (NRC), Save the Children International (SCI), Cooperazione Internazionale (COOPI), and Action Against Hunger (AAH).
+Programmatic &amp; Operational Response
+- On 3 October, UNRWA launched a Flash Appeal for US$ 27.3 million to address the urgent humanitarian needs resulting from the ongoing escalation in Lebanon, in addition to the displacement from Lebanon into Syria, over the next 90 days.
+Health
+- As of 6 November, out of 27 UNRWA health centers, 15 are operational while 12 remain closed due to the security context. Family Health Teams are rotating inside the 11 shelters.
+- On 4 November 2024, the Health Programme managed to open Burj el Chamali Clinic and conducted 350 consultations. On 6 November 2024, the Health Programme managed to open Rashadieh Health Clinic and conducted 542 consultations.
+- After further security assessments in Shatila, the health center will become operational on a daily basis as of 7 November for primary health care services.
+- As of 5 November, UNRWA conducted over 11,269 consultations inside the shelters to Palestine Refugees from Lebanon (PRL), Palestine Refugees from Syria (PRS), Lebanese and others. The total number of health consultations at the remaining 15 operational health centers is 95,308, specifically for PRL and PRS.
+- Since the activation of the emergency, 90 emergency hospitalizations for the treatment of civilian war injuries were reported, including one staff member from UNRWA.
+- Active surveillance systems are established in all health centers and medical facilities to identify early signs of infectious disease outbreaks. Water tanks undergo chlorination and are routinely monitored for waterborne diseases. Vaccination efforts take place daily, with UNRWA collaborating with UNICEF to provide six solar refrigerators for vaccine storage in newly set up centers.
+Education
+- With the support of 42 school counselors, UNRWA provides psychosocial support services to children, youth, and adults across and beyond all 11 shelters in Lebanon. This includes psychosocial first aid, counseling, awareness sessions on gender-based violence (GBV) and protection from sexual exploitation and abuse (PSEA), as well as recreational and educational activities.
+- Since the onset of the armed conflict, approximately 3,500 people including more than 1,500 children have benefited from 2,366 PSS sessions and recreational activities.
+- In addition, UNRWA has distributed 1,946 sets of PSS kits during the reporting period to a total of 903 individuals, including 689 children (355 girls and 334 boys).
+- UNRWA's Education team is also providing remote psychosocial support (PSS) to students and their families/caregivers outside emergency shelters to foster resilience, develop coping skills, and enhance wellbeing and safety. Since the beginning of the emergency, 13 school counselors have conducted 1,048 care calls, reaching 625 adults and 945 children (487 girls and 458 boys).
+- In preparation for Phase II of its Education in Emergencies (EiE) programme, UNRWA Education team has launched an emergency tracking system to monitor the locations of all UNRWA students and staff. This system aims to identify where the children are, assess the available workforce, and develop a plan for the 2024-25 academic year, adapting the modality for each school to be physical when possible, or blended or remote when necessary.
+- The start of the 2024/2025 academic year, originally scheduled for 4 November, was postponed by UNRWA due to the insecurity in the country. The Education Programme is in the process of determining a new starting date. UNRWA remains dedicated to providing educational services to 38,006 students in grades 1 to 12, comprising 19,760 girls and 18,246 boys.
+- UNRWA Protection team is implementing conflict prevention measures in emergency shelters following some reports of fighting between families, primarily linked to overcrowding. The importance of respecting safety regulations has been communicated to all involved.
+- During this reporting period, the UNRWA Protection team has been conducting regular community engagement coaching sessions with various stakeholders, including emergency shelter managers, to strengthen active involvement of community members in emergency shelters, ensuring that IDPs' voices are heard, and their knowledge and needs are integrated into the response of all UNRWA programmes.
+Water, Sanitation and Hygiene (WaSH)
+- While UNRWA Water and Sanitation services are currently being maintained, UNRWA faces a potential risk of fuel shortage, especially in the Tyre area, where access to fuel is severely limited. Water pumping is operating at minimal levels. UNRWA is undertaking efforts to secure regular fuel deliveries to the camps in the Tyre area to enable the ongoing operation of water facilities.
+- Solid waste management activities have shown improvement across all areas in recent weeks, largely due to the identification of alternative dumping sites by the UNRWA sanitation team and effective coordination with municipalities responsible for final disposal in various regions. In Ein el Hilweh, the restrictions to export solid waste from the camp as capacity to inspect the outgoing waste by Lebanese government forces as per ususal procedures is limitedare leading to an accumulation of waste within the camp.
+- On average, there is a ratio of 15 IDPs per toilet in the 11 UNRWA designated shelters. UNRWA’s sanitation teams clean the sewer lines and manholes to avoid blockage and floodings. Some flooding already occurred in the past week in shelters in Saida City (Nablus and Rafidiya Schools).
+- UNRWA teams are conducting maintenance and repairs across all 11 emergency shelters. Technical assessments are starting to take place by the engineering teams to prepare for additional buildings.
+- Winterization efforts are underway, with preparations ongoing like clearing rooftop areas and manholes.
+Food
+- UNRWA has distributed flour to six bakeries covering different areas of the country to pilot the production of bread, with available donated flour, to provide bread at no cost to affected Palestinian communities.
+- UNRWA is finalizing the establishment of community kitchens to prepare meals for internally displaced persons (IDPs) in emergency shelters. The kitchen at the Sibleen Training Center in Saida and the kitchens in Beqaa are ready for operation. The kitchen in Nahr el Bared, which will serve all northern shelters, is undergoing refurbishment. Hot meals are meanwhile provided by partners, such as Taawon.
+Logistics
+- Since the Logistics Cluster activation on 8 October 2024, nearly 180 metric tons of relief items. including hygiene kits, mattresses and other non-food items, have been dispatched through the Amman corridor to Beirut, supporting UNICEF, UNRWA, and UNHCR warehouses as key transition hubs to reach affected populations [3].
+- Eleven tons of flour were dispatched to Rashidieh camp.
+- Two trucks of medicines and medical consumables arrived in Lebanon via the Amman corridor.
+- The requested kitchen items to start operating the Siblin shelter kitchen for cooking for hundreds, potentially thousands of displaced, have arrived at the location.
+- [3] WFP Lebanon Emergency Response: External Situation Report 6 (31 October 2024)
+ENDS-
+Your donations can help provide emergency humanitarian assistance.
+FOR MORE INFORMATION, PLEASE CONTACT:
+Email:
+media@unrwa.org</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:04:39.668891+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #11 on the Lebanon Emergency Response: All information from 24 October - 30 October 2024, valid as of 30 October 2024 at 1:00 PM [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-11-lebanon-emergency-response-all-information-24-october-30-october-2024-valid-30-october-2024-100-pm-enar</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Key Points
+- UNRWA activated its Emergency Response in Lebanon on 24 September. The Agency is currently operating 11 emergency shelters across the country.
+- As of 30 October 2024, a total of 3,669 Internally Displaced Persons (IDPs) are registered in UNRWA shelters.
+- UNRWA is working with a range of partner organisations (community based, local NGOs and international NGOs) in all its emergency shelters to provide a full range of services, including hot meals and psychosocial support activities. In its emergency response, UNRWA has relied on the dedication and commitment of partners on the ground.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:04:45.768922+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #8 on the Syria emergency response to displacement from Lebanon. All information from 24 October - 27 October 2024, valid as of 27 October 2024 at 14:00 [EN/AR] - Syrian Arab Republic</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/syrian-arab-republic/unrwa-situation-report-8-syria-emergency-response-displacement-lebanon-all-information-24-october-27-october-2024-valid-27-october-2024-1400-enar</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Key Points
+- An estimated 440,000 people have been displaced from Lebanon to Syria according to UNHCR.
+- As of 27 October, 904 displaced Palestine Refugee families (an estimated 4,500 people) had approached UNRWA in Syria. The actual number of Palestine Refugee families who have crossed the borders is believed to be significantly higher. UNRWA is making continued efforts to liaise with local authorities to assess and respond to the needs of Palestine Refugees living in hosting centres across Syria, under the responsibility of the Government of Syria.
+- UNRWA has developed a questionnaire to gather disaggregated data and assess the immediate needs of the new arrivals. As of 27 October, 733 heads of households (2,197 people) had responded to the questionnaire. Out of the interviewees, over 77 per cent are women and children, and one per cent are people with disabilities. The vast majority of Palestine Refugees displaced from Lebanon are hosted by extended family and friends in overcrowded conditions.
+Overall Situation
+- The UN Resident and Humanitarian Coordinator for Syria, Adam Abdelmoula, expressed concern about the repeated airstrikes on border crossings between Lebanon and Syria, the latest being the 25 October airstrikes on the Joussieh crossing in Syria, the Al-Masnaa crossing in Lebanon, and the Jdeidat Yabous crossing in Syria. In his statement, he decried these attacks and the implications on the safety of people escaping the hostilities in Lebanon.
+- Out of the 2,197 Palestine Refugees displaced from Lebanon who participated in the questionnaire survey by UNRWA, over 56 per cent had previously lived in Syria and had fled the country during the crisis. Almost 94 per cent of them reported the security situation in Lebanon as the key factor behind their decision to return to Syria. Close to 90 per cent returned with all their family members, and almost 80 per cent returned to the area or location they lived in before they fled Syria. As the vast majority are currently relying on friends and extended family for housing and basic needs, the provision of material support to make their return to Syria sustainable is critical. Many have also requested assistance with the repair of their damaged houses in Syria.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:04:51.797219+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #10 on the Lebanon Emergency Response: All information from 21 October - 24 October 2024, valid as of 24 October 2024 at 1:00 PM [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-10-lebanon-emergency-response-all-information-21-october-24-october-2024-valid-24-october-2024-100-pm-enar</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Key Points
+- UNRWA activated its Emergency Response in Lebanon on 24 September. The Agency is currently operating 11 emergency shelters across the country.
+- As of 24 October 2024, a total of 3,679 Internally Displaced Persons (IDPs) are registered in UNRWA shelters, marking a decrease of 78 individuals since the last report.
+- UNRWA is working with a range of partner organisations (community based, local NGOs and international NGOs) in all its emergency shelters to provide a full range of services, including hot meals and psychosocial support activities. In its emergency response, UNRWA has relied on the dedication and commitment of partners on the ground.
+Overall Situation
+- The International Organization for Migration (IOM) reports a total of 809,043 IDPs[1] (52 per cent female and 48 per cent male) as of 20 October 2024. New displacements continue to be reported and recorded.
+- As of 21 October, 1,056 households, representing a total of 3,679 people, are registered in UNRWA emergency shelters across the country marking a decrease for the fourth consecutive reporting period. UNRWA is monitoring this decrease in numbers. Some IDPs have returned to their homes in the camps, while others have secured alternative housing arrangements, either by being hosted by relatives or through rentals. A significant return of IDPs is reported in the Tyre area, particularly from shelters in the Saida area, with many choosing to remain in the camps despite the ongoing heavy airstrikes. Factors influencing this movement include perceptions of improved safety in camps in the south, challenges in adapting to conditions of life in the shelters, and the need to protect livelihoods.
+[1] Mobility Snapshot - Round 55 - 21-10-2024: Lebanon - Mobility Snapshot - Round 55 - 21-10-2024 | Displacement Tracking Matrix (iom.int)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:04:57.831611+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #7 on the Syria emergency response to displacement from Lebanon. All information from 21 October - 23 October 2024, valid as of 23 October 2024 at 14:00 [EN/AR] - Syrian Arab Republic</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/syrian-arab-republic/unrwa-situation-report-7-syria-emergency-response-displacement-lebanon-all-information-21-october-23-october-2024-valid-23-october-2024-1400-enar</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Key Points
+- An estimated 425,000 people have been displaced from Lebanon to Syria according to UNHCR.
+- As of 23 October, 814 displaced Palestine Refugee families (an estimated 4,000 people) had approached UNRWA in Syria. The actual number of Palestine Refugee families who have crossed the borders is believed to be significantly higher, especially in northern and eastern rural Damascus. UNRWA is making continued efforts to liaise with local authorities to assess and respond to the needs of Palestine Refugees living in hosting centres across Syria, under the responsibility of the Government of Syria.
+- UNRWA has developed a questionnaire, being implemented across all its areas of operation, to gather disaggregated data and assess the immediate needs among the new arrivals. As of 23 October, 654 heads of households (1,964 people) had responded to the questionnaire. Out of the interviewees, over 77 per cent are women and children, with one per cent being people with disabilities. The vast majority of Palestine Refugees displaced from Lebanon are hosted by extended family and friends in overcrowded conditions.
+UNRWA provides Palestine Refugees displaced from Lebanon with non-food items in Damascus, Syria. © 2024 UNRWA Photo.
+Overall Situation
+- UNHCR reported that Syrian immigration authorities continue to show flexibility in admitting displaced people, and that the Government of Syria has extended an exemption until the beginning of November 2024 for returning Syrians, including Palestine Refugees from Syria, from rules requiring them to exchange US$ 100 at the border before entry. However, Lebanese immigration has resumed an Exit Stamping Protocol, which may slow down the processing of displaced people at the border or discourage the use of official border crossings.
+- Out of the 1,964 Palestine Refugees displaced from Lebanon who participated in the questionnaire survey by UNRWA, over 55 per cent had previously lived in Syria and had fled the country during the crisis. Almost 93 per cent reported the security situation in Lebanon as the key factor behind their decision to return to Syria. Over 61 per cent returned with all their family members, and almost 80 per cent returned to the area or location that they lived in before they fled Syria. As the vast majority are currently relying on friends and extended family for housing and basic needs, the provision of material support to make their return to Syria sustainable is critical. Many have also requested assistance with repair of their damaged houses in Syria.
+UNRWA Response
+- UNRWA’s current funding situation does not allow the Agency to provide sufficient emergency support to the displaced people arriving from Lebanon. The Syria portion of the Syria, Lebanon and Jordan Emergency Appeal 2024 is only 16 per cent funded as of 30 September, while the UNRWA Flash Appeal for the Lebanon Situation, remains 0 per cent funded.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:05:03.891206+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unity in Crisis: UNRWA's inclusive approach to shelter displaced people in Lebanon - Lebanon</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unity-crisis-unrwas-inclusive-approach-shelter-displaced-people-lebanon</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>On October 8, 2024, Ghazi, a 53-year-old Lebanese man originally from the Al Bustan area near the Blue Line in Southern Lebanon, saw his world turned upside down. With the escalation of the conflict in Lebanon, he, his wife Zahra, their two daughters, two sons, and his elderly mother Alia were forced to flee their home. They joined countless others seeking safety, facing uncertainty and fear.
+Their journey first led them to Babliyeh, a nearby village in the southern district of Saida, but soon they found themselves forced to leave once again in search of safety. The sound of bombardment resonated everywhere, each explosion echoing the urgency of their need to find refuge. With resolve, Ghazi gathered his family and pushed forward to Saida, where they were directed by municipal officials to Nablus School, one of UNRWA’s designated emergency shelters.
+Upon arrival at the shelter, the family saw hundreds of displaced people, including Lebanese, Syrians, and Palestine Refugees, gathered in the school. All were sharing the same difficulties and uncertainties.
+At the school, Ghazi’s family was received by UNRWA staff who welcomed and registered them, guided them to their room, and provided them with basic necessities.
+The family received essential supplies including mattresses, blankets, pillows, hot meals, water, and hygiene products.
+UNRWA collaborates with a range of partner organisations, including community-based, local NGOs, and international NGOs, in all its emergency shelters to provide a full range of services, including hot meals and psychosocial support activities.
+"It’s my first time living with Palestinians and Syrians under the same roof, and it’s been eye-opening,” Ghazi said.
+He added: “Now, my best friends here are Ali, a Palestinian, and Ahmad, a Syrian. Here in this place, we share meals, stories, and laughter, which brings us closer together. We listen to each other’s experiences, views, and thoughts, creating a deeper connection. We support each other through tough times.
+“We keep talking about recent developments, especially since we are facing the same challenges now. Even with everything happening outside, we’re creating a home together, showing that solidarity can overcome fear” he added.
+“UNRWA’s inclusive approach to emergency sheltering in Lebanon now accommodates over 4,000 displaced individuals across 11 shelters, comprising Palestinians, Lebanese, and Syrians. By bringing together diverse populations under one roof, UNRWA fosters a sense of unity and support for all communities during times of crisis,” said Dorothee Klaus, Director of UNRWA Affairs in Lebanon.
+Ghazi also expressed the hope that this war will end soon, and all displaced people will return to their homes. He reiterated that the silver lining to this displacement is that he has made new friends among the Palestinians and Syrians. He now looks forward to keeping in touch with them even after this ordeal is over.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:05:09.864058+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Statement of Philippe Lazzarini, Commissioner-General of UNRWA at the International Conference in Support of Lebanon’s People and Sovereignty [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/statement-philippe-lazzarini-commissioner-general-unrwa-international-conference-support-lebanons-people-and-sovereignty-enar</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Paris
+Monsieur le Président,
+Monsieur le Premier Ministre,
+Excellences,
+The escalating conflict in Lebanon is a tragic expansion of the devastating war in Gaza and the crisis in the West Bank.
+It is the spillover of conflict that we have feared for more than a year.
+Civilians once again are paying a heavy price.
+Air strikes are killing and injuring thousands of people, many of them women and children.
+Hundreds of thousands of people are displaced, searching for safety in a climate of fear and uncertainty.
+UNRWA – the United Nations Agency for Palestine Refugees – is offering shelter and humanitarian assistance to those in need throughout the country.
+Our shelters are currently hosting nearly 4,000 Palestinian, Lebanese and Syrian displaced people.
+This inclusive approach is critical for keeping intercommunal tensions at bay.
+We are providing daily meals and psychological support.
+We are also working with partners on the early detection of infectious disease outbreaks.
+To continue running our shelters and responding to growing humanitarian needs we need additional funding.
+Funding, however, is not all that is needed to provide humanitarian assistance and protection to civilians.
+We also require an enabling environment to operate.
+This includes respect for international humanitarian law.
+In Gaza only, at least 232 UNRWA staff have been killed.
+Over 200 UNRWA premises have been damaged or destroyed.
+Draft legislation in the Israeli Knesset seeks to collapse our operations in the occupied Palestinian territory.
+This would have a devastating impact on the provision of humanitarian aid and essential services like education and primary healthcare to millions of Palestine Refugees, including those in Lebanon.
+The failure to push back effectively against attempts to intimidate and undermine the United Nations has set a dangerous precedent.
+I must stress that these attacks are not confined to UNRWA.
+They are attacks on our common multilateral system.
+The attacks on the United Nations Interim Force in Lebanon demonstrate a disturbing trend that must be reversed.
+I urge all governments to give the utmost priority to ensuring respect for the international rules-based order and the United Nations.
+Today is United Nations Day.
+A renewed commitment to multilateralism and our shared values, enshrined in the UN Charter, must guide our response in Lebanon and across the region.
+Thank you.
+Background Information:
+UNRWA is the United Nations Relief and Works Agency for Palestine Refugees in the Near East. The United Nations General Assembly established UNRWA in 1949 with a mandate to provide humanitarian assistance and protection to registered Palestine refugees in the Agency’s area of operations pending a just and lasting solution to their plight.
+UNRWA operates in the West Bank, including East Jerusalem, The Gaza Strip, Jordan, Lebanon and Syria.
+Tens of thousands of Palestine refugees who lost their homes and livelihoods due to the 1948 conflict continue to be displaced and in need of support, nearly 75 years on.
+UNRWA helps Palestine Refugees achieve their full potential in human development through quality services it provides in education, health care, relief and social services, protection, camp infrastructure and improvement, microfinance, and emergency assistance. UNRWA is funded almost entirely by voluntary contributions.
+Your support is crucial to help us provide emergency aid
+to displaced families in Gaza
+For more information, please contact:
+UNRWA on Twitter:
+Email:
+Show Email</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:05:15.923704+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>The EU disbursement of EUR 16 million will continue to provide much needed support to Palestine refugees in Gaza and in the region - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/eu-disbursement-eur-16-million-will-continue-provide-much-needed-support-palestine-refugees-gaza-and-region</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>23 October 2024
+AMMAN- UNRWA welcomes a much-anticipated disbursement of EUR 16 million from the European Commission. This payment is the remaining tranche of the EU’s contribution to the Agency for 2024, bringing to EUR 82 million the EU's total assistance to UNRWA’s core budget for this year.
+UNRWA Commissioner-General Philippe Lazzarini said: “this timely contribution will enable the continuation of urgent humanitarian assistance in Gaza and essential services, including education and healthcare, in the region. I am grateful to the EU for its trust in the Agency’s systems and oversight processes and principled commitment to the human development of Palestine Refugees. UNRWA remains fully committed to the humanitarian principles, including neutrality, and we reaffirm our unwavering dedication to these values."
+Despite increased challenges facing its operations and the safety of its staff, UNRWA remains the backbone of the humanitarian operation in Gaza. The EU-UNRWA partnership is vital to support millions of Palestine Refugees in Gaza, the occupied West Bank – including East Jerusalem - Syria, Jordan, and Lebanon, where the Agency has activated its emergency response to provide shelter and assistance to those displaced by the ongoing conflict.
+Notes to editors
+- Since 1971, the strategic UNRWA-EU partnership has been based on the shared objective of supporting the human development, humanitarian assistance, and protection of Palestine Refugees.
+- The EU is the largest multilateral provider of international assistance to Palestine Refugees. Collectively, the EU and its Member States are among the largest contributors to the Agency's programme budget, humanitarian emergency appeals and projects.
+Background Information:
+UNRWA is the United Nations Relief and Works Agency for Palestine Refugees in the Near East. The United Nations General Assembly established UNRWA in 1949 with a mandate to provide humanitarian assistance and protection to registered Palestine refugees in the Agency’s area of operations pending a just and lasting solution to their plight.
+UNRWA operates in the West Bank, including East Jerusalem, The Gaza Strip, Jordan, Lebanon and Syria.
+Tens of thousands of Palestine refugees who lost their homes and livelihoods due to the 1948 conflict continue to be displaced and in need of support, nearly 75 years on.
+UNRWA helps Palestine Refugees achieve their full potential in human development through quality services it provides in education, health care, relief and social services, protection, camp infrastructure and improvement, microfinance, and emergency assistance. UNRWA is funded almost entirely by voluntary contributions.
+Your support is crucial to help us provide emergency aid
+to displaced families in Gaza
+For more information, please contact:
+UNRWA on Twitter:
+Email:</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:05:21.915239+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #9 on the Lebanon Emergency Response. All information from 18 October - 21 October 2024, valid as of 21 October 2024 at 13:00 [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-9-lebanon-emergency-response-all-information-18-october-21-october-2024-valid-21-october-2024-1300-enar</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Key Points
+- UNRWA activated its Emergency Response in Lebanon on 24 September. The Agency is currently operating 11 emergency shelters across the country.
+- As of 21 October 2024, a total of 3,757 Internally Displaced Persons (IDPs) are registered in UNRWA shelters, marking a decrease of 72 individuals since the last report. Reports indicate that some people from the Tyre area have sought to return to the south in recent days.
+- UNRWA is working with a range of partner organisations (community based, local NGOs and international NGOs) in all its emergency shelters to provide a full range of services, including hot meals and psychosocial support activities. In its emergency response, UNRWA has relied on the dedication and commitment of partners on the ground.
+Overall Situation
+- The International Organization for Migration (IOM) reports a total of 809,043 IDPs (52 per cent female and 48 per cent male) as of 20 October 2024. New displacements continue to be reported and recorded.
+- During the reporting period, Israeli Forces’ airstrikes on Beirut's southern suburbs and on villages in southern and eastern Lebanon continued. Casualties are on the rise as Lebanon’s Ministry of Public Health has reported 2,412 deaths and 11,285 injuries [1]. Vulnerable populations are the worst affected.
+- Education institutions in Lebanon remain closed, with the start of the school year postponed to 4 November following an announcement from the Ministry of Education and Higher Education (MEHE).
+- As of 21 October, 1,074 households, representing a total of 3,757 people, are registered in UNRWA emergency shelters across the country marking a decrease for the third consecutive reporting period. UNRWA is monitoring this decrease in numbers, noting that some IDPs have returned to their homes in Tyre, particularly from shelters in the Saida area. Factors influencing this movement include perceptions of improved safety in camps in the south, challenges in adapting to conditions of life in the shelters, and the need to protect livelihoods. This requires further monitoring to assess potential protection risks for returnees.
+[1] OCHA Flash Update #36 (as of 17 October 2024): Lebanon: Flash Update #36 - Escalation of hostilities in Lebanon, as of 17 October 2024 - Lebanon | ReliefWeb</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:05:27.967080+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #6 on the Syria emergency response to displacement from Lebanon. All information from 17 October - 20 October 2024, valid as of 20 October 2024 at 14:00 [EN/AR] - Syrian Arab Republic</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/syrian-arab-republic/unrwa-situation-report-6-syria-emergency-response-displacement-lebanon-all-information-17-october-20-october-2024-valid-20-october-2024-1400-enar</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Key Points
+- Around 421,000 people are estimated to have been displaced from Lebanon to Syria.
+- As of 20 October, 635 Palestine Refugee families - an estimated 3,000 people, based on average family sizes - who have been displaced from Lebanon had approached UNRWA in Syria. However, it is believed that the actual number of Palestine Refugee families who have crossed the borders is significantly higher, especially in northern and eastern rural Damascus. UNRWA is making continued efforts to liaise with local authorities to assess and respond to the needs of Palestine Refugees living in 17 out of 35 locally established hosting centres across Syria, under the responsibility of the Government of Syria.
+- UNRWA has developed a questionnaire, being implemented across all its operation areas, to gather disaggregated data and assess the immediate needs among the new arrivals. As of 20 October, 495 heads of households (1,468 people) had responded to the questionnaire. Out of the interviewees, 46 per cent are male and 54 per cent female, almost 43 per cent of the new arrivals are children, with 1 per cent being people with disabilities. The vast majority of Palestine Refugees displaced from Lebanon are hosted by extended family and friends in overcrowded conditions. This support is temporary.
+Overall Situation
+- UNHCR reported that Syrian immigration authorities continue to admit displaced people flexibly and that the Government of Syria has extended an exemption until the beginning of November 2024 for returning Syrians, including Palestine Refugees from Syria, requiring them to exchange US$ 100 at the border before entry. However, Lebanese immigration has resumed an Exit Stamping Protocol, which may slow down the processing of displaced people at the border or discourage the use of official border crossings.
+- Many Palestine Refugees displaced from Lebanon are relying on friends and extended family for housing and basic needs. Considering that this support system is believed to be only available for a limited time and extent, it is probable that they will revert to UNRWA for support. Many families returning to Aleppo, Damascus and Dera’a have reported that they lost their houses during the earthquake or the conflict in Syria.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:05:34.025957+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #8 on the Lebanon Emergency Response. All information from 14 October - 17 October 2024, valid as of 17 October 2024 at 12:00 [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-8-lebanon-emergency-response-all-information-14-october-17-october-2024-valid-17-october-2024-1200-enar</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Key Points
+- UNRWA activated its Emergency Response in Lebanon on 24 September. The Agency is currently operating 11 emergency shelters across the country.
+- On 3 October, UNRWA launched a Flash Appeal for US$ 27.3 million to address the urgent humanitarian needs resulting from the ongoing escalation in Lebanon, in addition to the displacement of some populations from Lebanon into Syria, over the next 90 days.
+- The 11 shelters currently operated by UNRWA are located in the following areas: one in Beirut (Yabud School), four in the Saida Area (Siblin Training Centre, Nablus School, Rafidya School, Beir Zeit/Beit Jala School), five in the north (Toubas School, Amqa School, Mount Tabour School, Battir School, and Majeddo and Mazar school - all in Nahr el-Bared Camp), and one in Beqaa (Jarmaq School, in Zahle District).
+- As of 14 October 2024[1], a total of 3,829 Internally Displaced Persons (IDPs) are registered in UNRWA shelters, marking a decrease of 254, or approximately 6.2%, since the last report. Initial reports indicate that some people from the Tyre area have sought to return to the south in recent days.
+- UNRWA is working with a range of partner organisations (community based, local NGOs and international NGOs) in all its emergency shelters to provide a full range of services, including hot meals and psychosocial support activities. In its emergency response, UNRWA has relied on the dedication and commitment of partners on the ground.
+Overall Situation
+- The International Organization for Migration (IOM) reports a total of 779,613 IDPs (52 per cent female and 48 per cent male) as of 16 October 2024. New displacements continue to be reported and recorded.[1]
+- During the reporting period, Israeli Forces’ airstrikes on Beirut's southern suburbs and on villages in southern and eastern Lebanon continued. Casualties are on the rise as Lebanon’s Ministry of Public Health has reported 2,309 deaths and 10,782 injuries,[2] with vulnerable populations the worst affected.
+- According to UNICEF,[3] at least 890 children have been injured and 127 children killed. Moreover, more than 400,000 children in Lebanon have been displaced over the past three weeks.
+- Education institutions in Lebanon remain closed, with the start of the school year postponed to 4 November following an announcement from the Ministry of Education and Higher Education (MEHE).
+- As of 1 October, 1,095 households, representing a total of 3,829 people, are registered in UNRWA emergency shelters across the country. UNRWA is analyzing this decrease in numbers, noting that some IDPs have returned to their homes in Tyre, particularly from shelters in the Saida area. Factors influencing this movement include perceptions of improved safety in southern camps, challenges in adapting to the shelters, and the need to protect livelihoods. This situation requires further monitoring to assess potential protection risks for returnees.</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:05:40.071563+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>UN humanitarian aid convoy reaches Lebanon from Jordan - Lebanon</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/un-humanitarian-aid-convoy-reaches-lebanon-jordan</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>A joint UN convoy including UNRWA has successfully delivered urgently needed aid to Lebanon for the first time since violence escalated there at the end of September.
+UNRWA and partners delivered 72 pallets of food parcels – enough to feed around 2,000 families for a week - plus 40 pallets of hygiene kits to provide essential care to nearly 900 families for a month, and 10 pallets of baby care items and essentials for newborns, such as diapers. The convoy also delivered 8,000 mattresses for displaced people in UNRWA buildings – UNRWA has transformed locations including its schools into emergency shelters for Palestine Refugees, Lebanese, and Syrians.
+“With the growing humanitarian needs of Palestine Refugees and other displaced people in Lebanon, this assistance will provide vital support to people in UNRWA emergency shelters, will help us meet their basic needs, and maintain safety and dignity in their displacement,” said Oliver Bridge, Deputy Director of UNRWA Affairs in Lebanon.
+Olaf Becker, Director of UNRWA Affairs in Jordan, noted how the aid delivery underscores UNRWA’s regional role. "In parallel with supporting Palestine Refugees in Gaza and Lebanon, every day we continue to serve Palestine Refugees in Jordan and across the region. Our commitment remains constant—offering hope amid hardship,” he said.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:05:52.577155+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #7 on the Lebanon Emergency Response. All information from 11 October - 14 October 2024, valid as of 14 October 2024 at 13:00 [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-7-lebanon-emergency-response-all-information-11-october-14-october-2024-valid-14-october-2024-1300-enar</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Key Points
+- UNRWA activated its Emergency Response in Lebanon on 24 September. The Agency is currently operating 11 emergency shelters across the country, several of which are operating at full capacity – with efforts ongoing to expand the capacity to meet expected demand.
+- In addition to the emergency response, UNRWA is working to sustain its regular operations while adapting interventions on an ad hoc basis across its five areas of intervention: South, Saida, Central Lebanon (Beirut), Beqaa, and the North. In Tyre, activities remain suspended, with only minimal water and sanitation services provided. The Saida, Beqaa, and Beirut areas are operating in emergency mode, characterized by limited movement and a focus on life-saving and essential services. In the northern area, operations are fully functional. UNRWA interventions are reviewed daily in response to the evolving security situation and context.
+- On 3 October, UNRWA launched a Flash Appeal for US$ 27.3 million to address the urgent humanitarian needs resulting from the ongoing escalation in Lebanon, in addition to the displacement of some populations from Lebanon into Syria, over the next 90 days.
+- The 11 shelters currently operated by UNRWA are located in the following areas: one in Beirut (Yabud School), four in the Saida Area (Siblin Training Centre, Nablus School, Rafidya School, Beir Zeit/Beit Jala School), five in the north (Toubas School, Amqa School, Mount Tabour School, Battir School, and Majeddo and Mazar school - all in Nahr el-Bared Camp), and one in Beqaa (Jarmaq School, in Zahle District).
+- UNRWA is working with a range of partner organisations (community based, local NGOs and international NGOs) in all of its emergency shelters in order to provide a full range of services, including hot meals and psychosocial support activities. In its emergency response, UNRWA has relied on the dedication and commitment of partners on the ground.
+- As of 14 October 2024, a total of 4,054[1] Internally Displaced Persons (IDPs) are registered in UNRWA shelters.
+- UNRWA Commissioner General Philippe Lazzarini has recently visited Lebanon. During his mission, he attended high level meetings on the ongoing situation in the country, and visited some UNRWA emergency shelters.
+Overall Situation
+- The International Organization for Migration (IOM) reports a total of 746,584 IDPs (52 per cent female and 48 per cent male) between 8 October 2023 and 13 October 2024. New displacements continue to be reported, and counting is ongoing.[1] Displacement surpasses that of the 2006 war, according to OCHA.[2]
+- During the reporting period, Israeli airstrikes on Beirut's southern suburbs and on villages in southern and eastern Lebanon continued at high intensity. Casualties are on the rise as Lebanon’s Ministry of Public Health has reported 2,169 deaths and 10,212 injuries,[3] with vulnerable populations the worst affected.
+- Education institutions in Lebanon remain closed, with the start of the school year postponed to 4 November following an announcement from the Ministry of Education and 111 Higher Education (MEHE). At least 60 per cent of the country’s public schools are currently being used as shelters for the displaced, impacting over 300,000 children’s access to education.
+- As of 1 October, 1,156 households, representing a total of 4,054 people, are registered in UNRWA emergency shelters across the country. Of these, approximately 41 per cent are Palestine Refugees from Lebanon, 20 per cent are Palestine Refugees from Syria, 17 per cent are Lebanese, and 19 per cent are Syrian. Additionally, about 1 per cent are of other nationalities, with less than 1 per cent classified as non-ID or falling into the "others" category.
+[1] IOM Displacement Matrix: Lebanon - Mobility Snapshot - Round 53 - 14-10-2024
+[2] OCHA Flash Appeal: Lebanon, October - December 2024 (October 2024): Flash Appeal: Lebanon, October - December 2024 (October 2024) | OCHA (unocha.org)
+[3] OCHA Flash Update #34 - Escalation of hostilities in Lebanon, as of 10 October 2024: Lebanon: Flash Update #34 - Escalation of hostilities in Lebanon, as of 10 October 2024 - Lebanon | ReliefWeb
+Humanitarian Access, Protection of Civilians
+- Humanitarian access remains severely restricted in the south of the country. A large percentage of the population of the three Palestine Refugee camps in the Tyre area is reported to have left. UNRWA services in these camps have been limited mainly to sanitation and water services. A team of UNRWA health workers managed to reach Rashadieh camp in the Tyre Area on 14 October and distributed critical medications to the remaining population. The same activity was planned for Burj Shemali camp, but it was cancelled due to the security environment.
+- No casualties among UNRWA staff have been reported over the past three days. UNRWA security team closely monitors the situation and staff movements to ensure the safety of frontline workers.
+- No additional damage to UNRWA facilities was reported during the reporting period. Since the onset of the emergency, three facilities — Qastal School in Baalbek (Beqaa) and Mansoura School in Tyre (south), and the Burj Al-Barajneh Health Centre — have sustained minor damage.
+Partnerships
+- UNRWA is currently operating 11 emergency shelters across the country, several of which have now reached maximum capacity, with efforts underway to expand the capacity where feasible.
+- In all areas UNRWA coordinates with local partners to provide additional services to displaced persons. This has been especially important in the initial phase of the emergency response where partners have been instrumental in providing critical services, including hot meals, ready-to-eat parcels, psychosocial activities and protection related services. At each emergency shelter, a co-support partner has been identified. These co-support partners include Nabaa, Tadamon, Beit Atfal El-Somoud, Najdeh, Mobader, and the Arab Resource Center for Popular Arts (ARCPA).
+- UNRWA has made psychosocial support (PSS) and case management services available to all nationalities in the emergency shelters in coordination with co-support partners such as Najdeh, Nabaa, Tadamon, ARCPA, Mobader, and Beit Atfal El Somoud. UNRWA, along with UNICEF and the technical lead partner MAP, has established a psychosocial support response modality where co-support partners address gaps in services and act as primary providers when and where UNRWA staff presence is limited, ensuring continuity of support within the emergency shelters.
+- UNRWA has been coordinating closely with UN Agencies and international organisations, including the IOM, UNICEF and the World Food Programme (WFP), the Norwegian Refugee Council (NRC), Save the Children International (SCI), and Action Against Hunger (ACF).
+UNRWA Shelters
+- On 7 October 2024, UNRWA closed the Deir El Kassi Emergency Shelter near Mieh Mieh Palestine Refugee Camp in Saida. The Agency has been communicating publicly that any infringement on its efforts to maintain humanitarian principles in these shelters cannot be tolerated. In light of this, individuals previously accommodated there have been redirected to alternative emergency shelters.
+Programmatic &amp; Operational Response
+Health
+- The further deterioration of the security situation across the country has impacted UNRWA's health care capacities. As of 14 October, out of 27 UNRWA health centres, 12 are operational and 15 are closed. All health centres in the Tyre area are closed, and two remain open in the Beirut area. In contrast, the situation in the north is more stable, with all centres functioning in both the northern area and the Bekaa Valley.
+- UNRWA health activities were suspended in the Tyre area due to security concerns. Accessing the remaining population in Palestine Refugee camps, including Rashidiyeh, Burj Shemali and Al Buss, presents significant challenges. A team of UNRWA health workers managed to reach Rashadieh camp in the Tyre Area on 14 October and distributed critical medications. The plan was to also conduct the same activity in Burj Shemali camp, but this part of the plan was cancelled due to the security environment. On 24 September, UNRWA activated its Emergency Hospitalization Response to provide treatment for wounded civilians at contracted hospitals. During the reporting period, a total of four emergency hospitalizations were recorded, following airstrikes on Barja village, Saida.
+- The UNRWA Protection team has facilitated the involvement of Women Committees in Nahr el-Bared, Beddawi, and Ein El Hilweh camps, who are supporting food and non-food item (NFI) distributions to internally displaced persons (IDPs) in their areas. The unit is also mapping the presence of these committees and evaluating their capacity to adapt their plans and roles in the emergency context.
+- Over the weekend, UNRWA Protection team and the Relief and Social Services (RSS) team conducted the second round of online sessions focused on community engagement. The target audience included Social Workers (SWs), Area Social Work Supervisors (ASWS), and School Counsellors (SCs). The sessions aimed to discuss practical steps for engaging the community in the emergency shelters management, including identifying respected community members to assist in problem-solving, encouraging community volunteerism in shelter’s functions, ensuring the inclusion of diverse population groups, and fostering positive relationships within the community.
+Sanitation Services/WASH
+- Solid waste management remains a significant challenge across all areas:
+- On 13 October, the UNRWA sanitation team successfully removed garbage from the El Buss camp in cooperation with the municipality of Tyre.
+- In Beirut and the north area, the high volume of waste generated by the camps and UNRWA emergency shelters exceeds UNRWA's capacity. In response, UNRWA has increased waste disposal trips and dedicated staff.
+- In Ein El Hilweh camp, military security restrictions at the entrance limit what can enter, reducing the number of solid waste disposal trips and exacerbating waste accumulation within the camp.
+- In Saida, the municipality has resumed garbage collection, improving the overall situation.
+- UNRWA team is also conducting maintenance and repairs across all 11 emergency shelters, prioritizing WASH utilities, shower units, electrical systems, and other essential services.
+Logistics
+- The security situation continues to affect logistics operations. Movements remain challenging, and the Agency continues to face difficulties in securing trucks and drivers in southern areas to move supplies and for garbage disposal, as many individuals continue to leave to the north.
+- A convoy of seven UNRWA trucks, loaded with food items, mattresses, hygiene kits, and other supplies, has reached the Lebanon border near Arida, in northern Lebanon, and is currently waiting for customs clearance. The supplies will be distributed to UNRWA shelters across the country.
+- Kitchen equipment, including fridges, ovens, and small appliances for the community kitchen to be established in the emergency shelters, has been received and stocked by UNRWA logistics teams across warehouses. These items will be dispatched in the coming days.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:05:58.672123+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>UNRWA Syria response to the influx from Lebanon - UNRWA Situation Report 4 (14 October 2024) [EN/AR] - Syrian Arab Republic</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/syrian-arab-republic/unrwa-syria-response-influx-lebanon-unrwa-situation-report-4-14-october-2024-enar</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>All information from 10 October - 13 October 2024, valid as of 13 October 2024 at 14:00
+Key Points
+- As of 13 October 2024, 481 families (approximately 2,400 individuals) of Palestine Refugees (PR) displaced from Lebanon had approached UNRWA Syria, while the overall estimated number of people displaced from Lebanon was approximately 264,000. UNRWA is making continued efforts to liaise with local authorities to assess and respond to the needs of PR living in hosting centers. The number of PR families in these centers who contact UNRWA directly or through the authorities is increasing.
+- In an effort to assess the needs of the newly arrived Palestine Refugees and to provide much needed support, UNRWA is conducting home visits in coordination with its government counterpart. Additionally, UNRWA has developed a questionnaire, which is implemented country-wide to assess the immediate needs among the new arrivals. All Palestine Refugee arrivals who have registered with UNRWA Syria across the country have been interviewed by UNRWA to assess their needs and intentions. Out of those interviewed:
+  - 98 per cent are in immediate need of NFIs (i.e. mattresses, blankets, clothes etc.)
+  - 98 per cent need food
+  - 91 per cent need hygiene items
+  - 79 per cent need clothes
+  - 36 per cent need items for babies
+Overall Situation
+- UNHCR reported that Syrian immigration continues to admit the displaced populations flexibly; however, Lebanese immigration has resumed an Exit Stamping Protocol, which may slow down the processing of displaced populations at the border or discourage the use of official border crossings.
+- There is an increase in attacks on Syrian Lebanese border crossing points; eight attacks by the Israeli Armed Forces have been recorded, some with significant impact on access to the Syrian territory. Following an Israeli Forces’ airstrike near the Masnaa border crossing point last week, an Israeli forces’ drone attack hit the surroundings of Hawsh al-Sayyid Ali town in South Rural Homs, destroying an informal border crossing bridge on 12 October 2024.
+- UNRWA protection is working to address protection concerns including documentation and to monitor secondary movements. The current trends seem to include an increased number of new arrivals heading towards Northeast Syria where at least 21,000 displaced individuals arrived, while the number of people fleeing Lebanon who crossed through Syria to Jordan according to UNHCR has passed 7,200 individuals.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:06:04.861703+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #6 on the Lebanon Emergency Response. All information from 7 October - 10 October 2024, valid as of 10 October 2024 at 13:00 [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-6-lebanon-emergency-response-all-information-7-october-10-october-2024-valid-10-october-2024-1300-enar</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Key Points
+- At the beginning of October, UNRWA temporarily suspended most of its operations in the Tyre area, primarily because of the displacement of UNRWA staff due to the security situation. Some limited water and sanitation services continue functioning in the area. A large percentage of the population of the three Palestine Refugee camps in the Tyre Area and one camp in Beirut have left in search of safety and protection elsewhere.
+- On 3 October, UNRWA launched a Flash Appeal for US$ 27.3 million to address the urgent humanitarian needs resulting from the ongoing escalation in Lebanon, in addition to the displacement of some populations from Lebanon into Syria, over the next 90 days.
+- Since the activation of its Emergency Response in Lebanon on 24 September, UNRWA has opened 12 emergency shelters. One of the shelters was closed on 7 October, bringing the total number of active emergency shelters down to 11. As of 10 October, three UNRWA emergency shelters have reached their maximum capacity.
+- The 11 shelters currently operated by UNRWA are located in the following areas: one in Beirut (Yabud School), four in the Saida Area (Siblin Training Centre, Nablus School, Rafidya School, Beir Zeit/Beit Jala School), five in the north (Toubas School, Amqa School, Mount Tabour School, Battir School, and Majeddo and Mazar school - all in Nahr el-Bared Camp), and one in Beqaa (Jarmaq School, in Zahle District).
+- As of 10 October 2024, a total of 4,083[1] Internally Displaced Persons (IDPs) are registered in UNRWA shelters. This number has slightly decreased due to the closure of one emergency shelter, as reported in the previous situation report, with ongoing registration of these IDPs in other shelters.
+[1] Cut off time: 10 October 1:00 PM
+Overall Situation
+- The International Organization for Migration (IOM) reports a total of 689,715 IDPs (52 per cent female and 48 per cent male) between 8 October 2023 and 9 October 2024. New displacements continue to be reported, and counting is ongoing.[1] Displacement now surpasses the 2006 war, according to OCHA[2].
+- Education institutions in Lebanon remain closed for learning. The start of the school year has been postponed to 4 November, following an announcement from the Ministry of Education and Higher Education (MEHE). The majority of public schools are currently being used as government-managed collective shelters, with approximately 75% of the 978 government shelters repurposed from public schools.[3]
+- According to WHO[4], at least 96 primary health care centers (PHCCs) and dispensaries, along with three hospitals, have been forced to close due to the conflict, significantly limiting access to critical medical care in surrounding areas. Furthermore, damage has been reported in at least ten hospitals nationwide, with three hospitals fully evacuated and two partially evacuated.
+- The Inter-Agency Standing Committee (IASC) announced a Systemwide Scale-Up on 4 October, for six months. The primary objective of this scale-up is to rapidly mobilize resources and capacities to enhance the emergency response in Lebanon.
+- As of 10 October, 1,162 households, representing a total of 4,083 people, are registered in UNRWA emergency shelters across the country. Of these, approximately 41.2 per cent are Palestine Refugees from Lebanon, 20.5 per cent are Palestine Refugees from Syria, 17.8 per cent are Lebanese, and 18.6 per cent are Syrian. Additionally, about 0.9 per cent are of other nationalities, with less than 1 per cent classified as non-ID or falling into the "others" category.
+[1] IOM Displacement Matrix round 52: Data collected up till 4 pm on 09 October 2024 (not yet online)
+[2] OCHA Flash Appeal: Lebanon, October - December 2024 (October 2024): Flash Appeal: Lebanon, October - December 2024 (October 2024) | OCHA (unocha.org)
+[3] OCHA Flash Update #33 - Escalation of hostilities in Lebanon, as of 7 October 2024: Lebanon: Flash Update #33 - Escalation of hostilities in Lebanon, as of 7 October 2024 - Lebanon | ReliefWeb
+[4] WHO Public Health Situation Analysis (PHSA) (09 October 2024): Escalation of Hostilities in Lebanon, Public Health Situation Analysis (PHSA) (09 October 2024) - Lebanon | ReliefWeb
+Humanitarian Access, Protection of Civilians
+- On 2 October, UNRWA suspended most of its operations in the Tyre area, affecting all three Palestine Refugee camps in the area: Rashidieh, El Buss, and Burj Shemali. Only minimal water and waste management services continue to be provided for the remaining inhabitants in the camps. UNRWA has submitted requests via OCHA to the humanitarian notification system, in order to reopen the UNRWA Primary Health Care clinics in the camps on a limited schedule.
+- In the three Palestine Refugee camps in the Tyre area, basic services such as electricity, water, and food supplies are severely restricted, with food available only in limited quantities from one to two vegetable shops in each camp. Estimates indicate that 25% of the population is in Rashadieh, 20% in Burj Shemali, and 10% in El Buss, with gatherings maintaining around 10%. Bakeries have ceased operations and electricity remains scarce.
+- No casualties among UNRWA staff have been reported over the past three days. UNRWA security team closely monitors the situation and staff movements to ensure the safety of frontline workers.
+- No additional damage to UNRWA facilities was reported during the reporting period. Since the onset of the emergency, three facilities — Qastal School in Baalbek (Beqaa) and Mansoura School in Tyre (south), and the Burj Al-Barajneh Health Centre — have sustained minor damage.
+UNRWA response
+- UNRWA is currently operating 11 emergency shelters across the country, three of which have already reached maximum capacity, namely: Amqa School in Nahr el-Bared Camp, Yabud School in Beirut, and Beit Jala-Beir Zeit School in Saida.
+- Where possible and relevant, UNRWA coordinates with local partners to provide additional services to displaced persons. In its delivery of services, UNRWA has been coordinating closely with UN Agencies and international organisations, including the IOM, UNICEF and the World Food Programme (WFP), the Norwegian Refugee Council (NRC), Save the Children International (SCI), and Action Against Hunger (ACF). At each emergency shelter, a co-support partner has been identified. These co-support partners include Nabaa, Tadamon, Beit Atfal El-Somoud, Najdeh, Mobader, and the Arab Resource Center for Popular Arts (ARCPA).
+- Notably, through the support of partners UNRWA is facilitating the provision of hot meals to IDPs in shelters, with Taawon and the Women Programme Association providing 1,500 meals in Narh el-Bared emergency shelters, Norwegian People’s Aid and the Community Organization for Development and Empowerment (INITIATE) delivering 1,200 daily meals in Siblin emergency shelter, and Save the Children and Nabaa contributing an additional 240 meals. Various community kitchens, including Siyak and Mousawat in the North area and Mosaned in Saida area, along with other local initiatives, are also addressing remaining food needs, while UNRWA is working to finalize community kitchens in the North, Siblin, and Beqaa for sustainable hot meal provision.
+Open UNRWA Emergency Shelter Locations as at 3/10/2024
+UNRWA Shelters
+- On 7 October 2024, UNRWA closed the Deir El Kassi Emergency Shelter near Mieh Mieh Palestine Refugee Camp in Saida. The Agency has been communicating publicly that any infringement on its efforts to maintain humanitarian principles in these shelters cannot be tolerated. In light of this, individuals previously accommodated there have been redirected to alternative emergency shelters.
+Programmatic &amp; Operational Response
+Health
+- The further deterioration of the security situation across the country has impacted UNRWA's health care capacities. As of 10 October, out of 27 UNRWA Health Centres, 12 are operational and 15 are closed. All health centres in the Tyre area are closed, and two remain open in the Beirut area. In contrast, the situation in the north is more stable, with all centres functioning in both the northern area and the Bekaa Valley.
+- With UNRWA health activities suspended in the Tyre area due to security concerns, accessing the remaining population in Palestine Refugee camps, including Rashidiyeh, Burj Shemali and Al Buss, presents significant challenges. Efforts are being made to temporarily open clinics for one or two days; however, the ability to secure health staff remains a concern, as many have relocated to northern areas.
+- The disruption of the national supply chain, marked by a significant reduction in flights to Lebanon and increased dangers for truck transport, has resulted in a situation where, although basic medications are still available, the lack of new shipments may lead to potential shortages, especially for non-communicable diseases and mental health medications. While UNRWA currently has sufficient stock, local procurement may be necessary if the situation continues.
+- In response to the closure of numerous UNRWA health clinics due to security concerns, the newly opened Health Point in central Beirut (Musaytbeh) is now fully operational, with five doctors providing care to patients daily. However, the current physical space is inadequate, and plans are being developed to expand the facility in order to meet the growing demand for services.
+Protection
+- The UNRWA Protection team has completed the Protection Monitoring activity at all operational UNRWA shelters in the north, Saida, Beirut, and Beqaa areas. The team is now addressing gaps related to staff training needs in child safeguarding and prevention of sexual exploitation and abuse (PSEA), while also enhancing activities for children and improving service provision and facilities for individuals with specific needs.
+- The UNRWA Protection Specialists ,in coordination with Education, Health, and Relief and Social Services, oversee psychosocial support (PSS) interventions in emergency shelters. Psychosocial support services are implemented in close coordination with partners in all emergency shelters, and activities (except case management) are open to all nationalities and tailored to age and gender.
+Sanitation Services/WASH
+- Solid waste management presents a significant challenge across all areas. Limited solid waste collection is proceeding in the Tyre area. In Saida, Beirut, and the north, the high volume of waste generated by the camps and UNRWA emergency shelters exceeds UNRWA's capacity. In Ein El Hilweh Camp, military security restrictions at the entrance limit what can enter, reducing the number of solid waste disposal trips and exacerbating waste accumulation within the camp. However, the situation is improving slightly in Saida, as the municipality has resumed garbage collection. In response, UNRWA has increased waste disposal trips and dedicated staff, but additional resources and support are still required.
+- UNRWA team is also permanently conducting maintenance and repairs across all 11 emergency shelters, prioritizing WASH utilities, shower units, electrical systems, and other essential services.
+Logistics
+- A convoy of seven UNRWA trucks, loaded with food items, mattresses, hygiene kits, and other supplies, is en route from Jordan and is expected to reach the Lebanon border near Aarida, in northern Lebanon, by 11 October 2024. The supplies will be distributed to UNRWA shelters across the country.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:06:10.939417+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>UNRWA Syria response to the influx from Lebanon - UNRWA Situation Report 3 (10 October 2024) [EN/AR] - Syrian Arab Republic</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/syrian-arab-republic/unrwa-syria-response-influx-lebanon-unrwa-situation-report-3-10-october-2024-enar</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Situation in numbers
+- Over 400 Palestine Refugee families, or approximately 2,000 people, have reported to UNRWA in various locations (Damascus, Central, North and South areas). The vast majority have come to Damascus and the surrounding rural area. It is believed that the actual number of Palestine Refugee families who have already crossed the border from Lebanon is higher. Most of those arriving are fromfemale headed households and there are high percentages of family separation.
+- They are largelybeing hosted by relatives and friends, while others temporarily occupy abandoned houses in Palestine Refugee camps which have been damaged over the years of crisis in Syria. This support system is believed to be only available for a limited time and extent, and the new arrivals are expected to revert to UNRWA for support.
+- UNRWA is in the process of re-positioning its stock of 825 non-food item (NFI) kits and 533 hygiene kits to the locations with the highest concentration of new arrivals to support these families, who all report needing NFIs.The distribution is scheduled to start next week.
+Funding Requirements
+- UNRWA has launched a Joint Flash Appeal for Syria and Lebanon and requires approximately US$ 1.53 million to respond to the needs of Palestine Refugees fleeing Lebanon in the first three months. Thus far, UNRWA has used its existing programming, budget and human resources to provide protection and services to newly arrived and returning Palestine Refugees who approach the Agency. However, as the number of Palestine Refugees grows, and in view of their dire situation and heightened vulnerabilities, there is an urgent need for additional funding to allow UNRWA to provide adequate assistance and services.
+- The link to the Flash Appeal is here.</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:06:16.994348+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Statement of Philippe Lazzarini, Commissioner-General of UNRWA, at the United Nations Security Council - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/statement-philippe-lazzarini-commissioner-general-unrwa-united-nations-security-council</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Madame la Présidente,
+Excellencies,
+I deeply regret that one year after the abhorrent attacks against Israel, and the catastrophic war on Gaza, no end is in sight to the brutal violence engulfing the region.
+It has been a year of profound loss and suffering.
+A year of dehumanization and barbarism.
+Hostages taken from Israel remain captive, their families left in deep and prolonged distress.
+Gaza is unrecognizable.
+A sea of rubble.
+A graveyard for tens of thousands of people, including far too many children.
+Almost the entire population is displaced.
+People have been forced to flee multiple times, searching for safety that does not exist.
+The latest developments in the north are especially alarming.
+Hundreds of thousands of people are again being pushed to move to the south, where living conditions are intolerable.
+And yet again, Gazans are teetering on the edge of a man-made famine.
+***
+Children in Gaza have not been spared.
+They are killed, injured and orphaned in shocking numbers.
+More than 650,000 children are out of school – deeply traumatized and living in the rubble.
+They have already lost two years of learning.
+Palestinians are no strangers to loss.
+But to be dispossessed from education – which has always been a source of pride – is new.
+We cannot afford to lose an entire generation and sow the seeds for future hatred and extremism.
+That is why UNRWA, beyond its lifesaving operations, has resumed some learning activities in Gaza.
+Every day, we provide psychosocial services to thousands of children.
+We build on these activities to help them read, write, and do some basic arithmetic.
+Bringing children back to learning should be a collective and urgent priority.
+UNRWA has also played a critical role in an emergency vaccination campaign against polio, which has returned to Gaza, 25 years after eradication.
+Together with WHO and UNICEF, UNRWA vaccinated more than half a million children during short pauses in military activities.
+The second round of the campaign is planned for mid-October.
+We hope to succeed again.
+For this we need sufficient political will.
+Madame President,
+Beyond Gaza, the West Bank is gripped by escalating violence.
+Nearly 700 people have been killed in the past year. Among them, more than 160 children.
+Civilian life is increasingly militarized, and settlement activity is expanding aggressively.
+The Israeli Security Forces routinely destroy public infrastructure during military operations, inflicting collective punishment on Palestinians.
+Lebanon is the latest casualty of this widening conflict.
+Civilians are paying a heavy price.
+Air strikes by Israeli forces are killing and injuring thousands, and displacing hundreds of thousands, while Hezbollah continues to attack Israel with rockets.
+UNRWA has opened 11 shelters in Lebanon, hosting more than 4,500 Lebanese, Palestinian and Syrian displaced persons.
+The need for the Agency’s services in Gaza, the occupied West Bank, and Lebanon has never been greater.
+And we have never been under fiercer attack.
+Excellencies,
+The blatant disregard for international humanitarian law, and a near total breakdown of civil order, is crippling the humanitarian response in Gaza.
+Gaza is the most dangerous place in the world for aid workers – 226 UNRWA personnel have been killed in 12 months.
+United Nations premises, including two-thirds of UNRWA’s buildings, have been damaged or destroyed.
+Our premises have also been used for military purposes by Palestinian armed groups, including Hamas, and the Israeli Security Forces.
+Humanitarian aid convoys are looted by armed gangs and obstructed by Israeli soldiers defying their own chain of command.
+Without a lasting ceasefire, the immediate and unconditional release of hostages, and unfettered humanitarian access, the aid operation will collapse, plunging two million people into chaos.
+***
+In the broader occupied Palestinian territory, the Agency’s operational space is shrinking.
+Senior Israeli officials have described destroying UNRWA as a war goal.
+Legislation to end our operations is ready for final adoption by the Israeli Knesset.
+It seeks to ban UNRWA’s presence and operations in the territory of Israel, revoking its privileges and immunities, in violation of international law.
+If the bills are adopted, the consequences will be severe.
+Operationally, the entire humanitarian response in Gaza – which rests on UNRWA’s infrastructure – may disintegrate.
+Coordination with Israel would cease, further disrupting the provision of shelter, food, and healthcare to people in desperate need as winter approaches.
+More than 650,000 children would lose any hope of resuming their education and an entire generation would be sacrificed.
+In the West Bank, the delivery of education, primary healthcare and emergency aid to hundreds of thousands of Palestine Refugees would grind to a halt.
+Legally, the Knesset legislation violates Israel’s obligations under the United Nations Charter and international law.
+It defies the will of the international community expressed through General Assembly resolution 302 on UNRWA, and deepens violations recognized by the International Court of Justice.
+Politically, the anti-UNRWA legislation, which is part of a broader campaign to dismantle the Agency, seeks to strip Palestinians from their refugee status, and change – unilaterally – the parameters for a future political solution.
+Madam President,
+These attacks set a grave precedent for other conflict situations where governments may wish to eliminate an inconvenient United Nations presence.
+They target not just UNRWA, but any individual or entity calling for compliance with international law and a peaceful political solution.
+Failing to push back against attempts to intimidate and undermine the United Nations in the occupied Palestinian territory will eventually compromise humanitarian and human rights work worldwide.
+This Council must decide to which extent it will tolerate acts that strike at the heart of multilateralism and compromise international peace and security.
+The climate of impunity that prevails will not dissipate without decisive action.
+We can uphold the UN Charter and enforce international law, including the Geneva Conventions and the decisions of international courts, without exception.
+Or we can concede that the post-World War II rules-based international order is at an end.
+The devastation of the past year should pull us back from the brink of creating dangerous new norms of warfare and reneging on our decades-long commitment to Palestine Refugees.
+UNRWA is an integral part of the United Nations, which anchors the multilateral system.
+I urge you to shield this UN agency from efforts to end its mandate, arbitrarily and prematurely, in the absence of a long-promised political solution.
+Thank you.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:06:23.037559+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #5 on the Lebanon Emergency Response. All Information from 3 October - 7 October 2024, Valid as of 7 October 2024 at 13:00 [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-5-lebanon-emergency-response-all-information-3-october-7-october-2024-valid-7-october-2024-1300-enar</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Key Points
+- As the armed conflict affecting Lebanon is escalating with increased frequency, intensity and scope of airstrikes, displacement of populations from affected areas continues. As of 7 October 2024, three Palestine refugee camps have been affected by Israeli Forces’ airstrikes: Ein El Hilweh camp close to Sidon, El Bass camp in Tyre and Beddawi camp North of Tripoli.
+- At the start of October, UNRWA temporarily suspended most of its operations in the Tyre area, primarily because of the displacement of UNRWA staff due to the security situation. Some limited water and sanitation services continue in the area. Three Palestine Refugee camps in the South and one camp in Beirut are significantly depopulated as people have fled to seek safety and protection elsewhere.
+- On 3 October, UNRWA launched a Flash Appeal for US$ 27.3 million to address the urgent humanitarian needs resulting from the ongoing escalation in Lebanon, in addition to the displacement of some populations from Lebanon into Syria, over the next 90 days.
+- Since the activation of its Emergency Response in Lebanon on 24 September, UNRWA has opened 12 emergency shelters. One of the shelters was closed on 7 October, bringing the total number of active emergency shelters down to 11. As of 7 October, three UNRWA emergency shelters have reached their maximum capacity.
+- The 11 shelters currently operated by UNRWA are located in the following areas: one in Beirut (Yabud School), four in the Saida Area (Siblin Training Centre, Nablus School, Rafidya School, Beir Zeit/Beit Jala School), five in the North (Toubas School, Amqa School, Mount Tabour School, Battir School, and Majeddo and Mazar school - all in Nahr el-Bared Camp), and one in Beqaa (Jarmaq School, in Zahle District).
+- A total of 4,570 Internally Displaced Persons (IDPs) are registered in UNRWA shelters as of 7 October 2024[1]. This number is expected to continue to increase.
+Overall Situation
+- The International Organization for Migration (IOM) reports a total of 541,527 IDPs (52 per cent female and 48 per cent male) between 8 October 2023 and 2 October 2024. New displacements continue to be reported, and counting is ongoing.[1]
+- More than 690 children have reportedly been injured in Lebanon as the conflict has dramatically escalated in recent weeks. This increase has raised the total number of children with conflict related injuries in Lebanon to 890 in the past year, with many suffering from severe injuries including concussions, shrapnel wounds, and hearing loss due to explosions, according to the latest UNICEF report.[2]
+- The health system has been severely impacted,[3] with 36 reported incidents impacting healthcare facilities between 8 October 2023, and 4 October 2024. According to WHO, at least 77 health workers were killed while on duty, including 28 in a single day on October 2-3 2024. Additionally, 96 primary health care centres and three hospitals have been forced to close, severely limiting access to critical medical care, while at least ten hospitals have sustained damage.
+- Education institutions in Lebanon remain closed for learning. The Minister of Education and High Education (MEHE) has announced the delay of the start of the 2024/25 academic year to 4 November 2024.[4]
+- As of 3 October, 1,312 households, representing a total of 4,570 people, are registered in UNRWA emergency shelters across the country. Of these, approximately 45 per cent are Palestine Refugees from Lebanon, 20 per cent are Palestine Refugees from Syria, 17 per cent are Lebanese, and 16 percent are Syrian. Additionally, about 1 per cent are of other nationalities, with less than 1 per cent classified as non-ID or fall into the "others" category.
+Humanitarian Access, Protection of Civilians
+- On 2 October, UNRWA suspended most of its operations in the Tyre area, affecting all three Palestine Refugee camps: Rashidieh, El Buss, and Burj Shemali. Only minimal water and waste management services continue to be provided for the remaining inhabitants in the camps. UNRWA teams are currently working with OCHA and UNDSS to ensure humanitarian notification of the Primary Health Care clinics to relevant parties to the conflict, aiming to reopen them twice a week to deliver primary health care services to the communities.
+- Intense Israeli Forces’ airstrikes targeted the area of Burj El Barajneh Palestine refugee camp over the past four days, provoking a new wave of displacement from the camp and the surroundings, with current estimates indicating that the population has dwindled to less than 20 per cent of its inhabitants. The camp has sustained material damage affecting private shelters. Sanitary services are operating under challenging conditions, as dumping areas are full and municipal garbage removal has not been conducted.
+- On the morning of 5 October, 2024, Beddawi Palestine refugee Camp in northern Lebanon was hit in an airstrike, resulting in the killing of one person identified as the head of the Hamas military wing (Qassam Brigade) in Lebanon, along with his wife and two daughters.
+- On 5 October, an UNRWA staff member sustained a head injury requiring stitches as a result of an airstrike in the Jiye area. The staff member promptly reported the incident through UNRWA's digital security system, enabling immediate assistance from UNRWA teams. The staff member received treatment at a clinic and is now recovering.
+- On 6 October, the door of the Burj Al-Barajneh Health Centre was damaged due to airstrikes. Due to the deteriorating security situation, UNRWA security team has been unable to conduct comprehensive assessments in areas of high risk, including certain parts of Tyre and the Beqaa Valley. No additional damage to UNRWA facilities was reported during the reporting period. Since the onset of the emergency, three facilities — Qastal School in Baalbek (Beqaa) and Mansoura School in Tyre (South), and the Burj Al-Barajneh clinic — have sustained minor damage.
+UNRWA response
+- UNRWA is currently operating 11 emergency shelters across the country, three of which have already reached maximum capacity, namely: Amqa School in Nahr el-Bared Camp, Yabud School in Beirut, and Beit Jala-Beir Zeit School in Saida.
+- In addition to the community kitchen available at the Siblin Training Centre emergency shelter in Saida, two additional community kitchens are being established in Nahr el-Bared (North) and Beqaa. These kitchens will provide hot meals to IDPs in the vicinity.
+- Where possible and relevant, UNRWA coordinates with local partners to provide additional services to displaced persons. In its delivery of services, UNRWA has been coordinating closely with UN Agencies and international organisations, including the IOM, UNICEF and the World Food Programme (WFP), the Norwegian Refugee Council (NRC), Save the Children International (SCI), and Action Against Hunger (ACF). At each emergency shelter, a co-support partner has been identified. These co-support partners include Nabaa, Tadamon, Beit Atfal El-Somoud, and the Arab Resource Center for Popular Arts (ARCPA).
+- During the reporting period, the Palestine Red Crescent Society (PRCS) supported UNRWA emergency shelters through the provision of 700 psychosocial support (PSS) kits, which included items such as pencils, rubber erasers, colouring books, and toys. Activities were also offered to help children aged eight to 12 relieve stress and develop positive coping mechanisms.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:06:29.116888+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>UNRWA Syria response to the influx from Lebanon - UNRWA Situation Report 2 (6 October 2024) [EN/AR] - Syrian Arab Republic</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/syrian-arab-republic/unrwa-syria-response-influx-lebanon-unrwa-situation-report-2-6-october-2024-enar</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Situation in numbers
+- 300 Palestine refugee families (approximately 1500 individuals have reported at UNRWA in various locations (Damascus, Central, North and South areas).
+- Relatives and friends are currently hosting most of these 300 families. UNRWA through a protection referral to Syrian Arab Red Crescent (SARC) ensured emergency transport for two PRL families from the South areas to a hosting center in Damascus and a few more cases of PRL families in hosting centres have become known to UNRWA, especially in the Central Areas.
+- UNRWA has a stock of only 825 non food items kits and 533 hygiene kits, which are being repositioned to the locations with the higher concentration of new arrivals to support the families who all report needing NFIs.
+Funding Requirements
+UNRWA Syria has launched a Joint Flash Appeal with UNRWA Lebanon and requires approximately US$ 1.53 Million to respond to the needs of the Palestine Refugees. Find the Flash Appeal here. UNRWA requires US$ 1.53 Million to meet the humanitarian needs of Palestine refugees fleeing Lebanon in the first three months. Thus far, UNRWA has made use of its existing programming, budget and human resources to provide protection and services to those of the newly arrived and returning Palestine Refugees who approach UNRWA. However, as the number of Palestine refugees is growing and in view of their dire situation and heightened vulnerabilities, there is an urgent need for additional funding to allow UNRWA to provide adequate assistance and services.
+Situation Overview
+- Since the escalation of the hostilities in Lebanon, approximately 220,000 people are believed to have crossed the border to Syria through both official and unofficial border crossing points. This population consists of Syrians, Lebanese, Palestine Refugees and Third Country Nationals (TCN). Available data does not provide a breakdown per nationality.
+- Two categories of Palestine Refugees are being displaced, Palestine Refugees in Lebanon (PRL), consisting of those originally registered in Lebanon, and Palestine Refugees from Syria (PRS) who fled to Lebanon because of the crisis in Syria.
+- Approximately 100 families of both categories are reported to have arrived in Palestine refugee camps in Syria during the last three days in addition to the 200 that were known to UNRWA as of the end of last week. In discussions between UNRWA and PRS displaced from Lebanon, they have indicated that they have relatives who are trying to reach Syria, an indication that the number will keep rising rapidly. It is estimated that several hundreds more have arrived in Syria and more will continue to arrive as the situation deteriorates in Lebanon. The majority are currently being hosted by relatives and friends.
+- The Government of Syria is practicing an open-door policy at the border, facilitating entry without stamping the documents in many instances or even for those without documents. They also provide freedom of movement once they arrive in the country. UNRWA is in contact with UNHCR and SARC to stay abreast of developments regarding internal and secondary movements, especially through Syria towards Jordan.
+- The government has extended for an additional ten days the exemption to the application of Cabinet Decision no. 46 of April 2021 requiring the exchange of the equivalent of US$100 at the borders before entering of Syrian returnees (including PRS).
+- The arrivals through the Jdaidet Yabous border point have been low since 4 October, when Israeli Forces airstrikes caused a crater on the road to the border crossing point. Many forcibly displaced people from Lebanon are taking longer routes to avoid this crossing point and others cross the crater on foot. UNHCR and SARC provide transportation services to the extremely vulnerable new arrivals from the crater caused by the airstrikes (Masnaa area) to the border crossing point on the Syria side.
+UNRWA Response overview
+Palestinian Refugees in Lebanon and Palestine Refugees from Syria were already among the most impoverished and marginalized due to protracted displacement, multiple displacement, their uncertain legal status, and limited social protection mechanisms while in Lebanon, which made them heavily reliant on UNRWA for their basic needs. Before the escalation in Lebanon, they were already facing a desperate socio-economic situation characterised by very high rates of poverty and unemployment, driven largely by systemic discrimination over generations, and the social and economic inequalities they experience. They were excluded from several Lebanese syndicate-regulated professions, other forms of formal employment, and public services leaving the majority unable to provide for their basic needs and leading to a near-total dependency on UNRWA’s assistance. PRS returning to Syria from Lebanon, are returning into their protracted displacement, and PRL are exchanging one displacement for another, both with depleted abilities to cope.
+UNRWA will transport 825 NFI kits and 553 hygiene kits to areas of influx before the end of the week for immediate distribution to the displaced refugees as part of the immediate first-line response.
+The Agency’s response is currently integrated into the existing programming and all Palestine refugees are accessing services at various UNRWA installations, such as services at health centres and admission in schools. In addition, a flash appeal has been launched with a planning figure of 1,000 families (approximately 5,000) individuals. This flash appeal is part of the Agency’s Lebanon regional appeal as well as the Syria inter-agency appeal which was launched on the 4th of October 2024. UNRWA plans to respond to the needs of the refugees in multiple ways listed below. The flash appeal has the following components reflecting the current needs;
+Multipurpose Cash Assistance &amp; Food Security
+The transfer values to be utilized will be in line with the Inter-agency Cash Working Group recommendations as well as sector standards from the NFI cluster.
+Shelter &amp; Non-Food Items (NFIs)
+The situation of the Palestine Refugees displaced by the hostilities in Lebanon is extremely dire with many of them arriving with little or no belongings. UNRWA currently has only 825 NFI kits in its warehouse, these kits are being re-positioned to the different area offices to aid in emergency response.
+Emergency health
+UNRWA will continue to provide all health services to newly arrived PRS and PRL from Lebanon, leading to increased overall costs. Several newly arrived Palestine Refugees with disabilities have approached UNRWA health clinics requesting for assistive devices and UNRWA is trying to urgently support them. MHPSS will also be provided at UNRWA Health clinics and at the communal hosting centres.
+Education in Emergencies
+PRS and PRL children are being registered in UNRWA schools and MHPSS services are being provided to ensure continued learning, limit education loss, and address psychological trauma. Many newly arrive children lack documentation, including proof of their education level in Lebanon and UNRWA education team is looking into adjusting its procedures to ensure that children can be swifty integrated into its schools.
+Protection and Social services
+Registration services and safe referrals will be provided. Protection monitoring will allow UNRWA to quickly address protection concerns that arise. Case management and social work interventions will focus on highrisk cases and legal aid especially to address civil documentation issues. Access to documentation, including IDs, family statement and education certificates is one of the urgent needs underlined by the Palestine refugees arriving at UNRWA offices. Awareness will be raised on the Protection from Sexual Exploitation and Abuse and gender-based violence among beneficiaries and staff in government hosting centres and via UNRWA Community Centres. The Agency will also extend cash for protection, while persons with disabilities will be provided with assistive devices.
+Transitional Shelter Assistance
+While the majority of Palestine Refugees arriving from Lebanon are currently hosted by extended family and other members of the host community, others report require emergency shelter. UNRWA has referred at least two PRL families to the government run hosting centers. Many PRS’ houses were totally destroyed and rendered uninhabitable. They plus the PRL will constitute a heavy burden on relatives and friends currently hosting them. UNRWA will provide cash for rent to most vulnerable families to allow them to be integrated in the Syrian society and to avoid creating dependency.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:06:35.178392+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>UNRWA Syria response to the influx from Lebanon - UNRWA Situation Report 1 (4 October 2024) [EN/AR] - Syrian Arab Republic</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/syrian-arab-republic/unrwa-syria-response-influx-lebanon-unrwa-situation-report-1-4-october-2024-enar</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Situation in numbers
+- 200 Palestine Refugee families, approximately 1,000 individuals have reported to UNRWA installations and have registered with UNRWA in various locations (Damascus, Central, &amp; South areas).
+- Relatives and friends are currently hosting all 200 families. None is staying at the governmentdesignated hosting centres.
+- UNRWA has only 825 NFI Kits which are being re-positioned to the locations of influx to support the emergency response.
+Funding Requirements
+- UNRWA Syria has launched a Joint Flash Appeal with UNRWA Lebanon and requires approximately US$ 1.53 Million to respond to the needs of the Palestine Refugees. Find the Flash Appeal here. UNRWA requires US$ 1.53 Million to meet the humanitarian needs of Palestine refugees fleeing Lebanon in the first three months. Thus far, UNRWA has made use of its existing programming, budget and human resources to provide protection and services to those of the newly arrived and returning Palestine refugees who approach UNRWA. However, as the number of Palestine refugees is growing and in view of their dire situation and heightened vulnerabilities, there is an urgent need for additional funding to allow UNRWA to provide adequate assistance and services.
+Situation Overview
+- Since the escalation of the hostilities in Lebanon, approximately 185,000 people are believed to have crossed the border to Syria through both official and unofficial border crossing points. This population consists of Syrians, Lebanese, Palestine Refugees and Third Country Nationals (TCN). Available data does not provide a breakdown per nationality.
+- Two categories of Palestine Refugees are being displaced, Palestine refugees in Lebanon (PRL), consisting of those originally registered in Lebanon, and Palestine Refugees from Syria (PRS) who fled to Lebanon because of the conflict in Syria (in 2011 onwards).
+- Approximately 200 families of both categories are reported to have arrived in Palestine refugee camps in Syria. It is estimated that several hundreds more have arrived in Syria and more will continue to arrive as the situation deteriorates in Lebanon. The majority are currently being hosted by relatives and friends.
+- The Government of Syria is practicing an open-door policy at the border, facilitating entry without stamping the documents in many instances or even for those without documents. They also provide freedom of movement once they arrive in the country.
+- The government also issued a one-week exemption of Syrian returnees (including PRS) from the application of Cabinet Decision no. 46 of April 2021 requiring the exchange of the equivalent of US$100 at the borders before entering.
+UNRWA Response overview
+- Palestine Refugees were already among the most impoverished and marginalized due to protracted displacement, multiple displacement, their uncertain legal status, and limited social protection mechanisms while in Lebanon, which made them heavily reliant on UNRWA for their basic needs. Before the escalation in Lebanon, they were already facing a desperate socio-economic situation characterised by very high rates of poverty and unemployment, driven largely by systemic discrimination over generations, and the social and economic inequalities they experience. They were excluded from several Lebanese syndicate-regulated professions, other forms of formal employment, and public services leaving
+- the majority unable to provide for their basic needs and leading to a near-total dependency on UNRWA’s assistance. PRS returning to Syria from Lebanon, are returning into their protracted displacement, and PRL are exchanging one displacement for another, both with depleted abilities to cope.
+- The Agency’s response is currently integrated into the existing programming and all Palestine Refugees are accessing services in UNRWA installations, such as services at health centres and admission in schools. In addition, a flash appeal has been developed with an initial planning figure of 1,000 families (approximately 5,000) individuals. This Flash Appeal is part of the Agency’s Lebanon regional appeal.
+Multipurpose Cash Assistance &amp; Food Security
+The transfer values to be utilized will be in line with the inter-agency Cash Working Group recommendations as well as sector standards from the NFI cluster.
+Shelter &amp; Non-Food Items (NFIs)
+The situation of the Palestine Refugees displaced by the hostilities in Lebanon is extremely dire with many of them arriving with little or no belongings. UNRWA currently has only 825 NFI kits in its warehouse, these kits are being re-positioned to the different area offices to aid in emergency response.
+Emergency health
+UNRWA will continue to provide all health services to newly arrived PRS and PRL from Lebanon, leading to increased overall costs. MHPSS will also be provided at UNRWA Health clinics and at the communal hosting centres.
+Education in Emergencies
+PRS and PRL children are being registered in UNRWA schools and MHPSS services are being provided to ensure continued learning, limit education loss, and address psychological trauma.
+Protection and Social services
+Registration services and safe referrals will be provided. Protection monitoring will allow UNRWA to quickly address protection concerns that arise. Case management and social work interventions will focus on high-risk cases and legal aid especially to address civil documentation issues. Awareness will be raised on the Protection from Sexual Exploitation and Abuse and gender-based violence among beneficiaries and staff in government hosting centres and via UNRWA Multipurpose Community Centres. The Agency will also extend cash for protection, while persons with disabilities will be provided with assistive devices.
+Transitional Shelter Assistance
+While the majority of Palestine Refugees arriving from Lebanon are currently hosted by extended family and other members of the host community, others report require emergency shelter. Many PRS’ houses were totally destroyed and rendered uninhabitable. They plus the PRL will constitute a heavy burden on relatives and friends currently hosting them. NRWA will provide cash for rent to most vulnerable families to allow them to be integrated in the Syrian society and to avoid creating dependency.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:06:41.963885+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Message from UNRWA Commissioner General Philippe Lazzarini - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/message-unrwa-commissioner-general-philippe-lazzarini</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>07 October 2024
+From Philippe Lazzarini, the UNRWA Commissioner-General as posted on his official X account (previously known as Twitter)
+One year on the horrendous massacre carried out by Hamas and other Palestinian armed groups on southern Israel, killing more than 1,250 people and taking 250 hostages.
+Since that day, the Middle East is sinking deeper into conflict, killing and sheer horrors.
+Twelve months of unspeakable suffering for the hostages in Gaza, their families left in limbo and a society deeply traumatized.
+Twelve months of brutal war have transformed the Gaza Strip into an unrecognizable sea of rubble, and a graveyard for tens of thousands of people, among them far too many children.
+One year has passed and not a day goes by without families in Gaza being subjected to unspeakable suffering, as forced displacement, disease, hunger, and death have become the daily norm for 2 million people trapped in a bombed- out and besieged enclave.
+A year of profound loss, grief and suffering.
+A year of dehumanization and disregard of international law; a free fall descent into barbarism.
+In Gaza, civilians continue to bear the brunt of the war. More than 220 UNRWA team members have been killed: the highest death toll in the history of the United Nations.
+Children have been the first and most to suffer. Beyond the killing and injury, every child in Gaza is traumatized many with life-long invisible scars. More than 650,000 children are losing another year of learning. Instead of being in classrooms, they are sifting through the rubble in despair and fear.
+The destruction of essential infrastructure has reached catastrophic levels.
+More than two thirds of UNRWA buildings have been hit and deemed unusable, the vast majority while sheltering displaced people under the UN flag.
+In the West Bank, civilians continued to endure destruction, fear and anxiety amid an escalation and increase in operations by the Israeli military and clashes with Palestinian armed groups. Poverty is deepening as people lose income and as movement restrictions are reinforced.
+The expansion of the war into Lebanon is wreaking havoc on civilians, many forced to relive traumas of the past.
+It is time for courage: a deal that would finally bring a ceasefire and respite to people in Gaza, Lebanon, Israel and the wider region.
+It is time to put the guns down after decades of killing and immense pain.
+It is time to release all hostages safely to their families, who are living through unbearable uncertainty.
+It is time to bring a standard flow of basic humanitarian supplies including to the hungry and sick in Gaza.
+There are no winners in wars. The only way out is through a diplomatic and peaceful solution.
+It’s time to heal the wounds. It’s time to choose peace!
+Background Information:
+UNRWA is the United Nations Relief and Works Agency for Palestine Refugees in the Near East. The United Nations General Assembly established UNRWA in 1949 with a mandate to provide humanitarian assistance and protection to registered Palestine refugees in the Agency’s area of operations pending a just and lasting solution to their plight.
+UNRWA operates in the West Bank, including East Jerusalem, The Gaza Strip, Jordan, Lebanon and Syria.
+Tens of thousands of Palestine refugees who lost their homes and livelihoods due to the 1948 conflict continue to be displaced and in need of support, nearly 75 years on.
+UNRWA helps Palestine Refugees achieve their full potential in human development through quality services it provides in education, health care, relief and social services, protection, camp infrastructure and improvement, microfinance, and emergency assistance. UNRWA is funded almost entirely by voluntary contributions.
+Your support is crucial to help us provide emergency aidto displaced families in Gaza</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:06:48.150293+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #4 on the Lebanon Emergency Response. All Information from 30 September - 3 October 2024, Valid as of 3 October 2024 at 14:00 [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-4-lebanon-emergency-response-all-information-30-september-3-october-2024-valid-3-october-2024-1400-enar</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Key Points
+- For the second consecutive week, airstrikes across the country have driven further displacement. Over the reporting period, airstrikes have expanded affecting wider areas, including central Beirut and Palestine Refugee camps.
+- At the start of October, UNRWA temporarily suspended most of its operations in the Tyre area, primarily because of the displacement of UNRWA staff due to the security situation.
+- Since the activation of its Emergency Response in Lebanon on 24 September, UNRWA has opened 12 emergency shelters. As of 3 October, three UNRWA emergency shelters have reached their maximum capacity.
+- The 12 shelters operated by UNRWA are located in the following areas: one in Beirut (Yabud School), five in the Saida Area (Siblin Training Centre, Nablus School, Rafidya School, Beir Zeit/Beit Jala School, and Deir Qasi school), five in the North (Toubas School, Amqa School, Mount Tabour School, Battir School, and Majeddo and Mazar school, all in Nahr el-Bared Camp), and one in Beqaa (Jarmaq School, in Zahle District).
+- A total of 4,250 Internally Displaced Persons (IDPs) have registered in UNRWA shelters as of 3 October[1], marking an 82 per cent increase from the 2,332 people registered in UNRWA shelters as of 30 September. This number is expected to continue to rise.
+[1] Data cut off time: 3 October 14:00
+Overall Situation
+- As of 1 October 2024, at least 1,745 people have been killed and 8,767 injured in Lebanon since October 2023 according to UNHCR, citing figures from the Ministry of Public Health.[2]
+- According to OCHA, Lebanese national authorities estimate that over 1 million people are now directly affected and/or displaced by the conflict. The International Organization for Migration (IOM) reports a total of 346,209 people (52 per cent female and 48 per cent male) being displaced between 8 October 2023 and 29 September 2024, with new displacements continuing to be reported and counting still ongoing[3].
+- Since 8 October 2023, six hospitals in Baalbek, Nabatieh, and southern Lebanon have been reported damaged, while approximately 40 out of 317 primary health centers and two hospitals have suspended services.
+- On 1 October, the Lebanese Prime Minister and the United Nations Humanitarian Coordinator for Lebanon jointly launched a Flash Appeal calling for US$ 425.7 million to address the urgent needs of 1 million people affected by displacement and the escalating conflict in the country, aiming to provide life-saving assistance and ensure the protection of civilians and essential services.
+- The number of public facilities serving as emergency shelters across the country has risen to over 875[4], primarily comprising public schools, educational complexes, vocational institutes, and agricultural centres. People are being directed to these shelters through governorate operations rooms, via designated hotlines. At the time of writing, 625 (71 per cent) of these facilities have reached maximum capacity.
+- Educational institutions in Lebanon remain closed for learning.
+- As of 1 October, approximately 177,000 Syrian and 63,000 Lebanese nationals had crossed into Syria to escape the conflict, according to the national authorities in Syria.[5]
+- As of 3 October[6], 1,285 households, representing a total of 4,250 people, are registered in UNRWA emergency shelters across the country, marking an increase of 82 per cent since the last report of 30 September. Of these, 66 per cent are Palestinian, 16 per cent are Syrian, and 18 per cent are Lebanese. Among the Palestinian population, 70 per cent are Palestine Refugees from Lebanon (PRL) and 30 per cent are Palestine Refugees from Syria (PRS).
+[2] UNHCR Lebanon Emergency Flash Update (1 October 2024)
+[3] OCHA Lebanon: Flash Update #31 - Escalation of hostilities in Lebanon, as of 1 October 2024 - 10:00 p.m: Lebanon: Flash Update #31 - Escalation of hostilities in Lebanon, as of 1 October 2024 - 10:00 p.m. - Lebanon | ReliefWeb
+[4] Ibid
+[5] Flash Update #31 - Escalation of hostilities in Lebanon, as of 1 October 2024 - 10:00 p.m: Lebanon: Flash Update #31 - Escalation of hostilities in Lebanon, as of 1 October 2024 - 10:00 p.m. - Lebanon | ReliefWeb
+[6] Cut off date: 3 October 15:00
+Humanitarian Access, Protection of Civilians
+- On 2 October, Israel authorities issued evacuation orders for residents of multiple locations in South Lebanon, both Burj Shemali and Rashadieh were mentioned in the order. This prompted many people, including Palestinians residing in the nearby camps and UNRWA staff, to leave to the Saida area and further north. Further to this displacement, UNRWA has suspended its operations in the Tyre area until further notice, affecting all three Palestine Refugee camps in the region: Rashidieh, El Buss, and Burj Shemali. It has been reported that only 25 per cent of the usual population remains in Rashidieh, only 50 per cent in Bourj Shemali, while El Buss is almost empty. These three camps usually host 20,000 people.
+- On 1 October, an airstrike reportedly targeted the house of Fatah leader Munir Makdah in Ein el-Hilweh Camp, resulting in eight reported fatalities. There is no confirmed information regarding Makdah's current status. UNRWA suspended operations in the camp on the day of the attack and resumed the following day.
+- In the reporting period, no additional damage to UNRWA facilities was reported. Since the onset of the emergency response, two facilities — Qastal School in Baalbek (Beqaa) and Mansoura School in Tyre (South) — have sustained minor damage, as previously reported.
+UNRWA response
+- Since announcing the activation of its Emergency Response on 24 September, UNRWA has opened 12 emergency shelters across the country, three of which have already reached maximum capacity, namely: Amqa School in Nahr el-Bared Camp Yabud School in Beirut, and Beit Jala-Beir Zeit School in Saida.
+- To increase shelter capacity, two additional shelters have now been prepared to accommodate IDPs: Manara School emergency shelter in Nahr el-Bared Camp, North Lebanon Area, with a capacity of 820 IDPs, and Sakhra School emergency shelter near Mieh Mieh camp, Saida area, with a capacity of 750 IDPs.
+- The rapidly increasing demand is exerting pressure on the emergency response, requiring additional staff for maintenance, security, and service provision. To enhance efficiency in addressing urgent needs, where possible UNRWA is reallocating regular staff to emergency operations.
+- However, additional funding is necessary, and UNRWA has launched a Flash Appeal for the emergency response.
+- Where possible and relevant, UNRWA coordinates with local partners to provide additional services to displaced persons. In its delivery of services, UNRWA has been coordinating closely with UN Agencies and international organisations including the IOM, UNICEF and the World Food Programme (WFP), and with international NGOs including the Norwegian Refugee Council (NRC) Save the Children International (SCI), and Action Against Hunger (ACF). At each emergency shelter, a co-support partner has been identified - these include Nabaa, Tadamon, Beit Atfal El-Somoud, and Arab Resource Center for Popular Arts (ARCPA).
+UNRWA Shelters
+- Toubas School (North)
+Toubas School emergency shelter opened on 24 September, with a capacity of 774 IDPs. This shelter is located within the Nahr el-Bared Camp in northern Lebanon. Psychosocial Support (PSS) and recreational activities are being implemented by a local partner, the Al Somoud Association. Currently, 114 families with 429 people have been registered in the shelter.
+- Amqa School (North)
+Amqa School emergency shelter opened on 27 September. The shelter is located in Nahr el-Bared camp and is prepared to receive up to 396 IDPs. Currently, 107 families with 412 people have been registered in the shelter. The shelter is now full and cannot receive any further IDPs.
+- Battir School (North)
+Battir School emergency shelter opened on the night of 29-30 September. The shelter is located in Nahr el-Bared camp and is prepared to receive up to 828 IDPs. Currently, 120 families with 404 people have been registered in the shelter.
+- Mount Tabour School (North)
+Mount Tabour school emergency shelter opened on 28 September. The shelter is located in Nahr el-Bared camp and is equipped to receive up to 161 IDPs. Currently, 133 families with 440 people have been registered in the shelter. The shelter is now full and cannot receive any further IDPs.
+- Majeddo and Mazar School (North) / New
+Majeddo and Mazar School emergency shelter opened on 2 October. The shelter is located in Nahr el-Bared. The shelter is equipped to accommodate up to 720 IDPs. Registration of IDPs has started but registration figures are not yet available.
+- Yabud School (Beirut)
+Yabud School emergency shelter opened on 29 September replacing Bir Hassan Shelter in order to offer increased capacity. It is equipped to accommodate up to 150 IDPs. Given the limited capacity of Yabud School emergency shelter and the increasing demand, UNRWA is referring IDPs to shelters located in the northern area. Currently, 58 families with 182 people have been registered in the shelter. The shelter is now full and cannot receive any further IDPs.
+- Siblin Training Centre (South)
+Siblin emergency shelter opened to IDPs on 24 September. This shelter, located in the Saida area, can to receive 1,400 IDPs with the possibility of significantly increasing its intake capacity. Currently, 200 families with 657 people have been registered in the shelter.
+- Nablus School (South)
+In response to a request from the Municipality of Saida, on the 25 September, UNRWA opened Nablus School emergency shelter to accommodate IDPs from the South. The school has the capacity to accommodate between 300 and 400 people. Currently, 77 families with 236 people have been registered in the shelter.
+- Rafidya School (South)
+Rafidya School emergency shelter opened on 26 September. The shelter is in Saida city and is prepared to receive up to 250 IDPs. Currently, 66 families, with 231 people, have been registered in the shelter.
+- Beir Zeit – Beit Jala School (South)
+Beir Zeit - Beit Jala School emergency shelter opened on the afternoon of 28 September. These two schools are inthe same compound in the northern Saida area, midway to Beirut. The shelter is fully equipped to accommodate up to 684 IPDs. Currently, 236 Families with 743 people have been registered in the shelter. The shelter is now full and cannot receive any further IDPs.
+- Deir Qasi School (South) / New
+Deir Qasi School emergency shelter opened on 1 October. The shelter is located in Mieh Mieh refugee camp, in the Saida area. The shelter is equipped to accommodate up to 480 IDPS. Currently, 108 families with 371 people have been registered in the shelter.
+- Jarmak School (Beqaa)
+Jarmak School emergency shelter, located in Saddnayel village (Zahle District), opened on 27 September. A community kitchen is being established at this shelter to enable displaced people to cook their own meals. The shelter can accommodate up to 468 people. Currently, 66 families, with 145 people, have been registered in the shelter.
+Programmatic &amp; Operational Response
+Health
+- The further deterioration of the security situation across the country has impacted UNRWA's health capacities. As of this report, out of 27 UNRWA Health Centres, 12 are operational and 15 are closed, with all centres in the Tyre area closed, and two remaining open in Beirut area. In contrast, the situation in the north is more stable, with all centres functioning in both the North area and Bekaa.
+- To provide health services to refugees in Beirut, a new emergency Health Centre has been opened in the Museytbeh neighborhood, operating out of an UNRWA Relief and Social Services Office to address the growing needs of the population and IDPs in the capital. The UNRWA central pharmacy is currently transferring stock of essential medications to this newly established centre.
+- On 24 September, UNRWA activated its Emergency Hospitalization Response on, covering the treatment of wounded civilians at contracted hospitals. Over the reporting period, there have been 11 emergency hospitalizations: six patients in Saida (all still admitted since 29 September), three patients in Tyre (all discharged), one patient in Beqaa (discharged), and one patient in the North area (discharged); no patients have been admitted in the Central Lebanon Area since the beginning of the conflict.
+Protection
+- During a funeral held in Nahr el-Bared Camp, a shooting in the air resulted in injuries and one fatality, contributing to heightened tensions in the area.
+- The UNRWA Protection team has begun conducting protection assessments in emergency shelters. On 2 October, the Legal Focal Point in the North Lebanon Area delivered an awareness-raising session on legal aid services.
+- In recent days, the UNRWA Protection team has actively engaged in external coordination, participating in various meetings to enhance collaboration and share best practices. Discussions included rights and challenges for Palestine Refugees from Syria wishing to return to Syria, as well as participation in the Emergency Protection Core Group and Child Protection Working Group meetings.
+Sanitation Services/WASH
+- The influx of IDPs into Nahr el-Bared has exacerbated water shortages in the camp and has led to a significant increase in solid waste generation within the camp. In response, the operating hours of water treatment plants have been extended; however, there is an urgent need for additional fuel to sustain these extended operations and to facilitate increased trips for the disposal of the accumulating solid waste.
+- Water scarcity is also a concern at the Yabud shelter in Beirut, due to the influx of IDPs. UNRWA is increasing the number of trucks delivering water to the shelter.
+Logistics
+- The security situation continues to impact on logistics operations. Movements remain challenging, and the Agency continues to face difficulties in securing trucks and drivers in southern areas to move supplies and for garbage disposal, as many individuals continue to leave to the north.
+- UNRWA's Procurement and Logistics Department consistently monitors stock levels and identifies gaps to plan the transportation of goods accordingly. During the reporting period, UNRWA transported 1,250 blankets from Beirut to shelters in the north.
+- To ensure the proper functioning of shelters and address the issue of continuous generator operation, UNRWA has transported and installed five backup generators for the Nablus, Rafidia, Battir, Majeddo, and Mazzar shelters.
+Quote from Latifa, displaced Palestine Refugee in Lebanon:
+“We were seven people in the car, on top of one another along with the children. The traffic was jammed and there was bombing all the way.”
+ENDS
+FOR MORE INFORMATION, PLEASE CONTACT:
+Global Media Requests
+WhatsApp: +962-7-9130-0567
+Japanese Media Requests
+WhatsApp: +972 54-240-2727
+European Media Requests
+English/French/Spanish:
+WhatsApp: +32473822006
+Email:media@unrwa.org</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:06:54.314194+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Lebanon Crisis Flash Appeal supporting the immediate emergency response in Lebanon and Syria October – December 2024 - Lebanon</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/lebanon-crisis-flash-appeal-supporting-immediate-emergency-response-lebanon-and-syria-october-december-2024</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Introduction
+In response to the ongoing escalation in Lebanon and the mass arrival of displaced people to Syria from Lebanon, UNRWA urgently seeks US$ 27.3 million for its humanitarian response over the coming 90 days. These funds are urgently needed to address the immediate needs for food, non-food items (NFIs), health services, shelter and protection for up to 10,000 individuals seeking safety in UNRWA-managed shelters in Lebanon and up to 5,000 Palestine refugees fleeing the conflict into Syria. In providing assistance, the Agency will ensure that attention is focused on serving the needs of specific vulnerable groups, including women, children, persons with disabilities and the elderly.
+All Lebanon-specific interventions in the present Appeal are: (i) integrated into the Inter-Agency Flash Appeal – Lebanon; and (ii) unless explicitly specified otherwise, are in addition to those included in the 2024 UNRWA Emergency Appeal for Syria, Lebanon and Jordan. Furthermore, all Syria-specific interventions are expected to be fully integrated into the Syria Inter- Agency Flash Appeal, the coordination of which has just commenced.
+The response in this Appeal can only be implemented if UNRWA also receives the necessary funding for its Programme Budget, which serves as the foundation for all Agency service provision in Lebanon and other fields of UNRWA operation.
+Lebanon: context and needs
+As a result of cross-border hostilities between Israel and Hezbollah, 211,319 persons, including 74,000 children, have been internally displaced in Lebanon since October 2023 up to 25 September 2024, with further displacement anticipated. Some 56 percent of the total number (118,466 individuals) have been displaced during the past week alone, due to a major escalation in the hostilities taking place in Lebanon, including between forces on the ground from 1 October 2024.3 Education institutions in the country have closed, with classes suspended for 340,000 students until the situation allows for a safe return to learning.4 Due to the arrival of displaced Palestine refugees from southern Lebanon seeking shelter in safer areas,5 UNRWA activated its emergency response. By 2 October, the Agency had opened twelve emergency shelters6 , providing the displaced with ready-to-eat meals, water, mattresses, pillows and other basic necessities. Based on humanitarian principles and in support of social cohesion, UNRWA emergency shelters are open to all persons in need. As of 2 October, 4,000 individuals were registered in UNRWA-managed shelters, with numbers expected to steadily increase. Fifty per cent of those registered are Palestine refugees, 25 per cent are nationals of Lebanon and 25 per cent are Syrian refugees. This Flash Appeal outlines the budgetary needs to address the emergency needs (food, cash, shelter, NFI, health, protection, psychosocial support and water, sanitation, hygiene [WASH]) for up to 10,000 newly displaced individuals in UNRWA shelters, with due focus on vulnerable groups. As the situation continues to deteriorate, the response to the especially vulnerable Palestinian refugees from Syria (PRS)7 in Lebanon will need to be scaled up within and outside of emergency shelters. The Appeal will be revised, as necessary.
+Syria: context and needs
+The influx of approximately 128,000 people from Lebanon to Syria (as at 30 September), driven by escalating hostilities in Lebanon since 23 September, has significantly increased humanitarian needs in the country. The incoming population includes Lebanese nationals, returning Syrian nationals and Palestine refugees; half are children and many are vulnerable, including women, persons with disabilities and the elderly. New arrivals are placing a significant strain on host communities, including those in Homs, Hama, Latakia, Tartous, Aleppo, Damascus and Rural Damascus, where many are being sheltered by relatives. The government has established collective shelters, while humanitarian organizations are delivering immediate assistance at border crossings. UNRWA is coordinating with stakeholders, including at the inter-agency level through the Humanitarian Country Team, to address the critical needs of the displaced Palestine refugees. To this end, the Agency aims to extend multi-purpose cash assistance (MPCA), NFIs and emergency shelter, health and protection services to affected families, along with psychosocial support (PSS) for all displaced Palestine refugee children.</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:07:00.336714+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #3 on the Lebanon Emergency Response. All information valid as of 30/09/2024 at 15:00 [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-3-lebanon-emergency-response-all-information-valid-30092024-1500-enar</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Key Points
+- The rapid increase in the number of displaced persons has resulted in an influx of individuals to emergency shelters across Lebanon. According to OCHA[1], there were 785 collective shelters open as of 28 September, with 551 having already reached full capacity. UNRWA continues to open new shelters to increase capacity across the country.
+- UNRWA activated its Emergency Response in Lebanon on 24 September, immediately opening two shelters. Since then, UNRWA has opened eight additional shelters, bringing the total number of operational UNRWA shelters to ten as of 30 September.
+- The ten shelters operated by UNRWA are distributed in the following areas: one in Beirut (Yabud School), four in the Saida Area (Siblin Training Centre, Nablus School, Rafidya School, Beir Zeit/Beit Jala School), four in the North (Toubas School, and Amqa School, Mount Tabour School, and Battir School, all in Nahr el-Bared Camp), and one in the Beqaa (Jarmaq School, in Zahle District).
+- A total of 2,332[2] internally displaced persons (IDPs) are registered in UNRWA shelters as of 30 September, representing an increase of 64 per cent compared to the 1,424 reported on 27 September. This number is expected to continue rising.
+Overall Situation
+- According to the last available OCHA report[1], since October 8, 2023, 1,640 people were killed in the hostilities in Lebanon – 1,030 of them in September 2024 alone. Over 8,408 individuals have been injured as of 28 September. This number is expected to have increased between 29 and 30 September.
+- Following heavy strikes by Israeli forces on the southern suburbs of Beirut on the afternoon of 27 September, on 28 September Hezbollah confirmed the death of its Secretary General, Hassan Nasrallah, along with other high-ranking officials, as result of these strikes.
+- Educational institutions in Lebanon remain closed for learning on 30 September, following the decision of the Ministry of Education and Higher Education to suspend classes in public and private schools[2] and to postpone the start of the new academic year.[3]
+- As of September 29, IOM reported[4] 346,209 internally displaced persons (IDPs) in the country since October 2023, with 35 per cent being children. This marks a significant increase since 26 September: an additional 134,890 IDPs have been displaced, representing a 64 per cent rise.
+- As of 30 September, 637 households, representing a total of 2,332 individuals, are registered in UNRWA emergency shelters across the country, marking an increase of 64 per cent since the previous report of 28 September. Of these registered individuals, 49 per cent are Palestinian, 23 per cent are Syrian, and 28 per cent are Lebanese. Among the Palestinian population, 65 per cent are Palestine Refugees from Lebanon (PRL) and 35 per cent are Palestine Refugees from Syria (PRS).</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:07:06.468417+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #2 on the Lebanon Emergency Response. All information valid as of 27/09/2024 at 15:00 [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-2-lebanon-emergency-response-all-information-valid-27092024-1500-enar</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Key Points
+- UNRWA declared the activation of its Emergency Response in Lebanon on 24 September 2024, immediately opening two emergency shelters. Between 25 September and 27 September, UNRWA has opened five additional emergency shelters, bringing the total number of operational UNRWA emergency shelters to seven.
+- A total of 1,424 individuals are registered in UNRWA emergency shelters, with numbers expected to further increase.
+- The seven emergency shelters operated by UNRWA are distributed in the following areas: one in Beirut (Bir Hassan – Nabih Berry Educational Complex), three in the Saida Area (Siblin Training Centre, Nablus School, and Rafidya School), two in the North (Toubas School, and Amqa School, in Nahr el-Bared Camp), and one in the Beqaa (Jarmaq School, in Zahle District).
+Overall Situation
+- Education institutions in Lebanon are currently closed for learning, following the Ministry of Education and Higher Education’s decision to postpone the start of the new academic year. Classes have been suspended in public schools until 14 October and private schools until 7 October 2024.[1]
+- According to the latest IOM report, as of 25 September, a total of 211,319, including around 74,000 children, have been recorded to be internally displaced in Lebanon since October 2023. This marks a significant increase in the past week, with 118,466 individuals newly displaced (+89 per cent).
+- The majority of internally displaced persons (IDPs) (73 per cent) originate from three districts, which span along the Southern border of Lebanon. Specifically, 42 per cent are from Bent Jbeil, 17 per cent are from Sour, and 14 per cent are from Marjaayoun. The remaining 27 per cent originate from 11 different districts, namely Baalbek, Baabda, El Nabatieh, Saida, Hasbaya, Beirut, El Hermel, Jezzine, West Bekaa, Zahle, and Chouf. The districts hosting the most newly displaced people during this period were Beirut, Chouf, Baabda, Saida, and Aley.[2]
+- In the Beqaa Valley, airstrikes in the district of Baalbeck have led many families to flee to areas perceived to be safer in central and west Beqaa. There is reportedly a significant influx of Palestine Refugees from Syria (PRS), and Syrian and Lebanese families crossing into Syria. The Syrian government has opened all border crossings to civilians arriving from Lebanon, a decision that has been welcomed by the United Nations through a joint statement from the Resident Coordinator and Humanitarian Coordinator for Syria, and the Regional Humanitarian Coordinator for the Syrian crisis[3] on 26 September.
+- A number of IDPs have reportedly sought shelter in Palestine Refugee camps, including Lebanese, Syrian, and Palestine Refugees. The majority are staying with relatives. IDP arrivals have been reported in Dbayeh camp north of Beirut, Mar Elias camp southwest of Beirut, Burj Barajneh and Shatila camps in southern Beirut, and Beddawi camp northeast of Tripoli. UNRWA is currently unable to verify the number of IDP arrivals in these camps.
+- As of 27 September, 364 households, representing a total of 1,424 individuals, are registered in UNRWA emergency shelters across the country, marking an increase of 200 per cent since the last report of 25 September. Of these registered individuals, 35 per cent are Palestinian, 25 per cent are Syrian, and 50 per cent are Lebanese. Among the Palestinians, 60 per cent are Palestine Refugees from Lebanon (PRL) and 40 per cent are Palestine Refugees from Syria (PRS).</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:07:12.503396+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Lebanon: UNRWA opens additional shelters for the displaced people [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/lebanon-unrwa-opens-additional-shelters-displaced-people-enar</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>BEIRUT,
+As armed conflict affecting Lebanon intensifies, UNRWA continues implementing its emergency response plan, activated on 24 September.
+As of 27 September 2024, the seven operating shelters accommodate 1,424 displaced individuals, including Palestinians, Lebanese, and Syrians. The Agency is providing food, mattresses, blankets, and other essentials in these DESs.
+UNRWA provides in these shelters aid based on impartiality and non-discrimination, hosting Palestine Refugees, Lebanese and Syrian refugees, supporting all in need. This reflects UNRWA's commitment to upholding humanitarian principles, delivering aid based on humanitarian need.
+Despite all challenges, our operations continue across Lebanon, primarily providing health services and garbage collection and relief.
+“We are passing through a difficult time, and I express my deep gratitude to our dedicated staff who continue supporting our operations and in particular the ongoing emergency response.” the Director of UNRWA Affairs in Lebanon said.
+For more information, please contact:
+UNRWA on Twitter:
+Email:</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:07:18.829551+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>UNRWA Situation Report #1 on the Lebanon Emergency Response. All information valid as of 25/09/2024 at 15:00 [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-situation-report-1-lebanon-emergency-response-all-information-valid-25092024-1500-enar</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Key Points
+- Following significant escalation in the armed conflict between Israel and Hezbollah in Lebanon on 23 September, and the subsequent arrival of Palestine Refugees from the south seeking shelter in safer areas, UNRWA started the emergency response in Lebanon
+- On 24 September, UNRWA opened two emergency shelters in Saida area (Siblin Training Centre) and the north (Toubas School inside Nahr el-Bared Camp). UNRWA opened another emergency shelter in its Nablus School in Saida city, in support of the overwhelmed Saida municipality on 25 September.
+- UNRWA is providing shelter to people in need, including displaced Lebanese, Syrian refugees and Palestine Refugees.
+- As of mid-day on 25 September, a total of 490 individuals were registered in the UNRWA emergency shelters, with numbers expected to double by end of the day.
+Overall Situation
+- On 23 September, the armed conflict between Israel and Hezbollah entered a new phase. Since then, Israeli Forces’ airstrikes have impacted multiple areas across Lebanon, including Mount Lebanon, Nabatieh, Jezzine, Saida and the Bekaa region (North of the Litani River) in addition to areas on the southern border (South of the Litani River).
+- As of 25 September, the Ministry of Health of Lebanon reported 558 persons killed (including 50 children), in addition to 1,835 injured.
+- The intensive airstrikes have displaced tens of thousands of civilians, with many seeking shelter in the north. The city of Saida (in the south) has reportedly experienced a large influx of displaced persons, leading to shortages of basic supplies as bread and drinking water. As of 24September, around 200,000 people were estimated to be displaced in Lebanon. According to IOM, a total of 111, 656 people were reported displaced in the country as of 17 September. An additional 90,530 persons have been displaced from 17 to 24 September.
+- The Government of Lebanon (GoL) and other institutions are stretched beyond capacity, affecting in particular the overwhelmed health care sector struggling to treat hundreds of wounded. The GoL has declared 240 schools and education facilities as shelters to accommodate the displaced people. It is however unprepared to manage this scale and provide sufficient food assistance.
+- Most of the displaced are fleeing the southern district and Nabatieh, heading towards Beirut, Mount Lebanon, and from eastern districts including Baalbeck-Hermel and Akkar.
+- Palestinians from gatherings and localities in Tyre and Saida inlcuding Adloun, Ansariya, Zahriya, Nabatiye have reportedly been displaced towards Saida and the northern areas. Most have sought to stay with family members in Saida, other cities and camps.
+- In Tyre, some Palestine Refugees have reportedly moved into the city’s Palestine Refugee camps (Burj Shemali, Rashidieh, El-Buss).
+- In the Beqaa Valley, airstrikes near Baalbeck, including Wavel Camp, have led many families to flee to areas perceived to be safer in central and west Beqaa, with a number of Palestine Refugees from Syria (PRS) reportedly opting to return to Syria.
+- As of now1, 121 households, representing a total of 490 people, are registered in the three opened UNRWA emergency shelters in the country. Of the registered individuals, 24 per cent are Palestinian, 29 percent are Syrian and 47 per cent are Lebanese. Among the Palestinians: 65 per cent are Palestine Refugees from Lebanon (PRL) and 35 per centare Palestinian refugees from Syria (PRS).
+- The number of displaced people continued to increase on 25 September.
+Humanitarian Access, Protection of Civilians
+- Since the escalation of hostilities on 23 September to date, only one UNRWA personnel in the Tyre area has been slightly injured. This team member received care at an UNRWA clinic and was subsequently released.
+- Since the onset of the emergency response, two UNRWA facilities have sustained minor damage: Qastal School in Baalbeck (Beqaa) and Mansoura School in Tyre (South) including broken windows from nearby airstrike blasts. Repairs are underway as access permits.
+- The Agency’s Mansoura School and the nearby Houleh School north of Tyre have been excluded from being used as UNRWA emergency shelters due to the proximity of airstrikes.
+UNRWA response
+- UNRWA announced the activation of its emergency response on 24 September and initially opened two of its emergency shelters for displaced persons: Toubas School in the Nahr el-Bared camp in the northand the Siblin Training Centre (STC) in Saida area. On 25 September, in response to the overwhelmed Saida municipality, UNRWA opened another emergency shelter in its Nablus school in Saida, to assist displaced people (mainly Lebanese nationals and Syrian refugees).
+- UNRWA provided the displaced with mattresses, pillows, ready-to-eat foods and water. All incoming displaced persons are registered byUNRWA and supervised by trained emergency shelter coordinators and managers.
+- UNRWA fitted the shelters with additional toilet and shower units, lighting and fuel tanks or solar panels. There is a small warehouse, a pharmacy and a medical clinic in the STC.
+- UNRWA has finalized preparations for a total of 12 emergency shelters to be opened as needed. These shelters are equipped with sanitation and hygiene facilities, and food and drinking water.
+UNRWA Shelters
+Siblin Training Center (South):
+The UNRWA emergency shelter at STC located in Saida area, with the current capacity to host 1,400 persons, opened to IDPs on the morning of24 September. It currently hosts 96 families including 388 people registered at the shelter.
+Toubas School (North):
+The UNRWA emergency shelter at Toubas School located in the Nahr el-Bared Palestine refugee camp, with the capacity to host 774 IDPs, opened on the morning of 24 September. It was s opened to accommodate displaced persons from both the south and the neighboring Bekaa area, which is regularly receiving Israeli Forces airstrikes. Currently, 15 families including 68 people are registered at the shelter.
+Nablus School (South):
+In response to a request from the overwhelmed Saida municipality, UNRWA opened an emergency shelter in its Nablus School on 25 September. The school is expected to reach full capacity quickly (up to 400 individuals). Currently, nine families including 30 people are registered in the shelter.
+Programmatic &amp; Operational Response
+Health
+- The UNRWA health team is mobilised and operational. All UNRWA health facilities are functioning with no reports of medications shortages.
+- UNRWA announced the activation of its emergency hospitalization response to cover wounded civilians at contracted hospitals.
+- Arrangements are being sought for kidney dialysis patients. Prior to the emergency response, these patients were being treated at a hospital in Saida. Many may no longer be able to reach this location. Some kidney dialysis patients from the south have been referred to stay at the emergency shelter in Saida to facilitate the frequent need for treatment.
+- Within the emergency hospitalization framework, two Palestine Refugees (one PRS and one PRL) have been reported hospitalized for injuries sustained in the Tyre area.
+Protection
+- UNRWA protection team is working to support the registration team in the set-up of registration of IDPs in its emergency shelters. Guidelines published and disseminated to the community (including in a voice note) over an official UNRWA WhatsApp channel.
+- Children remain particularly vulnerable in this crisis. In Tyre, one unaccompanied Palestine Refugee child was identified in the El Buss areaand was referred to protection partners.
+Sanitation Services/WASH
+- All water networks in the camps are currently operating, ensuring adequate water supply for residents.
+- Solid waste management is being implemented in all areas except Tyre, due to the current security situation. For the Tyre Area:
+  - In Rashidieh and El Buss Palestine Refugee camps: solid waste is being collected at designated platforms within the camps. However, transportation of these solid wastes to the dumping site in the Burj Shemali area is currently inaccessible due to ongoing security concerns, preventing any solid waste collection.
+  - In Burj Shemali Camp: solid waste from the Burj Shemali camp is brought to the Burj Shemali area dumping site. However, the current situation has rendered this process not possible. UNRWA is exploring options to rent a plot of land adjacent to the camp to establish a solid waste collection point, which would facilitate improved waste management operations.
+Logistics
+- UNRWA has prepositioned supplies across the country in six storage facilities: Lebanon Field Office in Beirut, Houleh School and Mansoura School in Tyre2, the Siblin Training Center in Saida and Saadnayel storage facility in the Beqaa Vally. The supplies are being moved, monitored and replenished according to UNRWA emergency shelter needs and the overall situation.
+- Prepositioned supplies include 5,000 ready-to-eat food parcels, 3,500 standard dry food parcels, drinking water, mattresses and pillows, cleaning supplies, hygiene kits, first aid kits and approximately 700 tons of flour ready to be distributed across the UNRWA emergency shelters.
+- Coordination with partners is underway to procure all necessary items based on identified needs. A joint procurement effort is being established with IOM, which will source goods for UNRWA emergency shelters upon request.
+[1] Data cut-off time: 25/09/2024 at 3 PM
+[2] Due to the exclusion of Houleh/Mansoura Schools as potential emergency shelters, supplies stored there are being transferred to the emergency shelter at Siblin Training Centre.
+Quote from Philippe Lazzarini, UNRWA Commissioner General:
+“Our worst fear seems to be unfolding. […] I would like to echo what the UN Secretary-General said to the Member States: don’t make Lebanon a new Gaza.”
+ENDS-
+FOR MORE INFORMATION, PLEASE CONTACT:
+Global Media Requests
+WhatsApp: +962-7-9130-0567
+European Media Requests
+English/French/Spanish:
+WhatsApp +32473822006
+Japanese Media Requests
+WhatsApp: +972 54-240-2727
+Email: media@unrwa.org</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:07:24.947251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>UNRWA Opens Two Designated Emergency Shelters for Displaced [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-opens-two-designated-emergency-shelters-displaced-enar</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>In response to the ongoing developments and the escalating conflict in Lebanon, UNRWA announces the opening of two of its Designated Emergency Shelters (DESs) for displaced individuals: Toubas School in Nahr El Bared in the north and Siblin Training Centre in the south. UNRWA management teams are on the ground at these DESs to receive and support the displaced. Additional DESs will be opened as needed. The Agency has pre-positioned food, and non-food supplies to support the displaced.
+While UNRWA prioritizes Palestine refugees in these shelters, it remains committed to assisting individuals of other nationalities in need during times of escalation, depending on resource availability. This commitment aligns with shared humanitarian principles and values—such as generosity, solidarity, and reciprocity—that are essential in conflict environments. In this context, the Agency provided some supplies yesterday to the municipality of Al Wardaneyeh village in Iqlim Al Khroub to support the displaced individuals hosted in the area.
+UNRWA is also responding to the request of the Saida municipality to open Nablus school for the displaced from the south as of tomorrow.
+As of today, the Agency has activated its emergency response plan, which includes providing hospitalization for wounded registered Palestine refugee civilians at contracted hospitals, as per its existing hospitalization policy for each hospital.
+“We are making all efforts now to support displaced persons in these challenging times. We hope that peace is restored soon,” said Dorothee Klaus, the Director of UNRWA Affairs in Lebanon. “I want to extend my thanks to all my colleagues, especially those working to support the displaced during these difficult times,” she added.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:07:30.949932+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>UNRWA's Journey Toward Digital Transformation - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/unrwas-journey-toward-digital-transformation</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Innovation has become a fundamental aspect of our daily lives, seamlessly integrated into our homes, workplaces, schools, and healthcare facilities. Technology plays a crucial role in enhancing productivity, optimizing processes, capturing data, and improving communication. The COVID-19 pandemic not only disrupted global markets but also accelerated the adoption of digital tools across various sectors, including development and humanitarian aid.
+At UNRWA, we are embracing this shift with a strategic focus on integrating innovative solutions into our service delivery for Palestine Refugees. The Agency’s leadership has prioritized digital transformation, recognizing its potential to leverage our digital ecosystem to enhance our operations and programmes.
+UNRWA’s strong digital presence and large workforce have long been drivers of our transformation initiatives. We are building on this foundation to improve the quality of services we provide to Palestine Refugees across the region.
+This transformation is led by a modernization plan and digital strategy designed to drive innovative initiatives. It will enhance service delivery while reducing the costs associated with traditional methods. Key to this strategy is our partnership with KfW Development Bank, a crucial supporter of UNRWA’s digital initiatives, particularly in the areas of health and education. KfW’s investment includes an EUR 13 million contribution in July 2022. This was followed by an additional EUR 12 million contribution in July 2023, earmarked for systems, infrastructure, cybersecurity, change management, capacity building, connectivity improvements, and policy development.
+As UNRWA advances implementation of this plan, the team is also exploring how best to utilize data for improved decision-making. In health, our eHealth system, operational since 2009, has generated extensive data that will soon be migrated to a modern electronic medical record (EMR) system. In education, an Education Management Information System (EMIS) and Digital Learning System are actively used by teachers and students across all fields of operation to capture essential education data.
+Looking ahead, a critical issue is how we can leverage the vast amounts of data collected through our various systems to enhance decision-making. Our goal is to not only improve service quality through digital systems but also to harness data for more effective resource management and quicker decision-making.
+Central to our services is the refugee data we collect, which, when combined with health, education, and other data layers, will help us identify trends and understand the challenges and opportunities in service delivery. This forward-thinking approach requires alignment and collaboration among all stakeholders.
+To address these challenges and strengthen support for health and education services, we are organizing a workshop to engage stakeholders and tackle critical digitization issues. We anticipate this will lead to a significant shift toward embracing digital technology, innovative models, and cost-effective practices, ultimately fostering a more digital and innovative agency.
+As Kaan Cetinturk, UNRWA’s Chief Information Officer and Director of the Digital Impact, Technology, and Innovation Department notes, “Digital transformation is not just about technology; it’s about transforming how we work and deliver results to create a better world. Embrace the change, and let technology be the enabler of our mission.”
+Additionally, UNRWA has partnered with leading private sector players, including Gartner and Microsoft, to support this journey. We believe that collaboration with the private sector, donors, and our staff is crucial to achieving our goals. Embracing digital innovation is key to improving operations, programmatic areas, and ultimately better serving the Palestine Refugee community. Through these partnerships, we aim to bridge operational gaps, invest in essential skills and infrastructure, and adopt best practices to enhance the health and education of Palestine Refugees.</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:07:36.934063+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>UNRWA MOPAN Assessment Report (August 2024) [EN/AR] - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/unrwa-mopan-assessment-report-august-2024-enar</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>A donor-led organizational performance assessment report lauds UNRWA’s unparalleled services for Palestine Refugees
+26 August 2024
+AMMAN
+A review of UNRWA by a group of UN Member States, all of them donor countries, has commended the Agency for managing to keep operating under highly challenging circumstances, including the war in Gaza. The report, analyzing UNRWA’s performance and effectiveness between July 2018 and April 2023, confirms its unparalleled ability to deliver education, health, and social services to Palestine Refugees.
+“UNRWA has demonstrated a commendable ability to adapt and continue its operations under highly challenging conditions, including active conflict zones,” said the report of MOPAN – the Multilateral Organization Performance Assessment Network.
+“The Agency’s ability to deliver education, health, and social services at scale to one of the world’s most vulnerable populations is unparalleled," it added.
+MOPAN previously reviewed UNRWA in 2011 and 2018. Germany and Qatar co-led this latest assessment. According to the report, the main strengths of the Agency are:
+- UNRWA’s unique and valuable contribution to regional and local stability.
+- A proven ability to consistently deliver quality services to a growing number of people under increasingly difficult conditions.
+- Proven adaptive capacity to deliver services in worsening conditions, including during the COVID-19 pandemic and the war in Gaza.
+- Committed staff with robust contextual understanding.
+MOPAN acknowledged that there had been improvements since the 2018 assessment, especially in evaluation and oversight, planning and reporting, and external outreach, including to donors and other parts of the UN system. It gave the Agency an overall “satisfactory” rating in the vast majority of assessed areas.
+MOPAN also identified areas where UNRWA could improve its performance. It recommended the development of a more decentralized organizational structure, called for the Agency’s physical infrastructure and assets to be improved or replaced, and said the digitization of its work processes and systems should be bolstered.
+In addition, it recommended UNRWA to do more on gender equality and environmental sustainability, risk management, prevention of sexual exploitation and abuse, ethics, evaluation, and human resources. Additionally, the MOPAN report recommended that the Agency further strengthens its external and internal communications - underscoring the significant improvement made in this area since the last assessment - as well as its performance monitoring, needs assessments and learning.
+“We welcome MOPAN’s acknowledgement of UNRWA’s unparalleled service delivery and unique contribution to regional and local stability,” said UNRWA Deputy Commissioner-General Natalie Boucly. “We are committed to addressing the areas for improvement and call on Member States to step up their political and financial support to the Agency to enable us to do so. Such support is critical to continue providing public-like services to Palestine Refugees across all fields, and to deliver lifesaving humanitarian assistance in Gaza.”
+ENDs-
+Notes to Editors
+- UNRWA is currently analyzing the findings of the MOPAN assessment. The Agency is cross-referencing the MOPAN recommendations with those of the Independent Review of UNRWA - the Colonna report, published in April - to identify synergies in the implementation of both.
+- The members of MOPAN are Australia, Belgium, Canada, Denmark, Finland, France, Germany, Ireland, Italy, Japan, Korea, Luxembourg, The Netherlands, New Zealand (observer), Norway, Qatar, Spain, Sweden, Switzerland, United Kingdom, United States, and Türkiye (observer).
+Background Information:
+UNRWA is the United Nations Relief and Works Agency for Palestine Refugees in the Near East. The United Nations General Assembly established UNRWA in 1949 with a mandate to provide humanitarian assistance and protection to registered Palestine refugees in the Agency’s area of operations pending a just and lasting solution to their plight.
+UNRWA operates in the West Bank, including East Jerusalem, The Gaza Strip, Jordan, Lebanon and Syria.
+Tens of thousands of Palestine refugees who lost their homes and livelihoods due to the 1948 conflict continue to be displaced and in need of support, nearly 75 years on.
+UNRWA helps Palestine Refugees achieve their full potential in human development through quality services it provides in education, health care, relief and social services, protection, camp infrastructure and improvement, microfinance, and emergency assistance. UNRWA is funded almost entirely by voluntary contributions.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:07:43.626951+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Safe Havens: Transforming Palestine Refugee Camps for Children in Lebanon - Lebanon</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/safe-havens-transforming-palestine-refugee-camps-children-lebanon</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>In Lebanon’s crowded Palestine refugee camps, the lack of child-friendly environments poses significant challenges for the children and youth. UNRWA has worked to create safe spaces where young people can play and thrive without facing potential harm.
+In various consultations, UNRWA asked children and their caregivers to identify their concerns. Time and again they highlighted the need for safe recreational areas. Child protection experts and UNRWA school staff also emphasized this need. A recent key Child Safety Assessment in Palestine refugee camps recommended these spaces as essential for children's well-being and development.
+The project was funded through the UNICEF and UNRWA partnership and implemented by the Taawon Foundation working alongside Al Houleh and Al Jaleel organizations, in Tyre.
+“Safe spaces where kids can learn, grow, and thrive despite the challenging conditions they face are so critical for Palestine refugees in Lebanon. UNRWA strives to support children and youth through collaboration with our partners,” said Oliver Bridge, the Deputy Director of UNRWA Affairs in Lebanon in charge of programmes.
+Al Jaleel organisation renovated Ain Al Asal playground in Rashidieh camp. The space now features swings, slides, a renovated basketball court and a landscaped garden area with benches shaded by beautiful trees. The space now equally boasts of an indoor library with running water in the facility.
+At Burj el Shemali camp, the Al Houleh organisation developed a football pitch on the rooftop of the building and the indoor meeting space underwent renovations.
+Initial reports from these refurbished spaces were promising. They observed increased usage by children of all ages, alongside engagement from other community groups like women’s committees. The spaces were designed to be accessible throughout the day, providing a haven away from hazardous alternatives like crowded coffee shops.
+Soad, a child from Rashidieh camp, said, "Having a safe place to play with my friends makes me feel happy."
+Naya, another child, expressed her appreciation for the green grass and how the garden has become more beautiful with the addition of trees. Yaser mentioned that he appreciates being able to play basketball in the garden without having to worry about the sun or rain.
+Supervision by trained personnel from collaborating organisations ensures that the spaces remain safe and conducive to children’s activities. This setup not only supports children’s physical health but also fosters social interactions and educational opportunities.
+As the initiative continues to expand, UNRWA remains committed to creating more friendly environments across Palestine refugee camps and to expanding existing partnerships to advance such activities.
+UNRWA thanks its partners UNICEF, Taawon, Al Houleh, and Al Jaleel for working together to revitalise the spaces and strengthen community ties among Palestine refugee children in Lebanon.</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:07:49.789546+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>UNRWA 2023/24 Graduate Students Achieve High Success Rates in the Baccalaureate II Exams and in the Technique Superieur Exams at Siblin - Lebanon</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-202324-graduate-students-achieve-high-success-rates-baccalaureate-ii-exams-and-technique-superieur-exams-siblin</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Following the release of the Technique Superieur (TS) vocational and technical exam results and the first round of the Baccalaureate II examination results, UNRWA congratulates all students who passed. Their hard work leading to excellent accomplishments is truly commendable.
+Siblin Training Centre students scored a 100 per cent pass rate, with 60 per cent of students passing with distinction.
+UNRWA's Baccalaureate II students in the Life Science stream achieved an impressive final score of 97.5 per cent of which 79.9 per cent with distinction. A total of 71.8 per cent of students in the Economic Stream passed of which 28 per cent with distinction, including two students with severe visual impairments.
+This achievement is especially remarkable considering the socio-economic difficulties faced by Palestine refugees in Lebanon, with currently 72 per cent living below the poverty line as per latest 2024 surveys.
+“The success of our students is a testament to their dedication and the vital role of education in their lives. Despite facing numerous challenges, their achievements highlight their hard work and the support of their families and communities. This also reflects the hard work that our teachers and school administration have invested to achieve such excellent outcomes. Well done!” said Dorothee Klaus, Director of UNRWA Affairs, Lebanon.
+“UNRWA remains dedicated to ensuring learning outcomes that place Palestine refugee children on a successful path for their futures. Their hopes to meaningfully contribute to society with their energy and commitment shall not be in vain.”, she added.
+Congratulations to our students, their families, our education staff, and the entire community. We are proud of the efforts demonstrated by all.
+We wish the very best of luck to those retaking the exams in the second round.
+Background Information:
+UNRWA is the United Nations Relief and Works Agency for Palestine Refugees in the Near East. The United Nations General Assembly established UNRWA in 1949 with a mandate to provide humanitarian assistance and protection to registered Palestine refugees in the Agency’s area of operations pending a just and lasting solution to their plight.
+UNRWA operates in the West Bank, including East Jerusalem, The Gaza Strip, Jordan, Lebanon and Syria.
+Tens of thousands of Palestine refugees who lost their homes and livelihoods due to the 1948 conflict continue to be displaced and in need of support, nearly 75 years on.
+UNRWA helps Palestine Refugees achieve their full potential in human development through quality services it provides in education, health care, relief and social services, protection, camp infrastructure and improvement, microfinance, and emergency assistance. UNRWA is funded almost entirely by voluntary contributions.
+For more information, please contact:
+UNRWA on Twitter: @UNRWA
+Email: media@unrwa.org</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:08:02.495641+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>UNRWA Ethics Office Annual Report 2023 - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/unrwa-ethics-office-annual-report-2023</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Introduction
+The Ethics Office assists the Commissioner-General in fostering an ethical environment whereby all UNRWA employees observe and perform their functions with the highest standards of integrity as required by the Charter of the United Nations.
+The present report provides an overview and assessment of the work of the Ethics Office in 2023. It is submitted pursuant to UN Secretary-General Bulletin ST/SGB/2007/11 and the UNRWA Organizational Directive 30 (OD 30 - Terms of Reference of the Ethics Office), requiring annual reporting on the activities of the Ethics Office and any related evaluations and assessments.
+It is the fourteenth report since the designation of an Ethics Officer in UNRWA in January 2008 and the thirteenth since the establishment of the UNRWA Ethics Office in September 2009.
+In accordance with Section 24 of OD 30, the report was shared for review and advice to the Advisory Committee on Internal Oversight (ACIO) and the Ethics Panel of the United Nations (EPUN). The report will be submitted to the Commissioner-General and to the Advisory Commission on UNRWA.
+In October 2023, the world witnessed a dramatic escalation of hostilities in Gaza, which resulted in unprecedented civilian casualties, including more than 140 UNRWA colleagues (as of December 2023), displacement of people and destruction of infrastructure. The war in Gaza also greatly affected operational requirements of the Agency and heightened demands by stakeholders for strong accountability and controls concerning the prevention, monitoring, and response to alleged breaches of neutrality.
+During the last years, the Ethics Office focused on reinforcing staff members’ knowledge and understanding of the UN Standards of Conduct, promoting accountability for breaches of UNRWA’s regulatory framework, including in relation to neutrality, and ensuring that ethics is integrated into policies and practices of UNRWA’s Departmental and Field Operations Programmes. Some of the most important initiatives led or supported by the Ethics Office in relation to neutrality include the revision of Code of Ethics, its launch, and distribution to UNRWA staff members; the development of the Affirmation of the Code of Ethics rolled out in all categories of personnel contracts by 2024; the revision of three of UNRWA’s mandatory e-courses, including “Ethics and Integrity at UNRWA” with a section on Humanitarian Principles and the use of Social Media; the development and roll out of face-to-face mandatory and refresher training that address Humanitarian Principles, including neutrality and political activities; and conducting missions to Field Offices for outreach and awareness raising on the topic.
+Building on these initiatives, and with a view to strengthening further UNRWA’s capacity to prevent and respond to breaches of neutrality and enhance mechanisms for control, accountability, and learning, the 2023 Ethics Office workplan adapted to emergency needs, undertaking significant efforts to continue raising awareness and monitoring staff conduct in the emergency context, while continuing to deliver on its six lines of service.</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:08:08.478901+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>UNRWA Commissioner-General Philippe Lazzarini on the statement of shared commitments on UNRWA - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/unrwa-commissioner-general-philippe-lazzarini-statement-shared-commitments-unrwa</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>From Philippe Lazzarini, the UNRWA Commissioner-General as posted on his official X account (previously known as Twitter)
+Thank you.
+An impressive show of solidarity and support of 118 member states including all members of the UN Security Council.
+It comes at a critical time as @UNRWA undergoes unprecedented attacks and systematic attempts to dismantle it.
+It is a tribute to our staff working across the region, including on the humanitarian front lines in #Gaza.
+There is no alternative to UNRWA.
+We are committed to continue delivering assistance and basic services including #education to Palestinian boys and girls.
+Read the statement of shared commitments to UNRWA supported by 118 Member States including all members of the UN Security Council here
+Background Information:
+UNRWA is the United Nations Relief and Works Agency for Palestine Refugees in the Near East. The United Nations General Assembly established UNRWA in 1949 with a mandate to provide humanitarian assistance and protection to registered Palestine refugees in the Agency’s area of operations pending a just and lasting solution to their plight.
+UNRWA operates in the West Bank, including East Jerusalem, The Gaza Strip, Jordan, Lebanon and Syria.
+Tens of thousands of Palestine refugees who lost their homes and livelihoods due to the 1948 conflict continue to be displaced and in need of support, nearly 75 years on.
+UNRWA helps Palestine Refugees achieve their full potential in human development through quality services it provides in education, health care, relief and social services, protection, camp infrastructure and improvement, microfinance, and emergency assistance. UNRWA is funded almost entirely by voluntary contributions.
+Your support is crucial to help us provide emergency aid
+to displaced families in Gaza
+FOR MORE INFORMATION, PLEASE CONTACT:
+UNRWA on Twitter:
+Email:
+Show Email</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:08:14.541396+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>UNRWA Annual Operational Report 2023 - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/unrwa-annual-operational-report-2023</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>The 2023 Annual Operational Report (AOR) describes UNRWA progress towards the attainment of the objectives set out in the Agency’s Strategic Plan 2023-28. The 2023 AOR also contains the final reporting on the Emergency and Early Recovery Response in support of Palestine Refugees in Syria and Lebanon Affected by the Earthquakes and Aftershocks Flash Appeal as well as progress reporting on the Humanitarian and Early Recovery Appeal for Jenin, the Ein El Hilweh Flash Appeal and the updated oPt Flash Appeal. In addition, the report contains an analysis of progress achieved against programmatic and resource mobilization targets set out under UNRWA’s Resource Mobilization and Outreach Strategy 2023-25 (ReMOS). The AOR also incorporates a series of annexes that include results frameworks and key statistics.
+oPt + 3 more</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:08:20.549317+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>The power of the image: Preserving UNRWA’s past and present for the future - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/power-image-preserving-unrwas-past-and-present-future</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>By Jonathan Fowler
+As the war in Gaza rages, causing unprecedented death and destruction, telling its story is a moral imperative. Preserving images from Gaza matters more than ever. Not just to document the spiraling humanitarian tragedy right now but also to preserve it for posterity.
+UNRWA is committed to this goal as part of its longstanding effort to recount its work as the UN agency specifically dedicated to providing relief and public services for Palestine refugees. Since its creation by the UN General Assembly in 1949, UNRWA has built up a vast trove of still and moving images. It is considered so important that in 2009 it was named by UNESCO as a Memory of the World archive of outstanding value.
+Few people in UNRWA have a better sense of this value than Gaza-based Amani,* who has followed the archive’s evolution from the inside since the turn of the century. She started as its Photo Librarian in 1999 at the age of 25, and has served as UNRWA’s Multimedia and Archiving Officer since 2023.
+“This archive protects and preserves the heritage of Palestine refugees. It also documents UNRWA’s efforts to provide for refugees since the Nakba right up to today,” said Amani who, like the overwhelming majority of UNRWA’s 30,000 staff, is Palestinian.
+“It really tells the story of the UNRWA response on the ground, the different aspects like education, primary healthcare, relief and social services, the microfinance programs, the women’s programs, and all other aspects.”
+“In addition, it’s a powerful reminder and witness of this endless tragedy, all those decades, all the historical milestones, from 1948 to 1967 and beyond. It even seems that this tragedy will pass to the next generation,” she said.
+The archive contains about half a million audiovisual materials, and its content charts the technological developments of nearly eight decades.
+“We have negatives – black and white, and color. We also have slides. We have films. We have video cassettes, both VHS and Umatic. We have everything right up to the latest digital content,” said Amani, who has long been responsible for constantly keeping the archive up to date – experiencing firsthand the evolution of the role of an archivist.
+“In the past, we used an old-fashioned camera with plastic roll film. We used to develop the film, make photo prints, and then I, as Photo Librarian, classified the photos according to subject and also according to the area. Then, I typed a caption for each photo, printed it out, and cut and pasted it onto the back of each photo. We’d send the printed photos in an envelope by mail to users. It was a long process – everything was manual,” she said.
+Even though that work is now fully digital, the task remains enormous, given the ever-increasing flow of content made possible by technology – notably the ability for anyone to gather high-quality material using a smartphone. Amani is fed content by a network of UNRWA colleagues across the agency’s five fields of operation: Gaza, the West Bank, including East Jerusalem, as well as Jordan, Lebanon, and Syria.
+“We enrich it on a monthly basis. There is coordination between me and the other Public Information Officers in the five fields.” Amani asks her colleagues in the fields to select their best photos every month and to upload them to their office’s online photo galleries. She then enters the metadata so that users have each photo’s details and makes them available in the overall UNRWA archive.
+The UNRWA archive contains 430,000 negatives, 65,000 slides, 75 films, and 730 video cassettes. Its enormous size makes choosing a favorite image difficult. But Amani rose to the occasion, picking image RL/Tyre/8.
+She explains the emotional story that it tells: “When you look at the photo, you see challenges in the eyes of the father, and you can feel how the mother is worried about their fate and the future of their daughter, while the daughter’s eyes are saying, ‘I don’t deserve to be a refugee.’ The family was uprooted from home and forced to flee to Lebanon.”
+Impressively, Amani has managed to keep doing this critical work despite the enormous challenges posed by the war – not only regular internet outages, but also personal stress and the struggle to survive. She epitomizes the courage and commitment displayed by UNRWA’s Gaza staff in the face of the war – at the time of writing, 193 of them have been killed, the highest death toll for UN personnel in the history of the world body.
+In the wake of its Memory of the World listing, UNRWA worked with UNESCO, the Palestinian Authority’s diplomats, and the French National Audio-Visual Institute to digitize the archive in its entirety as part of efforts to preserve it.
+“In 2013, UNRWA implemented a digitization project for all the material we had in our Gaza and Amman headquarters. We digitized everything,” said Amani.
+All that remains to be digitized is a separate collection of materials from UNRWA’s Education Department in Amman. It contains around 1,000 video cassettes and other materials, including photos taken for educational purposes. Financial and staffing constraints have meant that digitizing that content has been delayed, and UNRWA has been seeking support to complete it as soon as possible.
+Making the archive widely available is as essential for UNRWA as preserving it.
+“The online archive is available to the public. At the end of the digitization project, UNRWA launched its online photo archive located at unrwa.photoshelter.com. It contains tens of thousands of historical and content photos as well as films. It was launched in September 2016. Since that time, anyone can go online to see what we have there. We started off with only about 2,000 photos, but now we have about 40,000,” said Amani.
+Public availability is not just something that matters for its own sake – pictures also tell a story for a cause.
+“The archive is an essential tool for communication and fundraising for UNRWA. People want to see more than they want to read,” said Amani, reflecting on how content consumer habits have changed over the years.
+UNRWA’s digitized content is stored on dark disks and backed up in the cloud.
+“So, everything we have in the archive is safe and secure and preserved for the next generation,” said Amani.
+But what about UNRWA’s physical archive amid the war in Gaza? It was located at the agency’s offices in Gaza City, from which staff had to pull out at the start of the war in October. Over 170 UNRWA buildings have been damaged since then. The situation is highly uncertain.
+“What is the reality today? The availability and condition of the materials? I don’t have the answer now,” said Amani. “It means a lot to me. What’s happening is beyond our worst fears and imagination, and that includes the fate of the archive.”
+This item was first published in This Week in Palestine, Click here.</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:08:26.578990+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>UNRWA Department of Health Annual Report 2023 [EN/AR] - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/unrwa-department-health-annual-report-2023-enar</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Palestine Refugees face unprecedented health challenges to amid Gaza war: UNRWA Annual Health Report
+AMMAN,
+Palestine Refugees in the Gaza Strip are facing an unprecedented health emergency caused by the most devastating war in their history, according to UNRWA’s 2023 Annual Health Report, released today.
+Across UNRWA’s five fields of operation - Jordan, Lebanon, the West Bank, including East Jerusalem, Gaza, and Syria - over two million patients depend on the Agency’s health services. Despite challenges to it operations, including defunding, UNRWA managed to deliver nearly seven million primary healthcare consultations in 2023, maintaining high levels of immunization, including in Gaza, which has played a crucial role in preventing outbreaks of vaccine-preventable diseases.
+“The health crisis among Palestine refugees can only be mitigated with immediate and sustained healthcare interventions and support. UNRWA remains committed to addressing these urgent needs and improving the health and wellbeing of Palestine Refugees,” said Dr. Akihiro Seita, UNRWA Director of Health.
+The war in Gaza has severely impacted the health and well-being of Palestine Refugees, with increased levels of injury, trauma, and mental health disorders. Destruction of infrastructure and transportation has further complicated healthcare delivery, while overcrowded living conditions and limited access to clean water have heightened the risk of infectious diseases. Rising cases of acute hepatitis and various forms of diarrhea have been reported. Additionally, malnutrition has worsened, with one in three children under the age of two in northern Gaza suffering from acute malnutrition.
+In the last quarter of 2023, healthcare access declined as 14 of 22 health centres had to cease operating and power outages crippled telehealth systems. In response, UNRWA opened 155 emergency shelters and deployed 108 mobile medical units, coordinated the shipment of essential medicines, and implemented disease outbreak surveillance.
+“Our staff remained at the frontline in Gaza, as of May 2024, UNRWA has lost over 191 staff members, including 11 healthcare professionals. Our hearts go out to the affected families. This report underscores our gratitude for the dedication of our healthcare staff, who continue to deliver quality services despite their loss and being displaced several times,” noted Dr. Seita.
+In the West Bank, meanwhile increased movement restrictions and rising violence have posed additional challenges. UNRWA adapted by finding temporary solutions to ensure access for patients and that medical supplies were delivered without interruption.
+ENDs –
+Notes to Editors
+- Maternal and child healthcare remained a priority, with extensive services provided. Meanwhile, non-communicable diseases like cardiovascular diseases, diabetes, and hypertension continued to rise due to lifestyle factors. Communicable diseases were largely controlled through vaccination and outbreak management, but hygiene-related diseases reemerged in Gaza towards the end of 2023, after the war broke out in October. Mental health issues also increased due to ongoing conflict and economic instability, despite mental health and psychosocial support services being integrated in all health centres.
+- UNRWA’s focus on technology was demonstrated by a significant increase in the utilization rate of the Non-Communicable Diseases Mobile Application (e-NCD) and the Maternal and Child Health Mobile Application (e-MCH).
+Background Information:
+UNRWA is the United Nations Relief and Works Agency for Palestine Refugees in the Near East. The United Nations General Assembly established UNRWA in 1949 with a mandate to provide humanitarian assistance and protection to registered Palestine refugees in the Agency’s area of operations pending a just and lasting solution to their plight.
+UNRWA operates in the West Bank, including East Jerusalem, The Gaza Strip, Jordan, Lebanon and Syria.
+Tens of thousands of Palestine refugees who lost their homes and livelihoods due to the 1948 conflict continue to be displaced and in need of support, nearly 75 years on.
+UNRWA helps Palestine Refugees achieve their full potential in human development through quality services it provides in education, health care, relief and social services, protection, camp infrastructure and improvement, microfinance, and emergency assistance. UNRWA is funded almost entirely by voluntary contributions.</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:08:32.551327+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Press Conference (Transcript as Delivered) UNRWA Commissioner-General Philippe Lazzarini (Beirut, 27 May 2024) [EN/AR] - Lebanon</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/press-conference-transcript-delivered-unrwa-commissioner-general-philippe-lazzarini-beirut-27-may-2024-enar</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>27 May 2024
+Beirut
+Thank you and good morning.
+First of all, it is my first visit in a few months here in Beirut. I would have come earlier but as you all know Gaza and the issues related to the agency have taken a lot of my time but let me start first by thanking you for the coverage of the situation here in the region.
+Now, I just met the Prime Minister Mikati this morning.
+Basically, we were first talking about the situation in Rafah.
+You see how dramatically the situation is evolving.
+We have already more than 1 million people who have been recently displaced.
+Again, half the population of Gaza has been forced on the road and we are struggling to bring supply to the Gaza Strip, and you also saw last night again disturbing images of people, of mass casualties, and reportedly that even (areas sheltering displaced families) were on fire and number of people have been killed.
+Unfortunately, we have not been in contact yet because of the telecommunications difficulties with our team on the ground.
+We will certainly be able to report more later on.
+Now, we also discuss the overall financial situation of the agency.
+As you know, we are basically functioning hand-to-mouth on a monthly basis.
+The agency has been severely weakened by the financial crisis over the last few years, but it has also been accelerated in return at the time of the allegation that 12 staff might have participated in the horrible massacre of October 7.
+At that time, you might remember 16 donors announced the freeze.
+At that time, we have also taken a number of decisions.
+The first decision was to terminate the contracts (of those staff).
+The second one, to open an independent investigation.
+And the third one, to ask former Minister of Foreign Affairs of France Catherine Colonna with the support of three Scandinavian institutes to look at all the risk management system and mechanisms of the agency.
+You remember the outcome of this review was that the agency, as robust mechanism, is above the average of any other United Nations agencies in the region, but because of our footprint, because of the complex political environment, there are still a number of measures the agency can take, and this is what the Secretary General and myself have agreed to implement.
+Now, since then, 14 donors – all the EU members, Japan, Australia, Canada have resumed their contribution to the agency.
+And today, the only large donor missing is the United States, who have informed and announced that there will be no resumption before March 2025, and we have also the United Kingdom which has not yet announced its resumption.
+So, all this to say that the situation remains financially precarious, but I have also told the Prime Minister that we will do whatever possible to keep all our activities running across the region including in Lebanon.
+Now, we also discussed with the Prime Minister the attacks the agency is under.
+We, as you know, already in Gaza the United Nations including UNRWA has been blatantly disregarded.
+The number of UNRWA staff members who have been killed is unprecedented, 192 as of today, in addition to the number of premises which have been damaged or fully destroyed, the number of convoys which have been prevented or attacked.
+And besides that – beyond that – we have also complaints going on to label the agency as a terrorist organization or to push the agency not only out of Gaza but also out of Jerusalem.
+But we are not only under pressure there, I also raised a point with the Prime Minister that even here in Beirut we are under pressure.
+For more than two months, our personnel and staff have not been allowed to access the (UNRWA) headquarters (in Beirut).
+It reopened only last Friday with a one-week window.
+This is not acceptable.
+This is the United Nations, and United Nations personnel (should and) need to have access at any time to all its premises to make sure that services are provided to the population.
+Now, we also know that the situation in the camps (in Lebanon) is very dire.
+Poverty has reached skyrocketing proportions.
+And we also (know) that education has been too frequently disrupted in the camps.
+It is of utmost importance that the agency be able to continue to fulfill its mandate, and to support, assist, and protect Palestine Refugees, not only here in Lebanon but also the region.
+We should never forget that many of the attacks the agency is under are ultimately aimed at stripping the Palestinian refugees from their rights, and we have to push back.
+But incurring actions like the ones we see here are also undermining the ability of the agency to properly operate.
+I heard from many staff how this is impacting the day-to-day life of the people in the camps, and I really hope that during my two days we will address this issue because this is what we owe to the Palestinian refugees in the camps here in Lebanon.
+Thank you.
+Background Information:
+UNRWA is the United Nations Relief and Works Agency for Palestine Refugees in the Near East. The United Nations General Assembly established UNRWA in 1949 with a mandate to provide humanitarian assistance and protection to registered Palestine refugees in the Agency’s area of operations pending a just and lasting solution to their plight.
+UNRWA operates in the West Bank, including East Jerusalem, The Gaza Strip, Jordan, Lebanon and Syria.
+Tens of thousands of Palestine refugees who lost their homes and livelihoods due to the 1948 conflict continue to be displaced and in need of support, nearly 75 years on.
+UNRWA helps Palestine Refugees achieve their full potential in human development through quality services it provides in education, health care, relief and social services, protection, camp infrastructure and improvement, microfinance, and emergency assistance. UNRWA is funded almost entirely by voluntary contributions.
+FOR MORE INFORMATION, PLEASE CONTACT:
+UNRWA on Twitter: @UNRWA
+Email: media@unrwa.org</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:08:38.580024+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>UNRWA Education 2030: Baseline Report - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/unrwa-education-2030-baseline-report</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Executive Summary
+The United Nations Relief and Works Agency for Palestine Refugees in the Near East (UNRWA) is a relief and human development agency mandated by the UN General Assembly (UNGA), since 1949,which provides assistance and protection for Palestine Refugees within its five Fields of operation: Gaza, the West Bank, including East Jerusalem, Lebanon, Syria, and Jordan. UNRWA services for Palestine Refugees include primary and vocational education, primary health care, relief and social services, infrastructure and camp improvement, microfinance, and emergency response.
+UNRWA is unique in that it is a United Nations agency and the primary direct education provider for Palestine Refugees within its five Fields of operation. The Agency operates one of the largest school systems in the Middle East, providing free basic education to over half a million Palestine refugee children and youth in its five fields of operation, as well as secondary schooling for Palestine Refugees in Lebanon. The Agency provides postsecondary education for approximately 10,000 Palestine Refugees across the region through its eight Vocational Training Centres and two teacher training institutes located in the West Bank and Jordan.
+The report highlights the Agency’s successes and challenges in relation to the Education 2030 Agenda, based on the SDG4 indicators. UNRWA’s education targets and indicators are mapped against those of SDG4, and then the Agency’s performance is assessed against each of these ten targets (7+3). Where possible, contrast is provided between Agencywide achievements and those within UNRWA’s five Fields of operation. Where data is available, UNRWA’s educational achievements are contrasted with regional and global benchmarks.
+Unique amongst United Nations agencies mandated by the UN General Assembly (UNGA), UNRWA is a direct provider of education for refugees. In terms of a single agency managed system, UNRWA operates one of the largest school systems in the Middle East, and education is the largest of UNRWA’s programs, both in terms of staff engaged (70 per cent of total Agency staff) and budgetary allocation (59 per cent of the total regular budget). Moreover, the vast majority of UNRWA’s 20,000 educational staff (including nearly 17,000 fulltime teachers, 2000 daily paid teachers and 500 vocational training instructors) are Palestine Refugees themselves.
+The vision of UNRWA’s education system is to foster human capital and enable Palestine Refugees to achieve their full potential under the difficult circumstances in which they live (MTS 2023-2028). Over seventy-five years, UNRWA has built a solid reputation for excellence in providing education that has been recognised as being equal to, if not better than, that of countries hosting Palestine Refugees. UNRWA has produced approximately 132,000 TVET graduates who have gone on to work in a variety of employment fields.
+UNRWA’s education program operates within a complex regional and global context. Whilst coordinating effectively with national governments hosting Palestine Refugees, the Agency also harmonizes with regional bodies and the global education community to provide quality education services for Palestine Refugees. Where possible, UNRWA has aligned the targets and indicators of its strategic plan 2023-2028 to the UN Sustainable Development Goals (SDGs), including SDG4 – Quality Education.
+To date, UNRWA has not been a member of a dedicated forum where its achievements and lessons learned could be shared with the international community, nor has its data been well integrated into national systems or well included in regional and global reporting on the achievement of SDG4 targets.
+This baseline report is an opportunity for UNRWA to connect to the global monitoring of education and share its progress and challenges with the international community in relation to the achievement of the Education 2030 Agenda. The Agency’s education targets and indicators are mapped against SDG4, and its performance is assessed against each of the ten targets (7+3). Where possible, contrast is provided between the five Fields of operation so that Agencywide achievements do not overshadow discrepancies within the system. Again, where possible, a comparative analysis is made between UNRWA’s educational achievements and regional and global benchmarks as reported by UNESCO’s global education monitoring mechanisms (e.g. Global Education Monitoring Report), as well as other respected data sources. The report reveals that UNRWA has made substantial progress towards the achievement of some of the SDG4 targets.
+Target 4.1 (Universal primary and secondary education): Despite the covid-19 pandemic, in 2022 the agency shows a survival rate to the end of basic education of nearly 96 per cent , and a cumulative drop out of 0.86 per cent at elementary and 2.83 per cent in preparatory. However, the results of the assessment of learning outcomes call for more effort to reverse the learning loss, a global trend that has been amplified by the pandemic: less than 30 per cent of grade 4 and 8 students achieved minimum proficiency in Arabic and, 22 per cent in grade 4 and 16 per cent in grade 8 achieved the minimum proficiency in mathematics.
+Target 4.2 (Access to quality early childhood development, care and pre‑primary education): UNRWA does not provide early childhood education.
+Target 4.3 (Equal access to technical/vocational and higher education): UNRWA operates 8 vocational training centres and two faculties of education (teachers training institutions). In 2022/23, 7811 refugees were being trained in the VTCs (45 per cent are women) and 2051 in the teacher training institutes.
+Target 4.4 (Relevant skills for decent work): In 2022, the employment rate for graduates from VTCs was 79 per cent and of 88 per cent from the faculties.
+Target 4.5 (Gender equality and inclusion): in 2022, UNRWA nearly achieved gender parity in relation to completion rate for basic education (94 per cent for males and 97 per cent for females). However, less than 60 per cent of students identified with disability received support meeting their specific needs (58.6 per cent for females and 53.4 per cent for males). Between fields of operations, disparities exists in the achievements under each SDG4 target that are attributable to the influence of national and specific contexts of host countries in which UNRWA operates.
+Target 4.6 (Youth and adult literacy and numeracy): UNRWA does not have households-based surveys to measure adult literacy and numeracy levels of its population.
+Target 4.7 (Education for sustainable development and global citizenship): UNRWA education program uses host country school curricula. The agency has no mandate to alter curriculum or textbooks of host governments but has put in place a robust review system to ensure that curricula taught in its schools adhere to UN principles and values and reflects its educational approach of critical thinking and human rights education.
+Target 4.a (Effective learning environments): UNRWA premises suffer from under-resourcing and increasing demographic pressure; in some fields they have incurred further deterioration due to conflicts. UNRWA uses rented premises and operate schools on double or triple shifts base across its five fields of operation.
+Agencywide in 2023, more than half of schools (54 per cent ) where operating on double or triple shift modality with large disparities between the fields (83 per cent in Jordan, 71 per cent in Gaza, 57 per cent in Syria against 2 per cent in West Bank and 3 per cent in Lebanon). More than 50 per cent of classes have more than 40 students. This proportion remained stable since 2019.
+Target 4.b (Scholarships): Support to scholarship through UNRWA general fund was discontinued since 1997. Current scholarships are provided by donors since 2000 but are not enough to absorb the needs for the increasing number of students who need financial support to pursue their studies.
+Target 4.c (Teachers and educators): UNRWA provides training opportunities for teachers in its two faculties and has put in place continuous professional development program particularly for the newly recruited teachers. Out of its 18 thousand teachers, only 113 (0.6 per cent ) have no degree, and this number will decrease to zero in next years. Also as of 2022, 1,319 teachers had not yet completed an accredited initial teacher training program (724 females and 595 males)- a requirement to be recruited as per the agency policy. That is 7 per cent of teacher workforce is qualified but not trained.
+The report identifies digital transformation and strengthening of EiE data for crisis planning as among UNRWA’s strategic priorities to accelerate progress towards the achievement of SDG4 by 2030.
+It is hoped that by sharing UNRWA’s successes and challenges in relation to SDG4, this report will make a valuable knowledge contribution to the global education community and guide future collaborations.</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:08:44.611760+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>UNRWA Updated oPt Flash Appeal (April – December 2024) - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/unrwa-updated-opt-flash-appeal-april-december-2024</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>This is the second revision of the UNRWA Flash Appeal for the occupied Palestinian territory (oPt), covering the period April – December 2024. UNRWA is seeking US$ 1.21 billion to address the most critical humanitarian needs of 1.7 million of the most vulnerable refugees and non-refugees in Gaza, as well as over 200,000 individuals in the West Bank, including East Jerusalem. This appeal comes in response to the ongoing and unprecedented escalation of conflict and resulting needs in the Gaza Strip and the West Bank. It outlines the resource requirements to reduce suffering and prevent further loss of life.
+The entire 2.3 million population of the Gaza Strip is in need, on the brink of famine. Most health, water and shelter infrastructure has been flattened or placed out of commission by Israeli military operations and denial of access.</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:08:51.091319+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Belgium signs new EUR 27.5M agreement with UNRWA [EN/AR] - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/belgium-signs-new-eur-275m-agreement-unrwa-enar</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>19 April 2024
+EAST JERUSALEM,
+Belgian Minister of Development Cooperation Caroline Gennez has signed a new multi-year funding agreement with UNRWA, totaling EUR 27.5 million over the next three years.
+"UNRWA is currently the only aid agency in Gaza that has enough staff and infrastructure on the ground to get humanitarian aid to the people of Gaza. If the agency runs out of funds, the lives of tens of thousands of innocent people will be at stake," Minister Gennez said.
+Belgium's new multi-year agreement will cover the 2024-2026, including a EUR 13.5 million contribution for 2024, and EUR 7 million for each remaining year. Critically, the entire EUR 27.5 million is fully flexible, enabling UNRWA to choose how to spend it. This will help the Agency rapidly and comprehensively to address the most critical needs across its programme budget, emergency appeals, and projects in all five fields of operation -- not only in Gaza, but also the West Bank, including East Jerusalem, as well as Lebanon, Syria, and Jordan.
+"We sincerely thank the Government of Belgium for yet another meaningful milestone in our long-standing cooperation, and invaluable political support Belgium has provided to UNRWA and Palestine Refugees throughout this horrendous conflict," said UNRWA's Director of Partnerships Karim Amer.
+"We welcome Belgium's prompt disbursement of our new agreement's 2024 contribution. The true value of fully flexible funds cannot be overstated, as the Agency continues to work tirelessly to respond to the most urgent needs of Palestine Refugees in the occupied Palestinian territory and beyond."
+ENDs --
+Notes to Editors
+- Belgium has long been a strong supporter of UNRWA and remained in the Agency's top 20 donors as of 2023. It first introduced a fully flexible additional contribution of EUR 2 million in 2023, following the start of the war in Gaza.
+- Belgium's most recent multi-year agreement provided programme budget contributions of EUR 7 million per year for 2021-2023.
+- Belgium has remained a member of the UNRWA Advisory Commission since 1953, four years after UNRWA was created by the UN General Assembly.
+Background Information:
+UNRWA is the United Nations Relief and Works Agency for Palestine Refugees in the Near East. The United Nations General Assembly established UNRWA in 1949 with a mandate to provide humanitarian assistance and protection to registered Palestine refugees in the Agency's area of operations pending a just and lasting solution to their plight.
+UNRWA operates in the West Bank, including East Jerusalem, The Gaza Strip, Jordan, Lebanon and Syria.
+Tens of thousands of Palestine refugees who lost their homes and livelihoods due to the 1948 conflict continue to be displaced and in need of support, nearly 75 years on.
+UNRWA helps Palestine Refugees achieve their full potential in human development through quality services it provides in education, health care, relief and social services, protection, camp infrastructure and improvement, microfinance, and emergency assistance. UNRWA is funded almost entirely by voluntary contributions.
+**Your support is crucial to help us provide emergency aid **
+to displaced families in Gaza
+FOR MORE INFORMATION, PLEASE CONTACT:
+UNRWA on Twitter:  @UNRWA
+Email:  media@unrwa.org</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:08:57.340513+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2024 Syria, Lebanon, and Jordan Emergency Appeal [EN/AR] - Syrian Arab Republic</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/syrian-arab-republic/2024-syria-lebanon-and-jordan-emergency-appeal-enar</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2024-04-03</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>UNRWA launches US$ 415.4 million appeal for Palestine refugees in Syria, Lebanon, and Jordan
+BEIRUT,
+UNRWA is urging its partners to continue supporting Palestine Refugees in Syria, and those who have fled to neighbouring Lebanon and Jordan as a result of the 13-year conflict in Syria. The Agency is appealing for US$ 415.4 million to support its chronically underfunded operations in these three countries.
+“We must continue to support Palestine Refugees affected by the 13-year-long Syria crisis. While the horror unfolding in Gaza is consuming most of our attention, humanitarian needs in other crisis-affected areas of operations should not be overlooked,” said Natalie Boucly, UNRWA’s Deputy Commissioner-General for Programmes and Partnerships, who launched the appeal in Beirut.
+UNRWA has a long-standing humanitarian assistance programme to mitigate the worst effects of the conflict in Syria on Palestine Refugees, and to address the deteriorating socio-economic conditions of hundreds of thousands of vulnerable Palestine Refugees in Lebanon and Jordan.
+With funds received through this appeal, UNRWA will continue cash and in-kind food assistance, together with health care, education, technical and vocational training.
+Despite the growing needs, funding for UNRWA’s emergency appeals for Syria, Lebanon, and Jordan decreased over recent years, with a dramatic fall to only 27 per cent coverage in 2023.
+In 2021, just over half of the funding was covered, while it went down to 40 per cent in 2022.
+“UNRWA’s overall funding situation remains precarious, especially given the challenges it has faced since the conflict in Gaza started. With significant funding gaps impeding its ability to implement its mandate, UNRWA will soon struggle to maintain the level of humanitarian assistance it can provide, and that level is already at minimum,” said Natalie Boucly.
+“As the Palestine Refugee community faces even greater existential challenges across the region, UNRWA’s role has never been more vital,” she added.
+ENDs –
+Notes to Editors
+UNRWA, which is the backbone of the international humanitarian response in Gaza, is scheduled to launch a separate appeal later this month for its operations there and in the West Bank. In response to escalating poverty among Palestine Refugees, UNRWA's humanitarian effort under its 2023 emergency appeal focused on distributing cash assistance to over 611,000 individuals. This included three rounds of cash assistance for 416,519 people in Syria; support for all 30,171 Palestine Refugees from Syria residing in Lebanon, and 144,280 other vulnerable Palestine Refugees in Lebanon; and for 20,219 Palestine Refugees from Syria in Jordan. The details of the 2024 emergency appeal for Syria, Lebanon, and Jordan are as follows:
+Syria
+- In Syria, Palestine Refugees are one of the most vulnerable groups in a country where two-thirds of the population need humanitarian assistance after 13 years of conflict.
+- Some 438,000 Palestine Refugees are estimated to remain in Syria, with about 40 per cent of them displaced and more than 90 per cent living below the poverty line, on less than US$ 2.15 per day. Almost two-thirds of the household expenditure of Palestine Refugees goes towards purchasing food alone.
+- The devastating impact of the February 2023 Türkiye earthquakes on northern Syria, coming so soon after the 2022 cholera outbreak and the COVID-19 pandemic, heaped further misery onto their already desperate situation.
+- UNRWA’s most critical work in 2024 for Palestine Refugees in Syria includes emergency cash assistance for 420,000 people; in-kind food assistance for 155,500 people; shelter repair and rehabilitation of damaged UNRWA facilities; short-term cash for work; psychosocial counselling, education in emergencies; emergency health support; and water, sanitation, and health in camps.
+Lebanon
+- Amid Lebanon’s continued economic crisis, poverty rates among Palestine Refugees there are around 80 per cent. Their pressing needs have outpaced UNRWA’s ability to respond and mitigate their lack of access to basic services.
+- At least 168,000 Palestine Refugees in Lebanon rely on the Agency for emergency, multi-purpose cash distribution to improve food security and cover basic living expenses.
+- Rising tensions on Lebanon's southern border are raising fears within the Palestine Refugee community, in particular for those residing in the 12 refugee camps across the country.
+- Last year, heavy violence among Palestinian factions in Ein El Hilweh, Lebanon’s largest Palestine Refugee camp, had a devastating impact on the livelihoods of the community, damaged UNRWA schools and forced the Agency to set up temporary facilities outside the camp for thousands of students.
+- Palestine Refugees from Syria face ever more difficult circumstances, due to expiring civil documentation and an inability to obtain residency and employment permits, leading to a near total dependency on UNRWA’s cash assistance for rent and food.
+- UNRWA’s appeal aims to help meet basic needs including cash assistance for food, rent and winterization for 23,200 Palestine Refugees from Syria and 144,000 other Palestine Refugees in Lebanon, as well as emergency health and education in emergencies.
+Jordan
+- Although Jordan remains stable, socio-economic conditions have markedly declined. In June 2023, the World Bank reclassified the country as lower-middle income status. Over one-third of Jordanians currently live below the poverty line.
+- This is further exacerbated by the pressure of declining international humanitarian assistance to the country that, in 2023, hosted the second highest number of refugees per capita in the world.
+- Deteriorating socio-economic conditions significantly impact Palestine Refugees from Syria, of whom 20,084 are registered with UNRWA. They are one of the most vulnerable groups in Jordan – without legal documentation they cannot access formal employment, leaving many reliant on informal and precarious work and humanitarian assistance.
+- UNRWA provides Palestine Refugees from Syria in Jordan with emergency cash assistance, health, and education services. The Agency works to improve environmental health – including public sanitation services – in the 10 Palestine Refugee camps across the country.</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:09:03.382819+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>UNRWA: EUR 45 million in new contributions from Germany for services to Palestine Refugees in Jordan, Lebanon, Syria and the West Bank - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/unrwa-eur-45-million-new-contributions-germany-services-palestine-refugees-jordan-lebanon-syria-and-west-bank</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>UNRWA welcomes an announcement by the Government of Germany that it is providing EUR 45 million in new contributions to the Agency's work in Jordan, Lebanon, Syria and the West Bank.
+"With these new contributions, Germany is now our top donor, something I am deeply grateful for. Germany's solidarity with UNRWA is a proof of its commitment to contributing to the human development of Palestine Refugees, and to their right to a dignified life," said UNRWA Commissioner-General Philippe Lazzarini.
+The new funds include EUR 15 million to support essential health and education services to Palestine Refugees in Jordan and Lebanon, and EUR 7 million for cash-for-work activities for Palestine Refugees in Lebanon, both from the Federal Ministry for Economic Cooperation and Development (BMZ). In addition, they will include EUR 23 million for emergency cash assistance to Palestine Refugees in Jordan, Lebanon, and Syria, and for general food assistance in the West Bank, from the Federal Foreign Office.
+Additional support by Germany to UNRWA, namely for its operations in the Gaza Strip, will depend on the progress of an ongoing investigation by the UN Office of Internal Oversight Services into allegations made by the Israeli Authorities against 12 of UNRWA's 30,000 staff, as well as on the results and recommendations of a separate Independent Review of the Agency.
+ENDs --
+Notes to Editors
+- Germany has been a dedicated supporter of UNRWA since 1952 and is the Agency's second largest donor globally, with a total of EUR 197 million provided in 2023.
+- In 2023, Germany was the largest donor for emergency food aid in Gaza with a total of EUR 81 million as well as the largest contributor to the Emergency Appeal for Syria, with EUR 30 million.
+- With the new contributions announced by BMZ and the Federal Foreign Office, Germany's total support for UNRWA will reach EUR 48 million so far for 2024.
+- Germany has been a member of the UNRWA Advisory Commission since 2005.
+Background Information:
+UNRWA is the United Nations Relief and Works Agency for Palestine Refugees in the Near East. The United Nations General Assembly established UNRWA in 1949 with a mandate to provide humanitarian assistance and protection to registered Palestine refugees in the Agency’s area of operations pending a just and lasting solution to their plight.
+UNRWA operates in the West Bank, including East Jerusalem, The Gaza Strip, Jordan, Lebanon and Syria.
+Tens of thousands of Palestine refugees who lost their homes and livelihoods due to the 1948 conflict continue to be displaced and in need of support, nearly 75 years on.
+UNRWA helps Palestine Refugees achieve their full potential in human development through quality services it provides in education, health care, relief and social services, protection, camp infrastructure and improvement, microfinance, and emergency assistance. UNRWA is funded almost entirely by voluntary contributions.</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:09:09.420285+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>UNRWA launches Ramadan campaign against backdrop of Gaza emergency - 100 per cent of Zakat contributions go directly to people in need [EN/AR] - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/unrwa-launches-ramadan-campaign-against-backdrop-gaza-emergency-100-cent-zakat-contributions-go-directly-people-need-enar</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>More than 30,000 Palestinians have been killed in Gaza since the war began in October. Hunger has reached catastrophic levels, with over 90 per cent of the population facing acute food insecurity. In northern Gaza, parents are feeding their children animal fodder and native plants, leading to possible malnutrition and nutritional deficiencies. At least 10 children are reported to have died of dehydration malnutrition in the north in recent days.
+Against this background, UNRWA has launched its annual Ramadan campaign to provide much needed aid to the besieged Gaza Strip through emergency food assistance. Running until the end of the holy month of Ramadan, the campaign will provide 100 per cent of Zakat contributions direct to internally displaced people in the Gaza Strip who are facing starvation. Zakat contributions will also go to eligible Palestine Refugee families in the region through emergency food and cash assistance. As the single largest aid agency operating in Gaza, UNRWA is uniquely positioned to receive, transport and distribute aid to the more than 1.7 million displaced Palestinians in the embattled Strip, as well as across our four other fields of operation.
+"The people of Gaza and Palestine Refugees across the Middle East are entering the holy month of Ramadan amid a humanitarian catastrophe in Gaza, heightened violence in the West Bank, and serious economic challenges in Lebanon, Syria, and Jordan. Your support is needed to help UNRWA deliver much-needed humanitarian aid and critical services. 100 per cent of your donation will go to those in need. Please give generously and thank you for your support," said UNRWA Commissioner-General Philippe Lazzarini.
+To donate your Zakat today, click here.
+ENDs-
+Notes to Editors:
+- Learn more about the UNRWA Zakat program from our annual Zakat Impact Report for 2023.
+- UNRWA's Zakat Programme is in compliance with Sharia law:
+- 100 per cent distribution policy of Zakat, with no overhead fees deducted;
+- Endorsed by respected Islamic scholars, including from the al-Azhar and al-Aqsa mosques
+- Benefits eligible families, living in poverty and abject poverty, in the Gaza Strip, the West Bank, including East Jerusalem, Lebanon, Syria, Jordan;
+- Contributions are deposited into a separate, Islamic-banking compliant bank account at Safwa Islamic Bank.
+Background Information:
+UNRWA is the United Nations Relief and Works Agency for Palestine Refugees in the Near East. The United Nations General Assembly established UNRWA in 1949 with a mandate to provide humanitarian assistance and protection to registered Palestine refugees in the Agency's area of operations pending a just and lasting solution to their plight.
+UNRWA operates in the West Bank, including East Jerusalem, The Gaza Strip, Jordan, Lebanon and Syria.
+Tens of thousands of Palestine refugees who lost their homes and livelihoods due to the 1948 conflict continue to be displaced and in need of support, nearly 75 years on.
+UNRWA helps Palestine Refugees achieve their full potential in human development through quality services it provides in education, health care, relief and social services, protection, camp infrastructure and improvement, microfinance, and emergency assistance. UNRWA is funded almost entirely by voluntary contributions.
+**Your support is crucial to help us provide emergency aid **
+to displaced families in Gaza
+FOR MORE INFORMATION, PLEASE CONTACT:
+UNRWA on Twitter:
+@UNRWA
+Email:
+media@unrwa.org</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:09:15.467633+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Code of Ethics [EN/AR] - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/code-ethics-enar</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>1. unrwa mission statement
+The mission of the UNRWA is to help Palestine refugees achieve their full potential in human development under the difficult circumstances in which they live.
+In line with this mission, the Agency works towards five strategic outcomes:
+(a) Palestine refugees’ rights under international law are protected and promoted;
+(b) Palestine refugees’ health is protected and disease burden is reduced;
+(c) School-age children complete quality, equitable and inclusive basic education;
+(d) Palestine refugees’ capabilities are strengthened for increased livelihood opportunities; and (e) Palestine refugees are able to meet their basic human needs of food, shelter, and environmental health.
+2. introduction
+Ethical behaviour in the workplace is essential for us to deliver effective and efficient services to beneficiaries. An unethical workplace culture will have a negative impact on everyone. Focusing on the Agency’s mission and on meeting the needs of beneficiaries is a feature of an organization that has a culture of accountability. We must advance the Agency’s mission instead of focusing on individual achievements.
+In a culture of accountability, there is no expectation to have a rule for every situation. Rather, shared values guide decision-making and serve as the moral compass that informs our actions as new situations unfold. Ethically informed decision-making is facilitated by the Agency’s clear values.
+We should always bear in mind that how each of us behaves will determine our relationship with beneficiaries, donors, partners and colleagues, and impact the Agency’s reputation overall. Even one unethical act can undermine the Agency’s mission.
+Organizational culture is something that we shape together. It demonstrates who we are as an Agency, what we stand for, and how we achieve results</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:09:21.575896+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Syria, Lebanon and Jordan Emergency Appeal 2023: Progress Report for the Reporting Period 1 January - 30 June 2023 - Syrian Arab Republic</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/syrian-arab-republic/syria-lebanon-and-jordan-emergency-appeal-2023-progress-report-reporting-period-1-january-30-june-2023</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2023-12-16</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Executive Summary
+This Emergency Appeal 2023 progress report covers humanitarian interventions implemented by the United Nations Relief and Works Agency for Palestine Refugees in the Near East (UNRWA or “the Agency”) in Syria, Lebanon and Jordan from 1 January to 30 June 2023. It outlines the achievements made and challenges faced by the Agency in providing humanitarian aid to Palestine refugees in Syria and thousands of Palestinian refugees from Syria (PRS) residing in Lebanon and Jordan. Through this emergency appeal (EA), the Agency has also provided critical support to the most vulnerable Palestine refugees in Lebanon (PRL) and the most vulnerable Palestine refugees in Jordan (PRJ).
+As a result of multiple overlapping crises, humanitarian conditions in Syria continued to deteriorate during the first half of 2023. The Syrian population, including the estimated 438,000 Palestine refugees who live in Syria, is facing unprecedented social and economic hardship due to the conflict that entered its thirteenth year during the reporting period. According to the United Nations Office for the Coordination of Humanitarian Affairs (OCHA), 15.3 million people in Syria currently require humanitarian assistance, up from 14.6 million people in 2022. Palestine refugees remain one of the most vulnerable groups in Syria, with 96 per cent of this population (420,000 individuals) dependent on UNRWA’s emergency assistance, especially cash and food commodities.
+On 6 February 2023, Syria was faced with an additional humanitarian crisis as two major earthquakes in southern Türkiye caused major devastation in the north and north-west of the country, significantly affecting over 46,500 Palestine refugees. In response, UNRWA immediately launched a standalone Flash Appeal whose progress has been reported separately from this EA.
+The socio-economic and political crises that have hit Lebanon over the past few years have disproportionately impacted PRL and the 30,193 PRS residing in the country. With increasing pressure on Palestine refugee communities as their economic and financial situation deteriorated during the first half of 2023, violence inside the refugee camps and camp-adjacent areas increased, resulting in a number of operational challenges for the Agency. UNRWA remains the primary provider of humanitarian assistance and basic services for the majority of the Palestine refugee community in Lebanon, including PRS.
+In Jordan, the total number of PRS stands at 20,001. An increase in the number of PRS in the country over the past year has resulted in the Agency becoming more stretched in its ability to support the diverse needs of PRS who are experiencing prolonged displacement, increasing poverty and conflict-related psychological trauma.
+UNRWA wishes to thank all the donors that have generously contributed to the 2023 Syria, Lebanon and Jordan EA, allowing vital interventions to continue during the first half of the year. However, as of the end of June 2023, this EA was only 16 per cent funded, with just over US$ 70.1 million received out of a total requirement of US$ 436.7 million. The emergency services provided by UNRWA constitute the minimum support necessary to meet the critical needs of Palestine refugees affected by the protracted conflict in Syria and the most vulnerable displaced PRS and others in Lebanon and Jordan. Additional funding is urgently needed for the remainder of 2023 to ensure that humanitarian assistance is maintained to prevent more refugees falling into abject poverty and developing negative coping mechanisms.
+The UNRWA Response
+In the face of increasing poverty amongst Palestine refugees, UNRWA’s major humanitarian intervention under this EA, during the first half of 2023, was the distribution of cash assistance for essential needs to a total of 604,894 individuals: 416,377 in Syria, 168,516 in Lebanon, and 20,001 in Jordan.
+UNRWA delivered or subsidized 466,562 primary, secondary and tertiary health care consultations in Syria during the first half of 2023, exceeding the half-yearly target due to increased demand for UNRWA health services.
+In Lebanon, UNRWA responded to 103,608 primary health care patient visits and referrals to hospitalisation services. In Jordan, 9,569 consultations were provided to PRS through UNRWA's 25 primary health care centres, four mobile dental clinics and in the Jordan Health Aid Society (JHAS) clinic in Garden Camp (previously the King Abdullah Park), including referrals of secondary and tertiary cases to public and private hospitals.
+Of the 48,153 Palestine refugee students in Syria who were enrolled during the last semester of the 2022/23 school year, 42,729 were provided with psychosocial support (PSS), allowing them to better cope with the impact of crises. In Lebanon, 37,737 students were enrolled in UNRWA schools during the first half of 2023, including 4,426 PRS children. Under this EA, 14,015 children were provided with transportation subsidies covering the worst winter months, enabling them to attend school. In Jordan, UNRWA elementary and preparatory schools provided education to 1,079 PRS and Syrian refugee students during the 2022/23 school year. In addition, 55,567 students, including 516 PRS students, attended at least one PSS counselling session.
+In Lebanon, the Palestine refugee community witnessed a significant incidence of gender-based violence (GBV), as evidenced by the 93 reported cases to UNRWA during the reporting period. This surge mainly affected women and girls, underscoring the profound impact of deteriorating socio-economic conditions.
+The Impact of Underfunding
+As a result of funding shortages and lengthy international food procurement procedures, no food distributions were carried out in Syria during the first six months of the year, posing a risk of more Palestine refugee households falling into food insecurity. In addition, funding shortages meant that cash assistance was maintained at the 2022 reduced level. For those classified as the most vulnerable, assistance remained at US$ 15 per person, per month instead of the planned US$ 33, and for the remaining vulnerable caseload it stayed at US$ 11 per person, per month instead of the planned US$ 23. In addition, funding gaps prevented UNRWA from providing Explosive Ordnance Risk Education (EORE) to Palestine refugee students, community members and Agency staff. Given high levels of explosive remnants of war (ERW) contamination, this remains a priority if EA funding is made available during the second half of 2023. Finally, only five of the targeted forty UNRWA installations (distribution centres, area office buildings and community centres) could be maintained through minor repair works.
+No funds were received during the first half of 2023 to provide cash assistance to 500 PRL families living in unsafe shelters, support that would have enabled them to carry out urgent repairs. Finally, maintenance works could only be completed at five of the targeted forty UNRWA installations (distribution centres, area office buildings and community centres) through minor repair works.</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:09:27.586570+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Invest to prevent violence against Palestinian refugee women and girls [EN/AR] - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/invest-prevent-violence-against-palestinian-refugee-women-and-girls-enar</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>AMMAN,
+The United Nations Relief and Works Agency for Palestine Refugees in the Near East (UNRWA) joins the global call for an end to gender-based violence under the United Nations Secretary-General’s 2023 UNiTE campaign: Invest to Prevent Violence against Women and Girls.
+Amidst the ongoing crisis in Gaza, with potential long-term consequences for women and girls, the Agency is resolute in standing against all forms of Gender-Based Violence (GBV) while marking this year’s 16 Days of Activism. Our commitment to ending violence remains unwavering as we come together during these difficult times to organise initiatives across the West Bank, including East Jerusalem, as well as in Lebanon, Syria, and Jordan. These events aim to raise awareness on the different forms of violence experienced disproportionately by women and girls and mobilise civil society to take a leading role.
+Given the current war, activities in Gaza will focus on emergency response initiatives tailored to address pressing needs identified in the Rapid Gender Analysis. Simultaneously, in the West Bank, where the Gaza war reverberates within the Palestine Refugee community, activities will centre around collaborating with the community and civil society to eradicate GBV.
+In Jordan, schools and community centres are set to host GBV activists to foster discussions around women's empowerment. In Syria, the emphasis will be on raising awareness and conducting focus group discussions on GBV. Meanwhile, in Lebanon, local organizations championing women's and girls' rights within the nine largest camps will unite in a march under the rallying cry, "اتحدوا ضد العنف #UNITE Against Violence."
+UNRWA’s Head of Gender, Amrita Kapur, emphasizes that in times of conflict, women and girls face heightened risks of gender-based violence. “The increase in GBV can be attributed to forced displacement, lack of access to health care and to community services. UNRWA is preparing tailored response efforts, incorporating internal staff training on GBV with a specialized focus on a survivor-centred approach, psychosocial support and addressing social norms and gender bias."
+"Six weeks into the war in Gaza, UNRWA is sheltering over one million internally displaced people in its schools and premises throughout Gaza. These shelters are hopelessly overcrowded, and the conditions are appalling, lacking the bare minimum of hygiene and privacy. This situation has deeply gendered impacts and particularly affects women and girls,” says UNRWA Commissioner-General Philippe Lazzarini. “We must work together to ensure that incoming aid promptly and effectively addresses their unique needs."
+UNRWA is dedicated to working with Palestine Refugee communities, persistently advocating for women's rights and advancing gender equality, especially in the current crisis.
+Background Information:
+UNRWA is the United Nations Relief and Works Agency for Palestine Refugees in the Near East. The United Nations General Assembly established UNRWA in 1949 with a mandate to provide humanitarian assistance and protection to registered Palestine refugees in the Agency’s area of operations pending a just and lasting solution to their plight.
+UNRWA operates in the West Bank, including East Jerusalem, The Gaza Strip, Jordan, Lebanon and Syria.
+Tens of thousands of Palestine refugees who lost their homes and livelihoods due to the 1948 conflict continue to be displaced and in need of support, nearly 75 years on.
+UNRWA helps Palestine Refugees achieve their full potential in human development through quality services it provides in education, health care, relief and social services, protection, camp infrastructure and improvement, microfinance, and emergency assistance. UNRWA is funded almost entirely by voluntary contributions.
+FOR MORE INFORMATION, PLEASE CONTACT:
+Lily Esposito
+[English / French language] European Media Requests
+Mobile: +972-54-240-2680 (WhatsApp preferred)
+UNRWA on Twitter: @UNRWA
+Website: UNRWA
+Email: l.esposito@unrwa.org
+Estefania Diaz
+[English / French / Spanish / German language] European Media Requests
+Mobile: +32-473-82-2006 (WhatsApp)
+On Twitter: @UNRWA_EU
+UNRWA on Twitter: @UNRWA
+Website: UNRWA
+Email: e.diaz@unrwa.org
+Asako Nitta
+[Japanese language] Japanese Media Requests
+Mobile: +972 54-240-2727
+UNRWA on Twitter: @UNRWA
+Email: a.nitta@unrwa.org
+Laurane March
+[English / Italian language] Global Media Requests
+Mobile: +962-7-9130-0567 (WhatsApp preferred)
+UNRWA on Twitter: @UNRWA
+Website: UNRWA
+Email: l.march@unrwa.org</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:09:33.612282+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Mr. Philippe Lazzarini, Commissioner-General remarks at the Advisory Commission on UNRWA [EN/AR] - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/mr-philippe-lazzarini-commissioner-general-remarks-advisory-commission-unrwa-enar</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2023-11-21</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>'As Delivered'
+Via Zoom from Cairo, Egypt
+21 November 2023
+Excellencies,
+Distinguished Members of the Advisory Commission,
+I would like to begin by thanking you for your support for the Agency during one of the darkest chapters in the region's history.
+Thank you to the Chair, Julieta Valls Noyes of the United States of America, for convening the AdCom at this critical time, as well as the Vice-Chairs, Mohamed Samir, Ambassador of Egypt to Jordan, and Ms. Henrike Trautmann.
+I welcome you to your new role in this forum and will rely on your leadership and support in the difficult weeks and months ahead.
+I would also like to thank Ms. Catherine Palmier, for continuing in her role as SubCom Chair, and Engineer Rafiq Khirfan of Jordan, and Mrs. Sirpu Tulla for continuing in your roles as Vice-Chairs of SubCom.
+Dear colleagues,
+I am addressing you during an unprecedented humanitarian catastrophe.
+In the aftermath of the horrific Hamas attacks that killed more than 1,200 Israelis and foreign nationals, around 13,000 people in Gaza have been killed according to the Palestinian Central Bureau of Statistics.
+More than two-thirds of those killed were reportedly women and children.
+108 UNRWA staff members are confirmed killed.
+We cannot even protect people under the United Nations flag.
+Nearly 67 UNRWA installations have been hit, 17 of those directly.
+Most of them were in the middle areas and in the south, where people were promised safety.
+176 displaced people sheltering in these installations were reported killed and at least 778 injured. This includes the most recent attacks on two UNRWA schools, which resulted in scores of additional deaths and injuries.
+The people of Gaza are not safe anywhere: not at home, not under the UN flag, not in a hospital, not in the North, and not in the South.
+1.7 million people -- almost 80 per cent of the population -- are displaced from their homes and moved into half of the Gaza Strip.
+More than 900,000 people are sheltering in UNRWA installations, including in the north.
+The conditions in these shelters are indescribable.
+They are massively overcrowded and shockingly unsanitary.
+On average, 150 people share a single toilet and 700 people share a single shower when available.
+These are breeding grounds for despair and disease.
+The misery resulting from bombardment is compounded by the effects of a brutal siege.
+Hunger and thirst are as widespread as fear and anxiety.
+Municipal services, including pumping sewage water, are failing.
+Telecommunications too.
+We are seeing signs of civil order breaking down, as people are compelled to fend for themselves.
+Everyone is terrified, especially children.
+Children who should be in our schools to learn, not shelter from bombs.
+In all this, UNRWA remains a lifeline for Gazans, thanks to the heroism of our staff on the ground.
+Some 5,000 staff members in Gaza continue to work each day.
+They live alongside the people they serve, and suffer the same deprivation, the same heartbreak.
+They are helping to stretch limited resources to provide food, water, and basic sanitation services.
+In addition to running shelters, our staff supply hospitals, bakeries, and desalination plants with the little fuel available.
+Despite our best efforts, however, the humanitarian response in Gaza is glaringly insufficient.
+Humanitarian aid is made conditional -- dependent on political negotiations.
+Aid workers are asked to be complicit in further displacing a population.
+Water, food, medicine, and fuel are being used as weapons of war.
+The trickle of aid allowed in does too little to address the immense needs of Gazans.
+The number of trucks that entered Gaza in the last month is roughly equivalent to the number that typically entered over two days before the war.
+The fuel allowed in by the Israeli Authorities only covers half the daily critical needs, compromising our entire aid operation and jeopardizing the survival of civilians.
+We continue to advocate for the opening of additional crossing points like Kerem Shalom to no avail.
+The siege is a collective punishment.
+Conditioning humanitarian assistance is also a collective punishment.
+Members of the Advisory Commission,
+The immediate challenges in Gaza should not overshadow the devastating, long-term impact of this conflict on Gaza's children.
+Across Gaza, schools have turned into shelters.
+The quality education UNRWA offered just weeks ago seems a distant dream.
+300,000 students and almost 2,000 trainees are missing out on education.
+For students in Gaza, this is the third year out of the last four that their education has been severely disrupted.
+First COVID, then short-term escalations, and now this life-altering crisis.
+Even if the conflict ends tomorrow, many of our schools are damaged or sheltering hundreds of thousands of displaced people.
+The education UNRWA provides has been shown to foster understanding, tolerance, cultural identity, and gender equality.
+But when my colleague Farid, who used to head our education programme in Gaza, meets his students in shelters, they ask him why UNRWA taught them about human rights and tolerance, when these principles do not apply to them.
+What should he tell them?
+UNRWA has developed a three-phase plan to support the reintegration of students into learning.
+It begins with mental health and psychosocial support, progresses to providing non-formal education, and finally facilitates the re-integration of students in formal education.
+But the implementation of this plan requires a ceasefire and funding.
+Without it, we could see Gazan children out of education for years.
+Dear colleagues,
+While all eyes are on Gaza, the situation in the West Bank, including East Jerusalem, is dangerously deteriorating.
+Violence has reached levels not seen in the last 15 years.
+Since October 7, 200 Palestinians, including 52 children, have been killed by Israeli forces, in addition to eight, including one child, by settlers.
+Israeli Forces are conducting daily incursions into refugee camps, with up to 40 raids per day.
+Rising settler attacks and movement restrictions have displaced more than 1,000 people in the West Bank since 7 October.
+Restrictions on the movement of people and goods have strongly impacted the economy.
+The situation is seriously undermining UNRWA's ability to deliver services, particularly education. Over 10,000 students in refugee camps in northern West Bank, Hebron H2, East Jerusalem and Jericho area are especially impacted.
+Fear and anxiety are growing among Palestinians who are increasingly subjected to harassment and violence, barred from employment, and denied free movement.
+Along the Israel-Lebanon border, clashes are intensifying.
+There are serious concerns that this could turn into a full-blown conflict.
+The tension in several Palestine Refugee camps in Lebanon has been simmering for years.
+The latest conflict between Palestinian factions in Ein El Hilweh refugee camp caused the displacement of 4,000 people. UNRWA schools, which provide education to nearly 6,000 children, were rendered unusable.
+This occurs amid unprecedented economic hardship for Palestine Refugees, who have virtually no economic prospects in the country, which itself is in a state of financial collapse and political paralysis.
+In Syria,
+Palestine Refugees are confronting one disaster after another.
+They have endured conflict, economic crises, and a devastating earthquake.
+The economy has collapsed, security is deteriorating, and the humanitarian situation keeps worsening.
+In Jordan, widespread protests are taking place across the country in solidarity with the people of Gaza.
+These protests happen against a backdrop of soaring poverty and unemployment rates. This has the greatest impact on the most vulnerable, including Palestine Refugees from Syria and those who came from Gaza in 1967.
+Members of the Advisory Commission,
+Since 7 October, the world has looked to UNRWA to protect and aid the civilian population in Gaza.
+The Agency has received many generous contributions towards its flash appeal.
+But the backbone of the Agency -- our core budget, our staff-- remains severely underfunded.
+Even now, amid the unprecedented violence in Gaza, the largest UN agency providing humanitarian support on the ground does not have yet enough funds to pay its staff until the end of the year.
+This is unacceptable. I call for you to carry us and our critical services until the end of the year.
+We must also ensure the availability of sufficient funds to discharge our obligations towards staff who have been killed, injured, and displaced in Gaza.
+This will be done through the payment of benefits to which they are entitled and other measures -- I very much welcome the advice and support of the Advisory Commission in this regard.
+This is the time to keep UNRWA strong.
+It is the time to enable its stabilizing effect in a highly volatile environment.
+With the calamity in Gaza, alarming violence in the West Bank, protracted conflict in Syria, fragile stability in Jordan and the near collapse of Lebanon, this is the time to stand firmly with UNRWA, which remains a beacon of hope amidst despair and destruction.
+During previous Advisory Commission meetings, I repeatedly stressed how the de-prioritization of the Israeli-Palestinian conflict has translated into the chronic underfunding of UNRWA.
+On 6 October, the Agency was already so weakened that it was heading towards financial implosion.
+Yet, since then, UNRWA has established itself as the most authoritative international voice on the tragic situation in Gaza.
+This is primarily thanks to our staff on the ground and colleagues supporting them.
+States, the media, and political analysts have all sought UNRWA's views, figures, and policy advice.
+They all recognize that with its huge footprint in the local community, UNRWA is a pillar of strength for civilians in Gaza.
+But to play this stabilizing role in Gaza and beyond, UNRWA requires a sustainable model with predictable and sufficient income.
+Over the last two years, I have put forward several solutions, none of which have been the game-changer that Palestine Refugees, Host Countries and the region need.
+Now more than ever, I strongly urge you as Members of the Advisory Commission to step up, be bold and help define solutions that ensure a stable and predictable UNRWA which remains the international community's greatest asset in the region.
+Dear colleagues,
+In conclusion, a war of narratives is being waged to dehumanize Palestinians and de-legitimize UNRWA.
+Disturbing references to Palestinians as "human animals" and calls for their expulsion from Gaza are attempts to normalize a disgraceful and dangerous rhetoric.
+It seems that extremists are joining forces to also undermine the Agency.
+Some accuse UNRWA of betraying the people of Gaza and facilitating the transfer of the population to the South.
+The other propagates insidious claims that our schools and employees teach hatred and violence.
+The Agency has spared no effort to ensure that its teaching promotes UN Values and UNESCO standards.
+It has invested heavily in training staff members to uphold humanitarian principles.
+All alleged breaches are investigated and dealt with promptly.
+It is absurd that alleged breaches by a few are allowed to tarnish the reputation of a UN Agency and more than 28,000 dedicated and professional staff.
+These obsessive attempts to discredit the work of the UN and its personnel are unacceptable and harmful.
+We cannot accept that a tragic humanitarian situation is manipulated to advance a political agenda.
+As Members of the Advisory Commission, I urge you to defend with conviction the Agency that you know so well.
+More than ever, we need you to safeguard your decades-long investment in the education of Palestine Refugees.
+More than ever, we must do all we can to assuage inflammatory language that entrenches islamophobia and antisemitism globally.
+Finally, Madam Chair,
+Every week we hold a memorial service at UNRWA to honor our colleagues killed. These were teachers, engineers, sanitation workers, nurses, doctors and more. According to our information, most were killed with their family members including their children. I never believed that as Commissioner General I would be planning memorial services for my staff in advance. This cannot continue.
+The present situation is dire. It can and will get much worse unless we act.
+We need an immediate humanitarian ceasefire.
+We need respect for international humanitarian law so civilians are protected, and humanitarian organizations can work unhindered.
+We need a meaningful supply of humanitarian aid and commercial goods flowing into Gaza. The siege must be lifted.
+We need sufficient fuel, on which the entire aid operation and the survival of the population depend.
+We need the support of the Advisory Commission to make it clear to the world that the attacks on UNRWA are baseless and malicious.
+We need immediate funds to continue our life-saving operations and end the vicious cycle of debt eroding the Agency.
+We need your leadership to ensure that UNRWA remains a strong, stable and predictable partner during this turbulent time.
+We need your political will to end the perpetual cycle of violence and to work together towards a Middle East where all people can co-exist, feel secure, and realize their rights and full potential.
+Thank you.
+ENDs-</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:09:39.714612+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>UNRWA Updated oPt Flash Appeal (November 2023) - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/unrwa-updated-opt-flash-appeal-november-2023</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Introduction
+The magnitude of the humanitarian crisis in Gaza is unprecedented. This updated UNRWA oPt Flash Appeal1 seeks US$ 481 million to cover the most critical humanitarian needs of an estimated 1.6 million people in Gaza, both refugees and non-refugees, and around 150,000 persons in the West Bank, for the period October – 31 December 2023.
+On 7 October, Palestinian armed groups launched attacks on Israel in which approximately 1,400 Israelis and foreign nationals were killed, including women, children and older people, and reportedly over 242 were taken hostage. The government of Israel subsequently launched a military offensive in Gaza with heavy and sustained bombardment, and a self-described siege.
+Regular water, fuel and electricity supplies to Gaza have been cut. Only minimal quantities of basic supplies have been permitted to enter since 21 October – food, medicines, water and relief items.
+According to the Ministry of Health, over 10,0002 Palestinians had been killed in the hostilities3 , of whom two-thirds are women and children, consistent with their share of the overall population. Amongst the dead are, as of 7 November 2023, 92 UNRWA personnel, many of whom died along with their families; many more UNRWA personnel are missing, possibly trapped beneath the rubble of buildings. Tens of thousands of people have been injured amid widespread damage to homes and public infrastructure. Within 16 days of the start of the conflict, at least 45 percent of Gaza’s housing stock had reportedly been destroyed or damaged4 . As of 5 November 2023, approximately 1.5 million people had been forcibly displaced within Gaza, or around 70 percent of the total population. An estimated 730,000 internally displaced persons (IDPs) are sheltering in 151 UNRWA facilities, of whom 570,000 have sought refuge in 94 installations in the Middle, Khan Younis and Rafah areas. Nearly 160,000 IDPs were sheltering in 57 UNRWA schools in the North and Gaza areas as of 12 October 2023, i.e. prior to an evacuation order issued by the Israeli authorities5 .
+The situation in the West Bank, including East Jerusalem, has also deteriorated significantly since 7 October, and is extremely volatile. An increase in the number of large-scale operations by Israeli forces and armed clashes between Israeli forces and Palestinians particularly in refugee camps, have resulted in record-high levels of fatalities, injuries, and high numbers of arrests. In this volatile and tense environment, widespread Israeli settler violence is also causing Palestinian casualties and placing Palestinian communities, including refugee communities, at risk of being displaced. Mobility restrictions in place throughout the West Bank since 7 October significantly constrain the movement of both Palestinian communities and humanitarian actors, preventing vulnerable Palestinians from accessing basic services, including healthcare and education.
+In Gaza, UNRWA is urgently seeking funding to cover the daily distribution of basic food rations (ready-to-eat meals) for 1.6 million people, including refugees and non-refugees in UNRWA shelters and other refugees in the community. Through this appeal UNRWA will also provide primary health care at Agency health centres and mobile medical points located in the shelters, which are equipped with emergency, trauma and delivery kits. Inside shelters, non-food items (NFIs), such as mattresses, blankets, kitchen sets and hygiene kits, will be provided for at least 800,000 IDPs.
+Furthermore, psycho-social support and recreational activities will be provided to IDPs sheltering at UNRWA facilities, particularly children. If the situation allows, other education in emergencies interventions, such as starting up temporary learning spaces, may be initiated. Displaced Palestine refugees hosted with families and friends in the community will also be supported through this Appeal, including with one-off multi-purpose cash assistance (MPCA).
+Many of the approximately 13,000 UNRWA personnel in Gaza, the majority of whom are themselves Palestine refugees, are working around the clock to provide humanitarian services assistance. UNRWA senior management continues to reach out to relevant parties to reiterate the neutrality and inviolability of all UNRWA premises and to advocate for unhindered humanitarian access, including safe passage for staff to deliver critical assistance to those in most need.
+The interventions planned for Gaza in this Appeal can only be implemented if the following planning assumptions are met (as outlined in the Inter-Agency Flash Appeal for the occupied Palestinian territory (oPt) prepared by OCHA)6 :
+i. Humanitarian actors must have safe and sustained access to all people in need, across the Gaza Strip and the West Bank.
+ii. Sufficient quantities of fuel must be made available to allow for humanitarian actors to function.
+iii. The flow of humanitarian assistance into Gaza must increase.
+iv. Funding must be timely and flexible to allow for humanitarian actors to adapt programming to a highly dynamic context.
+In the West Bank, including East Jerusalem, funds are needed to assist around 150,000 vulnerable Palestine refugees, including abject poor, residents of isolated communities and Palestinians from Gaza displaced to the West Bank, to meet their basic needs, through the provision of MPCA. The Agency will also extend basic healthcare services to around 80,000 Palestine refugees living in isolated and remote communities, which are impacted by heightened access restrictions.
+UNRWA will expand its protection response for vulnerable Palestine refugees, including women, children and displaced communities, and pre-position items and assets as preparedness actions ahead of the potential further deterioration of the security situation.
+Through this Appeal, UNRWA is also seeking funds for emergency preparedness measures in Lebanon, in anticipation of a potential mass displacement of Palestine refugees, particularly in the areas of Saida and Tyre, in the southern part of the country. Finally, funds are also sought for key coordination, support and technical positions at UNRWA HQ, in areas such as humanitarian affairs, protection, information management and emergency logistics, which are critical to support the Agency’s response in Gaza and the West Bank.
+The humanitarian needs in this document are also reflected in the OCHA Inter-Agency Flash Appeal for the oPt and will be updated as the situation evolves7 .
+This Flash Appeal replaces the Gaza component of the UNRWA 2023 Emergency Appeal (EA) and complements the West Bank and HQ components of the 2023 EA8 . The response in this Appeal can only be implemented if UNRWA also receives the necessary funding for its regular programme budget, which is the foundation for all Agency services in Gaza and all other fields of operation.</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:09:46.470989+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Remarks by UNRWA Commissioner-General Philippe Lazzarini to the United Nations General Assembly Fourth Committee [EN/AR] - occupied Palestinian territory</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/occupied-palestinian-territory/remarks-unrwa-commissioner-general-philippe-lazzarini-united-nations-general-assembly-fourth-committee-enar</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2023-11-04</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>04 November 2023
+As Delivered
+NEW YORK, 3 NOVEMBER 2023
+Introductory Remarks by Greta Gunnarsdottir, Director of the UNRWA Representative Office in New York
+Madame Chair,
+Distinguished Delegates,
+It is an honor to present to you, on behalf of the Commissioner-General of UNRWA, his annual report on the work of the Agency.
+The Commissioner-General is fully engaged in UNRWA's response to the humanitarian and human catastrophe in Gaza and sends his regrets for being unable to address you in person today.
+I will now turn to the Statement of the Commissioner-General.
+STATEMENT OF UNRWA COMMISSIONER-GENERAL PHILIPPE LAZZARINI
+Madam Chair,
+Distinguished Delegates,
+This session of the Fourth Committee comes at a time when the eyes of the world are on Israel and Palestine.
+As I told the United Nations Security Council on Monday:
+The last three weeks have been horrific. Almost everyone in Israel, the occupied Palestinian territory and the broader region is in mourning.
+The horrific attacks by Hamas in Israel on October 7th were shocking.
+The relentless bombardment by the Israeli Forces of the Gaza Strip is shocking.
+I was in Gaza two days ago for the first time since this conflict started.
+The day I spent with the UNRWA team on the ground was one of the saddest of my entire 30-year humanitarian career.
+I visited a school, hosting thousands of displaced persons. The place was overcrowded. The level of distress and the unsanitary living conditions were beyond comprehension. Everyone was asking for water and food. Instead of being at school to learn, children were asking for a sip of water and a loaf of bread. It was heartbreaking.
+The school I visited was damaged by bombardments. One person was killed and 80 were injured. Yesterday, four schools in Gaza, sheltering nearly 20,000 displaced persons, were hit during bombardments leading to the deaths of at least 23, and injuring at least 35.
+Since the beginning of the war, nearly 50 UNRWA buildings and assets have been impacted, with some being directly hit.
+Entire families moved to our shelters with the hope that they would be safe, in a UN building, under the UN flag.
+In my discussions with my staff in Gaza, they reported that basic services, including health care, are collapsing. Fuel, medicine, food and water are all running out.
+Depriving a whole population of items essential for survival is collective punishment. It is a violation of international humanitarian law.
+The streets of Gaza have started overflowing with sewage, which will cause a massive health hazard very soon.
+Recurring communications blackouts aggravate panic and distress among civilians.
+Madam Chair,
+We have lost 72 UNRWA colleagues in less than a month.
+It is the highest number of aid workers killed in a conflict in such a short time in the history of the UN.
+Like most Gazans, our staff have lost relatives, friends, neighbors and are themselves displaced with their families.
+And yet, at least 5,000 of my UNRWA colleagues in Gaza show up every day to work and operate 150 UNRWA shelters. They keep one-third of our health centers open and run 80 mobile health teams.
+They support the entry of humanitarian convoys and the storage and distribution of aid.
+They distribute the little fuel we have left to hospitals, bakeries and shelters.
+My UNRWA colleagues are a glimmer of hope for the entire Gaza Strip, a ray of light as humanity sinks into darkness.
+But they will soon be unable to operate if we do not act decisively now.
+Let me be clear -- a handful of convoys being allowed through Rafah does not make for a meaningful humanitarian operation, nor is it commensurate with the intense political and diplomatic shuttling that has been taking place.
+How is it that a near full siege is imposed for two weeks, then lifted ever so slightly to allow a trickle of aid, and no fuel in?
+The system in place to allow aid into Gaza is geared to fail unless there is political will to make the flow of supplies meaningful, matching the scale and magnitude of the needs of over two million people.
+It is my duty to bring to the attention of this Assembly that hunger, despair, and a feeling of abandonment are turning into anger against the international community. Gazans cannot comprehend how the world can watch this tragedy unfold without protecting and assisting civilians.
+I fear that their anger will soon shift towards the UN and UNRWA. In Gaza, the international community is better known as UNRWA.
+My colleagues in Gaza are warning against a breakdown in civil order - we saw the beginning of this when scores of people broke into UN warehouses on the day of a full communication blackout.
+We anticipate more such incidents if the UN does not live up to the expectation of people that it will protect and assist them. A breakdown of civil order will make it extremely difficult, if not impossible, for us to continue operating. It will also make it impossible to bring in convoys.
+I say this while being fully aware that UNRWA is the last lifeline for the Palestinian people in Gaza.
+Madam Chair,
+There is trouble brewing far beyond the borders of the Gaza Strip.
+The West Bank, including East Jerusalem, is simmering with tension, as violence has reached unprecedented levels not seen in the last 15 years.
+Rising settler attacks and movement restrictions have displaced over 800 people in the West Bank since October 7th.
+The Israeli military is conducting daily incursions into refugee camps.
+According to OCHA, the total number of Palestinians killed by Israeli forces or settlers since October 7th is 123, including 34 children.
+Street demonstrations are turning increasingly violent.
+Movement restrictions across the occupied territory are severely undermining UNRWA's ability to deliver services.
+Along the Israeli-Lebanese border, regular clashes and civilian casualties are reported.
+The situation inside several Palestine refugee camps in Lebanon has been boiling for years.
+The latest conflict between Palestinian factions in Ein El Hilweh refugee camp caused the displacement of 4,000 people and rendered UNRWA schools, which provide education to nearly 6,000 children, unusable.
+This came in the context of unprecedented economic hardship for Palestine Refugees, who have virtually no economic prospects in the country.
+There is a telling example from our own operations that captures the despair well: in July, UNRWA opened 13 vacancies for sanitation laborer posts.
+We received no less than 37,000 applications, including from refugees with university degrees.
+This shows how little opportunity there is for Palestine Refugees to lead a life of dignity and opportunity.
+In Syria,
+Palestine Refugees are confronting one disaster after another.
+They have endured the civil war, economic crises, a devastating earthquake, and now they risk further instability with an increasing number of reports of strikes on different actors' positions on Syrian territory as the region heats up.
+In Jordan, widespread protests are taking place across the country in solidarity with the people of Gaza.
+These protests are happening against a backdrop of soaring poverty rates and unemployment. This has the greatest impact on the most vulnerable - Palestine Refugees from Syria and those who came from Gaza in 1967.
+Distinguished delegates,
+We must immediately agree on urgent measures to tackle together.
+First, there must be strict adherence to international humanitarian law. Civilian infrastructure including humanitarian and UN facilities, particularly those sheltering civilians, must be protected wherever they are, North and South. Hostages must be released.
+Second, we need an immediate humanitarian ceasefire and the flow of humanitarian aid, including fuel, should be safe, unimpeded, substantial and continuous. And it should reach all people across Gaza.
+Third, for UNRWA to lead the humanitarian response in Gaza, we need adequate financial resources.
+UNRWA has received generous contributions towards its initial flash appeal.
+But without a fully-funded core budget -- the backbone of the Agency - we will not be able to pay the salaries of our staff, including those in Gaza, this month and next.
+With the alarming violence in the West Bank, the protracted conflict in Syria, the fragile stability in Jordan and the near collapse of Lebanon, THIS is the time to stand firmly with UNRWA, one of the most stable entities in an otherwise unstable region.
+Over the last 10 to 15 years, we have seen the Israeli-Palestinian conflict deprioritized by the international community.
+The political stagnation has translated into the chronic underfunding of UNRWA.
+On October 6th, the Agency was already so weakened that it was heading towards financial implosion.
+Yet, since October 7th, UNRWA has established itself as the most authoritative international voice on the tragic developments in Gaza. This is primarily thanks to the UNRWA staff that continue to work and report to us.
+UN Member States, the media, and political analysts have all sought UNRWA's views, figures, and policy advice.
+And they have all recognized that with its huge footprint in the local community, UNRWA is a pillar of stability for civilians in Gaza, if it can effectively play its humanitarian role.
+But to play its stabilizing role, in Gaza and beyond, UNRWA requires a sustainable model.
+Over the last two years I have put forward several solutions, but none have been the game-changer that Palestine Refugees, the Hosts and the region need.
+Now more than ever, I strongly urge Member States to step up, be bold and find concrete solutions for ensuring that a stable and predictable UNRWA remains the international community's greatest asset in the region.
+Madam Chair,
+Lastly,
+Looking at the day after, one must acknowledge that there is no going back to the pre-war status quo that fueled the present disaster.
+The biggest open-air prison, over two million people under air, sea, and land blockade for 16 years - that status quo cannot be tenable.
+Israelis and Palestinians are neighbors. Their fates are intertwined. They will need to find a way to co-exist, and the actions being taken today against the civilian population of Gaza will only poison that shared future.
+A political solution has become a matter of life and death for millions of people and must be put firmly back on the table.
+A genuine prospect of Palestinian statehood and security for all people is critical to stabilize the current situation and to step back from the brink, before it's too late.
+I urge all Member States to change the trajectory of this crisis, and with your help, UNRWA is ready to do its part.
+Thank you.
+FOR MORE INFORMATION, PLEASE CONTACT:
+Louise Wateridge
+Global Media Requests
+Mobile:
++972-54-240-2716 (Whatsapp)
+UNRWA on Twitter:
+Website:
+Lily Esposito
+[English / French language] European Media Requests
+Mobile:
++972-54-240-2680 (Whatsapp preferred)
+Estefania Diaz
+[English / French / Spanish / German language] European Media Requests
+Mobile:
++32-473-82-2006 (WhatsApp)
+On Twitter:
+UNRWA on Twitter:
+Asako Nitta
+[Japanese language] Japanese Media Requests
+Mobile:
++972 54-240-2727
+UNRWA on Twitter:</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:09:52.797028+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>UNRWA-OCHA Joint Sit-Rep Report #13 on the situation in Ein el Hilweh camp, Lebanon (As of 1600hrs, Friday October 2023) - Lebanon</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://reliefweb.int/report/lebanon/unrwa-ocha-joint-sit-rep-report-13-situation-ein-el-hilweh-camp-lebanon-1600hrs-friday-october-2023</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2023-10-08</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>This report is produced jointly by UNRWA and OCHA Lebanon. It covers the period from 30 September to 6 October 2023. Reports will be issued each Friday, with more frequent reporting if the situation requires.
+HIGHLIGHTS
+- The ceasefire in Ein el Hilweh camp continued to hold between 30 September and 6 October, although underlying tensions remained.
+- Displaced persons continued to return to the camp. As a result, the last remaining UNRWA designated emergency shelter closed on 6 October, with only the Fawar non-UNRWA collective site still hosting a small number of displaced families.
+- However, over 2,700 households are recorded as having been displaced in emergency shelters or hosted in the community (noting, however, the fluidity of the situation makes precise counting challenging). Many of those still displaced are believed to have come from parts of the camp in which fighting was concentrated and where many shelters were damaged or destroyed. Others are families facing a safety risk related to the occupation of their shelters by armed actors or their being barred from their homes (for example, youths above 16 years old have faced challenges returning to some neighborhoods).
+- The armed actors who had been occupying two UNRWA compounds containing eight schools reportedly vacated the premises on 29 September after the deployment of the Joint Security Force, which reportedly remained inside one of the two school complexes. UNRWA has not received formal communication from relevant camp governance actors about the status of schools and has not been able to access the area of the school compounds due to the prevailing security situation.
+- UNRWA is carrying out its regular sanitation services in areas assessed as accessible within Ein el Hilweh camp. The resumption of other services will be dependent on an assessment of security conditions in the camp.
+SITUATION OVERVIEW
+The ceasefire was maintained in Ein el Hilweh camp as the inter-factional Palestinian Joint Security Force (JSF) continued to deploy in parts of the camp, including the areas where the two UNRWA school compounds that had been occupied by armed actors are located. The JSF has not yet deployed to the Hittin neighbourhood, one of the flashpoints in the last round of fighting.
+Families who had fled the camp reportedly continued to return to their homes. The number of people in UNRWA designated emergency shelters (DES) dropped from 427 to zero between 28 September and 6 October. On 6 October, UNRWA closed its final remaining DES in the Siblin Training Centre, having closed the DES in Bir Zeit school in Siblin and Nablus School in Saida earlier in the week (in addition to Beit Jala DES, which had closed earlier, as previously reported). All non-UNRWA collective sites are also now empty of displaced persons except for the collective site in al Fawar.
+However, a large number of camp residents remain displaced, including many who are unable to return to their shelters due to their damage or destruction. Alongside the approximately 30 people in al Fawar collective site, at least 2,700 households are reported to have been sheltering with relatives or elsewhere in the community. During this reporting period, some families reportedly departed the camp to seek new accommodation in the Saida area. UNRWA and partners have devised a joint mechanism for the distribution of multi-purpose cash assistance for those whose shelters have been damaged or destroyed. Details will be announced shortly.
+UNRWA is preparing for an assessment of damage to its installations inside the camp and the removal of rubble, with work to begin once security conditions allow. UNRWA continued providing sanitation services in parts of the camp less affected by the clashes, working in conjunction with a private contractor. Approximately 200 tons of garbage were removed between 2 and 6 October.
+UNRWA has not yet received formal confirmation that its eight schools in Ein el Hilweh have been vacated by all armed persons. Due to the serious damage these schools have sustained during the clashes, as well as the use of three other Saida-area schools to host displaced families, the opening of UNRWA schools in Saida, which had been scheduled for 2 October, will be postponed for more than 11,000 Palestine refugee children. UNRWA is in the final stages of preparing alternative arrangements to ensure children in and around the camp are able to return to school as soon as possible.
+Disclaimer
+- UN Office for the Coordination of Humanitarian Affairs
+- To learn more about OCHA's activities, please visit https://www.unocha.org/.</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:09:58.853284+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
